--- a/BELGRANO 1646/Mayo/MAYO-BLG1646.xlsx
+++ b/BELGRANO 1646/Mayo/MAYO-BLG1646.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BELGRANO 1646\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FCE3E2E-B2E1-41F9-B8D4-D58C2866832E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB448BAD-8ACD-49C0-B26B-10029C718689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$134</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$143</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="169">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -504,30 +504,9 @@
     <t>JPL - Articulos de limpieza 14/04</t>
   </si>
   <si>
-    <t>Agua porteria - Bidones - Consumo de un año</t>
-  </si>
-  <si>
-    <t>Casa ruan compra de disyuntor</t>
-  </si>
-  <si>
-    <t>Servisur - reemplazo sensor de movimiento</t>
-  </si>
-  <si>
-    <t>Casa ruan compra de sensor</t>
-  </si>
-  <si>
-    <t>Hidraulica Rubber - Cepillo pileta</t>
-  </si>
-  <si>
-    <t>Gabriel Villegas - Desvinculacion contrato ADS</t>
-  </si>
-  <si>
     <t>Fumigacion 9/04</t>
   </si>
   <si>
-    <t>Compra motor PPA - Porton acceso al montavehiculos</t>
-  </si>
-  <si>
     <t>FEUILLANT, GASTON</t>
   </si>
   <si>
@@ -549,13 +528,46 @@
     <t>Energoup MES DE MAYO</t>
   </si>
   <si>
-    <t>Mes de MAYO 23/04</t>
-  </si>
-  <si>
     <t>EN TEORIA EN ESTE PUNTO (MAYO DEL 2025) LA CAJA NOS DA BIEN, TENEMOS 1,4M EN EL BANCO Y CERCA DE 120MIL PESOS EN EFECTIVO</t>
   </si>
   <si>
     <t>Ingreso mes de ABRIL</t>
+  </si>
+  <si>
+    <t>Ruso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kromacolor  -  Recuplast </t>
+  </si>
+  <si>
+    <t>Lucas</t>
+  </si>
+  <si>
+    <t>Sur Energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mes de MAYO </t>
+  </si>
+  <si>
+    <t>Ferreteria</t>
+  </si>
+  <si>
+    <t>Contessi provision y colocacion de 60 lts de aceite hidraulico en la sede del monta auto</t>
+  </si>
+  <si>
+    <t>Salvatierra limpieza de columna de baño desde piso 3 (inclusive) hasta el piso 10 (inclusive)</t>
+  </si>
+  <si>
+    <t>Remis Sr. Diego - Dia de paro</t>
+  </si>
+  <si>
+    <t>Alejandro 1646</t>
+  </si>
+  <si>
+    <t>Contessi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camaras del sur 19/05 </t>
   </si>
 </sst>
 </file>
@@ -1283,7 +1295,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="244">
+  <cellXfs count="252">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
@@ -1570,92 +1582,126 @@
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1683,19 +1729,7 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2069,7 +2103,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N144"/>
+  <dimension ref="A1:N153"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.44140625" customWidth="1"/>
@@ -2126,10 +2160,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C5" s="71" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D5" s="71"/>
       <c r="E5" s="72"/>
@@ -2157,26 +2191,26 @@
     <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="203" t="s">
+      <c r="B14" s="204" t="s">
         <v>135</v>
       </c>
-      <c r="C14" s="204"/>
-      <c r="D14" s="205"/>
+      <c r="C14" s="205"/>
+      <c r="D14" s="206"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="206"/>
-      <c r="C15" s="207"/>
-      <c r="D15" s="208"/>
+      <c r="B15" s="207"/>
+      <c r="C15" s="208"/>
+      <c r="D15" s="209"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="206"/>
-      <c r="C16" s="207"/>
-      <c r="D16" s="208"/>
+      <c r="B16" s="207"/>
+      <c r="C16" s="208"/>
+      <c r="D16" s="209"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="209"/>
-      <c r="C17" s="210"/>
-      <c r="D17" s="211"/>
+      <c r="B17" s="210"/>
+      <c r="C17" s="211"/>
+      <c r="D17" s="212"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
@@ -2201,7 +2235,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="130"/>
@@ -2652,7 +2686,7 @@
         <v>140</v>
       </c>
       <c r="C53" s="7"/>
-      <c r="D53" s="199">
+      <c r="D53" s="198">
         <f>102143.27+6011.02+54099.18</f>
         <v>162253.47</v>
       </c>
@@ -2674,7 +2708,7 @@
         <v>139</v>
       </c>
       <c r="C54" s="7"/>
-      <c r="D54" s="199">
+      <c r="D54" s="198">
         <v>532295.61</v>
       </c>
       <c r="E54" s="134">
@@ -2725,169 +2759,137 @@
       <c r="F56" s="7"/>
       <c r="H56" s="150"/>
     </row>
-    <row r="57" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="195" t="s">
-        <v>141</v>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="114" t="s">
+        <v>163</v>
       </c>
       <c r="B57" s="179"/>
       <c r="C57" s="180"/>
       <c r="D57" s="200">
+        <v>700000</v>
+      </c>
+      <c r="E57" s="115"/>
+      <c r="F57" s="7"/>
+      <c r="H57" s="150"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" s="114" t="s">
+        <v>167</v>
+      </c>
+      <c r="B58" s="179"/>
+      <c r="C58" s="180"/>
+      <c r="D58" s="200">
+        <v>300000</v>
+      </c>
+      <c r="E58" s="115"/>
+      <c r="F58" s="7"/>
+      <c r="H58" s="150"/>
+    </row>
+    <row r="59" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="195" t="s">
+        <v>141</v>
+      </c>
+      <c r="B59" s="179"/>
+      <c r="C59" s="180"/>
+      <c r="D59" s="199">
         <v>330000</v>
       </c>
-      <c r="E57" s="149">
-        <f>D57</f>
+      <c r="E59" s="149">
+        <f>D59</f>
         <v>330000</v>
       </c>
-      <c r="F57" s="7"/>
-      <c r="G57" s="109">
-        <f>D57</f>
+      <c r="F59" s="7"/>
+      <c r="G59" s="109">
+        <f>D59</f>
         <v>330000</v>
       </c>
-      <c r="H57" s="161">
-        <f>E57+F57</f>
+      <c r="H59" s="161">
+        <f>E59+F59</f>
         <v>330000</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="121" t="s">
+    <row r="60" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="B58" s="164"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="113">
-        <v>0</v>
-      </c>
-      <c r="E58" s="149">
-        <f t="shared" ref="E58:E63" si="8">D58*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F58" s="134">
-        <f t="shared" ref="F58:F63" si="9">D58*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G58" s="109">
-        <f t="shared" ref="G58:G75" si="10">D58</f>
-        <v>0</v>
-      </c>
-      <c r="H58" s="161">
-        <f t="shared" ref="H58:H75" si="11">E58+F58</f>
-        <v>0</v>
-      </c>
-      <c r="I58" t="str">
-        <f t="shared" ref="I58:I74" si="12">IF(G58=H58, "", "Error")</f>
+      <c r="B60" s="164"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="198">
+        <v>118708.63</v>
+      </c>
+      <c r="E60" s="149">
+        <f t="shared" ref="E60:E65" si="8">D60*91.91%</f>
+        <v>109105.10183299999</v>
+      </c>
+      <c r="F60" s="134">
+        <f t="shared" ref="F60:F65" si="9">D60*8.09%</f>
+        <v>9603.5281670000004</v>
+      </c>
+      <c r="G60" s="109">
+        <f t="shared" ref="G60:G84" si="10">D60</f>
+        <v>118708.63</v>
+      </c>
+      <c r="H60" s="161">
+        <f t="shared" ref="H60:H84" si="11">E60+F60</f>
+        <v>118708.62999999999</v>
+      </c>
+      <c r="I60" t="str">
+        <f t="shared" ref="I60:I83" si="12">IF(G60=H60, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="94" t="s">
-        <v>161</v>
-      </c>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="113">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" s="94" t="s">
+        <v>154</v>
+      </c>
+      <c r="B61" s="7"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="198">
         <v>129675</v>
       </c>
-      <c r="E59" s="149">
+      <c r="E61" s="149">
         <f t="shared" si="8"/>
         <v>119184.2925</v>
       </c>
-      <c r="F59" s="134">
+      <c r="F61" s="134">
         <f t="shared" si="9"/>
         <v>10490.7075</v>
       </c>
-      <c r="G59" s="109">
+      <c r="G61" s="109">
         <f t="shared" si="10"/>
         <v>129675</v>
       </c>
-      <c r="H59" s="161">
+      <c r="H61" s="161">
         <f t="shared" si="11"/>
         <v>129675</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="94" t="s">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B62" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C60" s="7"/>
-      <c r="D60" s="113">
+      <c r="C62" s="7"/>
+      <c r="D62" s="113">
         <v>74622</v>
       </c>
-      <c r="E60" s="149">
+      <c r="E62" s="149">
         <f t="shared" si="8"/>
         <v>68585.080199999997</v>
       </c>
-      <c r="F60" s="134">
+      <c r="F62" s="134">
         <f t="shared" si="9"/>
         <v>6036.9197999999997</v>
       </c>
-      <c r="G60" s="109">
+      <c r="G62" s="109">
         <f t="shared" si="10"/>
         <v>74622</v>
       </c>
-      <c r="H60" s="161">
+      <c r="H62" s="161">
         <f t="shared" si="11"/>
         <v>74622</v>
-      </c>
-      <c r="I60" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="94" t="s">
-        <v>11</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C61" s="7"/>
-      <c r="D61" s="113">
-        <f>314851+309690.68</f>
-        <v>624541.67999999993</v>
-      </c>
-      <c r="E61" s="149">
-        <f t="shared" si="8"/>
-        <v>574016.25808799989</v>
-      </c>
-      <c r="F61" s="134">
-        <f t="shared" si="9"/>
-        <v>50525.421911999998</v>
-      </c>
-      <c r="G61" s="109">
-        <f t="shared" si="10"/>
-        <v>624541.67999999993</v>
-      </c>
-      <c r="H61" s="161"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="129" t="s">
-        <v>10</v>
-      </c>
-      <c r="B62" s="98" t="s">
-        <v>142</v>
-      </c>
-      <c r="C62" s="98"/>
-      <c r="D62" s="113">
-        <v>909879.28</v>
-      </c>
-      <c r="E62" s="149">
-        <f t="shared" si="8"/>
-        <v>836270.046248</v>
-      </c>
-      <c r="F62" s="134">
-        <f t="shared" si="9"/>
-        <v>73609.233752</v>
-      </c>
-      <c r="G62" s="109">
-        <f t="shared" si="10"/>
-        <v>909879.28</v>
-      </c>
-      <c r="H62" s="161">
-        <f t="shared" si="11"/>
-        <v>909879.28</v>
       </c>
       <c r="I62" t="str">
         <f t="shared" si="12"/>
@@ -2895,1062 +2897,1240 @@
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="129" t="s">
-        <v>145</v>
-      </c>
-      <c r="B63" s="98"/>
-      <c r="C63" s="98"/>
+      <c r="A63" s="94" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C63" s="7"/>
       <c r="D63" s="113">
-        <v>40000</v>
+        <f>314851+309690.68</f>
+        <v>624541.67999999993</v>
       </c>
       <c r="E63" s="149">
         <f t="shared" si="8"/>
-        <v>36764</v>
+        <v>574016.25808799989</v>
       </c>
       <c r="F63" s="134">
         <f t="shared" si="9"/>
-        <v>3236</v>
+        <v>50525.421911999998</v>
       </c>
       <c r="G63" s="109">
         <f t="shared" si="10"/>
+        <v>624541.67999999993</v>
+      </c>
+      <c r="H63" s="161"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64" s="129" t="s">
+        <v>10</v>
+      </c>
+      <c r="B64" s="98" t="s">
+        <v>142</v>
+      </c>
+      <c r="C64" s="98"/>
+      <c r="D64" s="198">
+        <v>909788.31</v>
+      </c>
+      <c r="E64" s="149">
+        <f t="shared" si="8"/>
+        <v>836186.43572099996</v>
+      </c>
+      <c r="F64" s="134">
+        <f t="shared" si="9"/>
+        <v>73601.874279000011</v>
+      </c>
+      <c r="G64" s="109">
+        <f t="shared" si="10"/>
+        <v>909788.31</v>
+      </c>
+      <c r="H64" s="161">
+        <f t="shared" si="11"/>
+        <v>909788.30999999994</v>
+      </c>
+      <c r="I64" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" s="129" t="s">
+        <v>145</v>
+      </c>
+      <c r="B65" s="98"/>
+      <c r="C65" s="98"/>
+      <c r="D65" s="113">
         <v>40000</v>
       </c>
-      <c r="H63" s="161">
+      <c r="E65" s="149">
+        <f t="shared" si="8"/>
+        <v>36764</v>
+      </c>
+      <c r="F65" s="134">
+        <f t="shared" si="9"/>
+        <v>3236</v>
+      </c>
+      <c r="G65" s="109">
+        <f t="shared" si="10"/>
+        <v>40000</v>
+      </c>
+      <c r="H65" s="161">
         <f t="shared" si="11"/>
         <v>40000</v>
       </c>
-      <c r="I63" t="str">
+      <c r="I65" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="98" t="s">
-        <v>148</v>
-      </c>
-      <c r="B64" s="183"/>
-      <c r="C64" s="184"/>
-      <c r="D64" s="113">
-        <v>113500</v>
-      </c>
-      <c r="E64" s="149">
-        <f t="shared" ref="E64:E69" si="13">D64</f>
-        <v>113500</v>
-      </c>
-      <c r="F64" s="134"/>
-      <c r="G64" s="109">
-        <f t="shared" si="10"/>
-        <v>113500</v>
-      </c>
-      <c r="H64" s="161">
-        <f t="shared" si="11"/>
-        <v>113500</v>
-      </c>
-      <c r="I64" s="181"/>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="215" t="s">
-        <v>150</v>
-      </c>
-      <c r="B65" s="216"/>
-      <c r="C65" s="217"/>
-      <c r="D65" s="113">
-        <v>22000</v>
-      </c>
-      <c r="E65" s="149">
-        <f t="shared" si="13"/>
-        <v>22000</v>
-      </c>
-      <c r="F65" s="134"/>
-      <c r="G65" s="109">
-        <f t="shared" si="10"/>
-        <v>22000</v>
-      </c>
-      <c r="H65" s="161">
-        <f t="shared" si="11"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="215" t="s">
-        <v>149</v>
-      </c>
-      <c r="B66" s="216"/>
-      <c r="C66" s="217"/>
-      <c r="D66" s="113">
-        <v>25000</v>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" s="98" t="s">
+        <v>168</v>
+      </c>
+      <c r="B66" s="183"/>
+      <c r="C66" s="184"/>
+      <c r="D66" s="198">
+        <v>235500</v>
       </c>
       <c r="E66" s="149">
-        <f t="shared" si="13"/>
-        <v>25000</v>
+        <f t="shared" ref="E66:E78" si="13">D66</f>
+        <v>235500</v>
       </c>
       <c r="F66" s="134"/>
       <c r="G66" s="109">
-        <f>D66</f>
-        <v>25000</v>
+        <f t="shared" si="10"/>
+        <v>235500</v>
       </c>
       <c r="H66" s="161">
         <f t="shared" si="11"/>
-        <v>25000</v>
-      </c>
-      <c r="I66" t="str">
-        <f>IF(G66=H66, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="215" t="s">
+        <v>235500</v>
+      </c>
+      <c r="I66" s="181"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" s="216" t="s">
         <v>157</v>
       </c>
-      <c r="B67" s="216"/>
-      <c r="C67" s="217"/>
-      <c r="D67" s="199">
-        <v>6000</v>
+      <c r="B67" s="217"/>
+      <c r="C67" s="218"/>
+      <c r="D67" s="198">
+        <v>111026</v>
       </c>
       <c r="E67" s="149">
         <f t="shared" si="13"/>
-        <v>6000</v>
+        <v>111026</v>
       </c>
       <c r="F67" s="134"/>
       <c r="G67" s="109">
-        <f>D67</f>
-        <v>6000</v>
+        <f t="shared" si="10"/>
+        <v>111026</v>
       </c>
       <c r="H67" s="161">
         <f t="shared" si="11"/>
-        <v>6000</v>
+        <v>111026</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="198" t="s">
-        <v>152</v>
-      </c>
-      <c r="B68" s="193"/>
-      <c r="C68" s="194"/>
-      <c r="D68" s="113">
-        <v>200000</v>
+      <c r="A68" s="216" t="s">
+        <v>160</v>
+      </c>
+      <c r="B68" s="217"/>
+      <c r="C68" s="218"/>
+      <c r="D68" s="198">
+        <f>104002.96</f>
+        <v>104002.96</v>
       </c>
       <c r="E68" s="149">
         <f t="shared" si="13"/>
-        <v>200000</v>
+        <v>104002.96</v>
       </c>
       <c r="F68" s="134"/>
       <c r="G68" s="109">
         <f>D68</f>
-        <v>200000</v>
+        <v>104002.96</v>
       </c>
       <c r="H68" s="161">
         <f t="shared" si="11"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" s="215" t="s">
-        <v>153</v>
-      </c>
-      <c r="B69" s="216"/>
-      <c r="C69" s="217"/>
-      <c r="D69" s="199">
-        <v>66000</v>
+        <v>104002.96</v>
+      </c>
+      <c r="I68" t="str">
+        <f>IF(G68=H68, "", "Error")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="216" t="s">
+        <v>160</v>
+      </c>
+      <c r="B69" s="217"/>
+      <c r="C69" s="218"/>
+      <c r="D69" s="198">
+        <f>104002.96</f>
+        <v>104002.96</v>
       </c>
       <c r="E69" s="149">
         <f t="shared" si="13"/>
+        <v>104002.96</v>
+      </c>
+      <c r="F69" s="134"/>
+      <c r="G69" s="109"/>
+      <c r="H69" s="161"/>
+    </row>
+    <row r="70" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="216" t="s">
+        <v>160</v>
+      </c>
+      <c r="B70" s="217"/>
+      <c r="C70" s="218"/>
+      <c r="D70" s="198">
+        <f>104002.96</f>
+        <v>104002.96</v>
+      </c>
+      <c r="E70" s="149">
+        <f t="shared" si="13"/>
+        <v>104002.96</v>
+      </c>
+      <c r="F70" s="134"/>
+      <c r="G70" s="109"/>
+      <c r="H70" s="161"/>
+    </row>
+    <row r="71" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="216" t="s">
+        <v>160</v>
+      </c>
+      <c r="B71" s="217"/>
+      <c r="C71" s="218"/>
+      <c r="D71" s="198">
+        <f>104002.96</f>
+        <v>104002.96</v>
+      </c>
+      <c r="E71" s="149">
+        <f t="shared" si="13"/>
+        <v>104002.96</v>
+      </c>
+      <c r="F71" s="134"/>
+      <c r="G71" s="109"/>
+      <c r="H71" s="161"/>
+    </row>
+    <row r="72" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="201" t="s">
+        <v>166</v>
+      </c>
+      <c r="B72" s="175"/>
+      <c r="C72" s="202"/>
+      <c r="D72" s="198">
+        <v>100419.01</v>
+      </c>
+      <c r="E72" s="149"/>
+      <c r="F72" s="134"/>
+      <c r="G72" s="109"/>
+      <c r="H72" s="161"/>
+    </row>
+    <row r="73" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="201" t="s">
+        <v>166</v>
+      </c>
+      <c r="B73" s="175"/>
+      <c r="C73" s="202"/>
+      <c r="D73" s="198">
+        <v>97003.05</v>
+      </c>
+      <c r="E73" s="149"/>
+      <c r="F73" s="134"/>
+      <c r="G73" s="109"/>
+      <c r="H73" s="161"/>
+    </row>
+    <row r="74" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="227" t="s">
+        <v>150</v>
+      </c>
+      <c r="B74" s="228"/>
+      <c r="C74" s="229"/>
+      <c r="D74" s="198">
+        <v>6000</v>
+      </c>
+      <c r="E74" s="149">
+        <f t="shared" si="13"/>
+        <v>6000</v>
+      </c>
+      <c r="F74" s="134"/>
+      <c r="G74" s="109">
+        <f>D74</f>
+        <v>6000</v>
+      </c>
+      <c r="H74" s="161">
+        <f t="shared" si="11"/>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="227" t="s">
+        <v>165</v>
+      </c>
+      <c r="B75" s="228"/>
+      <c r="C75" s="229"/>
+      <c r="D75" s="198">
+        <v>7000</v>
+      </c>
+      <c r="E75" s="149">
+        <f t="shared" si="13"/>
+        <v>7000</v>
+      </c>
+      <c r="F75" s="134"/>
+      <c r="G75" s="109"/>
+      <c r="H75" s="161"/>
+    </row>
+    <row r="76" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="203"/>
+      <c r="B76" s="193"/>
+      <c r="C76" s="194"/>
+      <c r="D76" s="198">
+        <v>98393.96</v>
+      </c>
+      <c r="E76" s="149">
+        <f t="shared" si="13"/>
+        <v>98393.96</v>
+      </c>
+      <c r="F76" s="134"/>
+      <c r="G76" s="109">
+        <f>D76</f>
+        <v>98393.96</v>
+      </c>
+      <c r="H76" s="161">
+        <f t="shared" si="11"/>
+        <v>98393.96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" s="227" t="s">
+        <v>147</v>
+      </c>
+      <c r="B77" s="228"/>
+      <c r="C77" s="229"/>
+      <c r="D77" s="198">
         <v>66000</v>
       </c>
-      <c r="F69" s="134"/>
-      <c r="G69" s="109">
+      <c r="E77" s="149">
+        <f t="shared" si="13"/>
+        <v>66000</v>
+      </c>
+      <c r="F77" s="134"/>
+      <c r="G77" s="109">
         <f t="shared" si="10"/>
         <v>66000</v>
       </c>
-      <c r="H69" s="161">
+      <c r="H77" s="161">
         <f t="shared" si="11"/>
         <v>66000</v>
       </c>
-      <c r="I69" t="str">
+      <c r="I77" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="7" t="s">
+    <row r="78" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="230" t="s">
+        <v>164</v>
+      </c>
+      <c r="B78" s="231"/>
+      <c r="C78" s="194"/>
+      <c r="D78" s="198">
+        <v>218400</v>
+      </c>
+      <c r="E78" s="149">
+        <f t="shared" si="13"/>
+        <v>218400</v>
+      </c>
+      <c r="F78" s="134"/>
+      <c r="G78" s="109"/>
+      <c r="H78" s="161"/>
+    </row>
+    <row r="79" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B70" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="113">
+      <c r="B79" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C79" s="7"/>
+      <c r="D79" s="198">
         <v>79895</v>
       </c>
-      <c r="E70" s="149">
-        <f t="shared" ref="E70:E75" si="14">D70</f>
+      <c r="E79" s="149">
+        <f t="shared" ref="E79:E84" si="14">D79</f>
         <v>79895</v>
       </c>
-      <c r="F70" s="7"/>
-      <c r="G70" s="109">
+      <c r="F79" s="7"/>
+      <c r="G79" s="109">
         <f t="shared" si="10"/>
         <v>79895</v>
       </c>
-      <c r="H70" s="161">
+      <c r="H79" s="161">
         <f t="shared" si="11"/>
         <v>79895</v>
       </c>
-      <c r="I70" t="str">
+      <c r="I79" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="94" t="s">
-        <v>147</v>
-      </c>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="113">
-        <v>96300</v>
-      </c>
-      <c r="E71" s="149">
-        <f t="shared" ref="E71" si="15">D71*91.91%</f>
-        <v>88509.329999999987</v>
-      </c>
-      <c r="F71" s="134">
-        <f t="shared" ref="F71" si="16">D71*8.09%</f>
-        <v>7790.67</v>
-      </c>
-      <c r="G71" s="109">
+    <row r="80" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="94" t="s">
+        <v>162</v>
+      </c>
+      <c r="B80" s="7"/>
+      <c r="C80" s="7"/>
+      <c r="D80" s="198">
+        <v>6530.7</v>
+      </c>
+      <c r="E80" s="149">
+        <f t="shared" ref="E80" si="15">D80*91.91%</f>
+        <v>6002.3663699999997</v>
+      </c>
+      <c r="F80" s="134">
+        <f t="shared" ref="F80" si="16">D80*8.09%</f>
+        <v>528.33362999999997</v>
+      </c>
+      <c r="G80" s="109">
         <f t="shared" si="10"/>
-        <v>96300</v>
-      </c>
-      <c r="H71" s="161">
+        <v>6530.7</v>
+      </c>
+      <c r="H80" s="161">
         <f t="shared" si="11"/>
-        <v>96299.999999999985</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="113">
-        <v>460000</v>
-      </c>
-      <c r="E72" s="149">
+        <v>6530.7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="198">
+        <v>10391.24</v>
+      </c>
+      <c r="E81" s="149">
         <f t="shared" si="14"/>
-        <v>460000</v>
-      </c>
-      <c r="F72" s="7"/>
-      <c r="G72" s="109">
+        <v>10391.24</v>
+      </c>
+      <c r="F81" s="7"/>
+      <c r="G81" s="109">
         <f t="shared" si="10"/>
-        <v>460000</v>
-      </c>
-      <c r="H72" s="161"/>
-    </row>
-    <row r="73" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="199">
+        <v>10391.24</v>
+      </c>
+      <c r="H81" s="161"/>
+    </row>
+    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B82" s="7"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="198">
         <v>120000</v>
       </c>
-      <c r="E73" s="149">
+      <c r="E82" s="149">
         <f t="shared" si="14"/>
         <v>120000</v>
       </c>
-      <c r="F73" s="7"/>
-      <c r="G73" s="109">
+      <c r="F82" s="7"/>
+      <c r="G82" s="109">
         <f t="shared" si="10"/>
         <v>120000</v>
       </c>
-      <c r="H73" s="161"/>
-    </row>
-    <row r="74" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="98" t="s">
-        <v>151</v>
-      </c>
-      <c r="B74" s="114"/>
-      <c r="C74" s="163"/>
-      <c r="D74" s="113">
-        <v>11800</v>
-      </c>
-      <c r="E74" s="149">
+      <c r="H82" s="161"/>
+    </row>
+    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="98" t="s">
+        <v>159</v>
+      </c>
+      <c r="B83" s="114"/>
+      <c r="C83" s="163"/>
+      <c r="D83" s="198">
+        <v>80000</v>
+      </c>
+      <c r="E83" s="149">
         <f t="shared" si="14"/>
-        <v>11800</v>
-      </c>
-      <c r="F74" s="134"/>
-      <c r="G74" s="109">
+        <v>80000</v>
+      </c>
+      <c r="F83" s="134"/>
+      <c r="G83" s="109">
         <f t="shared" si="10"/>
-        <v>11800</v>
-      </c>
-      <c r="H74" s="161">
+        <v>80000</v>
+      </c>
+      <c r="H83" s="161">
         <f t="shared" si="11"/>
-        <v>11800</v>
-      </c>
-      <c r="I74" t="str">
+        <v>80000</v>
+      </c>
+      <c r="I83" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A75" s="155"/>
-      <c r="B75" s="156"/>
-      <c r="C75" s="156"/>
-      <c r="D75" s="167"/>
-      <c r="E75" s="149">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84" s="155"/>
+      <c r="B84" s="156"/>
+      <c r="C84" s="156"/>
+      <c r="D84" s="167"/>
+      <c r="E84" s="149">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="F75" s="134"/>
-      <c r="G75" s="109">
+      <c r="F84" s="134"/>
+      <c r="G84" s="109">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="H75" s="161">
+      <c r="H84" s="161">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I75" t="str">
-        <f>IF(G75=H75, "", "Error")</f>
+      <c r="I84" t="str">
+        <f>IF(G84=H84, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A76" s="96" t="s">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="B76" s="96"/>
-      <c r="C76" s="96"/>
-      <c r="D76" s="108">
-        <f>SUM(D58:D75)</f>
-        <v>2979212.96</v>
-      </c>
-      <c r="E76" s="108">
-        <f>SUM(E58:E75)</f>
-        <v>2827524.007036</v>
-      </c>
-      <c r="F76" s="108">
-        <f>SUM(F58:F75)</f>
-        <v>151688.95296400003</v>
-      </c>
-      <c r="G76" s="109">
-        <f>E76+F76</f>
-        <v>2979212.96</v>
-      </c>
-      <c r="H76" s="150" t="str">
-        <f>IF(D76=G76, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="189"/>
-      <c r="E77" s="115"/>
-      <c r="F77" s="7"/>
-      <c r="H77" s="150"/>
-    </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="7"/>
-      <c r="B78" s="7"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="189"/>
-      <c r="E78" s="114"/>
-      <c r="F78" s="7"/>
-      <c r="H78" s="150"/>
-    </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="7"/>
-      <c r="B79" s="7"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="189"/>
-      <c r="E79" s="114"/>
-      <c r="F79" s="7"/>
-      <c r="H79" s="150"/>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A80" s="94" t="s">
-        <v>146</v>
-      </c>
-      <c r="B80" s="98"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="113">
-        <v>186900</v>
-      </c>
-      <c r="E80" s="149">
-        <f>D80*91.91%</f>
-        <v>171779.78999999998</v>
-      </c>
-      <c r="F80" s="134">
-        <f>D80*8.09%</f>
-        <v>15120.21</v>
-      </c>
-      <c r="G80" s="160"/>
-      <c r="H80" s="150"/>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A81" s="98"/>
-      <c r="B81" s="162"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="113"/>
-      <c r="E81" s="149">
-        <f>D81</f>
-        <v>0</v>
-      </c>
-      <c r="F81" s="134"/>
-      <c r="H81" s="150"/>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A82" s="7"/>
-      <c r="B82" s="7"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="113"/>
-      <c r="E82" s="165">
-        <f>D82</f>
-        <v>0</v>
-      </c>
-      <c r="F82" s="7"/>
-      <c r="H82" s="150"/>
-      <c r="I82" s="109"/>
-    </row>
-    <row r="83" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="95" t="s">
-        <v>17</v>
-      </c>
-      <c r="B83" s="95"/>
-      <c r="C83" s="95"/>
-      <c r="D83" s="107">
-        <f>SUM(D80:D82)</f>
-        <v>186900</v>
-      </c>
-      <c r="E83" s="107">
-        <f>SUM(E80:E82)</f>
-        <v>171779.78999999998</v>
-      </c>
-      <c r="F83" s="107">
-        <f>SUM(F80:F82)</f>
-        <v>15120.21</v>
-      </c>
-      <c r="G83" s="109">
-        <f>E83+F83</f>
-        <v>186899.99999999997</v>
-      </c>
-      <c r="H83" s="150" t="str">
-        <f>IF(D83=G83, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="J83" s="109"/>
-    </row>
-    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="7"/>
-      <c r="B84" s="7"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="189"/>
-      <c r="E84" s="115"/>
-      <c r="F84" s="7"/>
-      <c r="H84" s="150"/>
-    </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="7"/>
-      <c r="B85" s="7"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="189"/>
-      <c r="E85" s="114"/>
-      <c r="F85" s="7"/>
-      <c r="H85" s="150"/>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A86" s="94" t="s">
-        <v>13</v>
-      </c>
+      <c r="B85" s="96"/>
+      <c r="C85" s="96"/>
+      <c r="D85" s="108">
+        <f>SUM(D60:D84)</f>
+        <v>3549906.42</v>
+      </c>
+      <c r="E85" s="108">
+        <f>SUM(E60:E84)</f>
+        <v>3198461.5747119999</v>
+      </c>
+      <c r="F85" s="108">
+        <f>SUM(F60:F84)</f>
+        <v>154022.78528800001</v>
+      </c>
+      <c r="G85" s="109">
+        <f>E85+F85</f>
+        <v>3352484.36</v>
+      </c>
+      <c r="H85" s="150" t="str">
+        <f>IF(D85=G85, "", "Error")</f>
+        <v>Error</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
       <c r="D86" s="189"/>
-      <c r="E86" s="114"/>
+      <c r="E86" s="115"/>
       <c r="F86" s="7"/>
       <c r="H86" s="150"/>
     </row>
-    <row r="87" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="94" t="s">
-        <v>14</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>117</v>
-      </c>
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="7"/>
+      <c r="B87" s="7"/>
       <c r="C87" s="7"/>
-      <c r="D87" s="199">
-        <v>222264.92</v>
-      </c>
-      <c r="E87" s="149">
-        <f>D87*91.91%</f>
-        <v>204283.68797199999</v>
-      </c>
-      <c r="F87" s="134">
-        <f>D87*8.09%</f>
-        <v>17981.232028000002</v>
-      </c>
+      <c r="D87" s="189"/>
+      <c r="E87" s="114"/>
+      <c r="F87" s="7"/>
       <c r="H87" s="150"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A88" s="94" t="s">
-        <v>108</v>
-      </c>
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="7"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
-      <c r="D88" s="199">
-        <v>28000</v>
-      </c>
-      <c r="E88" s="149">
-        <f>D88*91.91%</f>
-        <v>25734.799999999999</v>
-      </c>
-      <c r="F88" s="134">
-        <f>D88*8.09%</f>
-        <v>2265.1999999999998</v>
-      </c>
+      <c r="D88" s="189"/>
+      <c r="E88" s="114"/>
+      <c r="F88" s="7"/>
       <c r="H88" s="150"/>
-      <c r="J88" s="113"/>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A89" s="7"/>
-      <c r="B89" s="7"/>
+      <c r="A89" s="94" t="s">
+        <v>146</v>
+      </c>
+      <c r="B89" s="98"/>
       <c r="C89" s="7"/>
-      <c r="D89" s="189"/>
-      <c r="E89" s="116"/>
-      <c r="F89" s="7"/>
+      <c r="D89" s="113">
+        <v>186900</v>
+      </c>
+      <c r="E89" s="149">
+        <f>D89*91.91%</f>
+        <v>171779.78999999998</v>
+      </c>
+      <c r="F89" s="134">
+        <f>D89*8.09%</f>
+        <v>15120.21</v>
+      </c>
+      <c r="G89" s="160"/>
       <c r="H89" s="150"/>
-      <c r="J89" s="109"/>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A90" s="95" t="s">
-        <v>101</v>
-      </c>
-      <c r="B90" s="95"/>
-      <c r="C90" s="95"/>
-      <c r="D90" s="107">
-        <f>SUM(D87:D89)</f>
-        <v>250264.92</v>
-      </c>
-      <c r="E90" s="107">
-        <f>SUM(E87:E89)</f>
-        <v>230018.48797199997</v>
-      </c>
-      <c r="F90" s="107">
-        <f>SUM(F87:F89)</f>
-        <v>20246.432028000003</v>
-      </c>
-      <c r="G90" s="109">
-        <f>E90+F90</f>
-        <v>250264.91999999998</v>
-      </c>
-      <c r="H90" s="150" t="str">
-        <f>IF(D90=G90, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="J90" s="109"/>
-    </row>
-    <row r="91" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="98"/>
+      <c r="B90" s="162"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="113"/>
+      <c r="E90" s="149">
+        <f>D90</f>
+        <v>0</v>
+      </c>
+      <c r="F90" s="134"/>
+      <c r="H90" s="150"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
       <c r="D91" s="113"/>
-      <c r="E91" s="117"/>
+      <c r="E91" s="165">
+        <f>D91</f>
+        <v>0</v>
+      </c>
       <c r="F91" s="7"/>
       <c r="H91" s="150"/>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A92" s="94" t="s">
+      <c r="I91" s="109"/>
+    </row>
+    <row r="92" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="95" t="s">
+        <v>17</v>
+      </c>
+      <c r="B92" s="95"/>
+      <c r="C92" s="95"/>
+      <c r="D92" s="107">
+        <f>SUM(D89:D91)</f>
+        <v>186900</v>
+      </c>
+      <c r="E92" s="107">
+        <f>SUM(E89:E91)</f>
+        <v>171779.78999999998</v>
+      </c>
+      <c r="F92" s="107">
+        <f>SUM(F89:F91)</f>
+        <v>15120.21</v>
+      </c>
+      <c r="G92" s="109">
+        <f>E92+F92</f>
+        <v>186899.99999999997</v>
+      </c>
+      <c r="H92" s="150" t="str">
+        <f>IF(D92=G92, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J92" s="109"/>
+    </row>
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="7"/>
+      <c r="B93" s="7"/>
+      <c r="C93" s="7"/>
+      <c r="D93" s="189"/>
+      <c r="E93" s="115"/>
+      <c r="F93" s="7"/>
+      <c r="H93" s="150"/>
+    </row>
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="7"/>
+      <c r="B94" s="7"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="189"/>
+      <c r="E94" s="114"/>
+      <c r="F94" s="7"/>
+      <c r="H94" s="150"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A95" s="94" t="s">
+        <v>13</v>
+      </c>
+      <c r="B95" s="7"/>
+      <c r="C95" s="7"/>
+      <c r="D95" s="189"/>
+      <c r="E95" s="114"/>
+      <c r="F95" s="7"/>
+      <c r="H95" s="150"/>
+    </row>
+    <row r="96" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="94" t="s">
+        <v>14</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C96" s="7"/>
+      <c r="D96" s="198">
+        <v>222264.92</v>
+      </c>
+      <c r="E96" s="149">
+        <f>D96*91.91%</f>
+        <v>204283.68797199999</v>
+      </c>
+      <c r="F96" s="134">
+        <f>D96*8.09%</f>
+        <v>17981.232028000002</v>
+      </c>
+      <c r="H96" s="150"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A97" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="B97" s="7"/>
+      <c r="C97" s="7"/>
+      <c r="D97" s="198">
+        <v>28000</v>
+      </c>
+      <c r="E97" s="149">
+        <f>D97*91.91%</f>
+        <v>25734.799999999999</v>
+      </c>
+      <c r="F97" s="134">
+        <f>D97*8.09%</f>
+        <v>2265.1999999999998</v>
+      </c>
+      <c r="H97" s="150"/>
+      <c r="J97" s="113"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A98" s="7"/>
+      <c r="B98" s="7"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="189"/>
+      <c r="E98" s="116"/>
+      <c r="F98" s="7"/>
+      <c r="H98" s="150"/>
+      <c r="J98" s="109"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A99" s="95" t="s">
+        <v>101</v>
+      </c>
+      <c r="B99" s="95"/>
+      <c r="C99" s="95"/>
+      <c r="D99" s="107">
+        <f>SUM(D96:D98)</f>
+        <v>250264.92</v>
+      </c>
+      <c r="E99" s="107">
+        <f>SUM(E96:E98)</f>
+        <v>230018.48797199997</v>
+      </c>
+      <c r="F99" s="107">
+        <f>SUM(F96:F98)</f>
+        <v>20246.432028000003</v>
+      </c>
+      <c r="G99" s="109">
+        <f>E99+F99</f>
+        <v>250264.91999999998</v>
+      </c>
+      <c r="H99" s="150" t="str">
+        <f>IF(D99=G99, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J99" s="109"/>
+    </row>
+    <row r="100" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="7"/>
+      <c r="B100" s="7"/>
+      <c r="C100" s="7"/>
+      <c r="D100" s="113"/>
+      <c r="E100" s="117"/>
+      <c r="F100" s="7"/>
+      <c r="H100" s="150"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A101" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="B92" s="7"/>
-      <c r="C92" s="7"/>
-      <c r="D92" s="113">
+      <c r="B101" s="7"/>
+      <c r="C101" s="7"/>
+      <c r="D101" s="113">
         <v>96626.92</v>
       </c>
-      <c r="E92" s="149">
-        <f>D92*91.91%</f>
+      <c r="E101" s="149">
+        <f>D101*91.91%</f>
         <v>88809.802171999996</v>
       </c>
-      <c r="F92" s="134">
-        <f>D92*8.09%</f>
+      <c r="F101" s="134">
+        <f>D101*8.09%</f>
         <v>7817.1178279999995</v>
       </c>
-      <c r="H92" s="150"/>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A93" s="94" t="s">
+      <c r="H101" s="150"/>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A102" s="94" t="s">
         <v>103</v>
       </c>
-      <c r="B93" s="7"/>
-      <c r="C93" s="122"/>
-      <c r="D93" s="113">
+      <c r="B102" s="7"/>
+      <c r="C102" s="122"/>
+      <c r="D102" s="113">
         <v>44400</v>
       </c>
-      <c r="E93" s="149">
-        <f>D93*91.91%</f>
+      <c r="E102" s="149">
+        <f>D102*91.91%</f>
         <v>40808.039999999994</v>
       </c>
-      <c r="F93" s="134">
-        <f>D93*8.09%</f>
+      <c r="F102" s="134">
+        <f>D102*8.09%</f>
         <v>3591.96</v>
       </c>
-      <c r="H93" s="150"/>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A94" s="95" t="s">
+      <c r="H102" s="150"/>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A103" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="B94" s="95"/>
-      <c r="C94" s="95"/>
-      <c r="D94" s="158">
-        <f>SUM(D92:D93)</f>
+      <c r="B103" s="95"/>
+      <c r="C103" s="95"/>
+      <c r="D103" s="158">
+        <f>SUM(D101:D102)</f>
         <v>141026.91999999998</v>
       </c>
-      <c r="E94" s="147">
-        <f t="shared" ref="E94:F94" si="17">SUM(E92:E93)</f>
+      <c r="E103" s="147">
+        <f t="shared" ref="E103:F103" si="17">SUM(E101:E102)</f>
         <v>129617.84217199999</v>
       </c>
-      <c r="F94" s="147">
+      <c r="F103" s="147">
         <f t="shared" si="17"/>
         <v>11409.077827999999</v>
       </c>
-      <c r="G94" s="109">
-        <f>E94+F94</f>
+      <c r="G103" s="109">
+        <f>E103+F103</f>
         <v>141026.91999999998</v>
       </c>
-      <c r="H94" s="150" t="str">
-        <f>IF(D94=G94, "", "Error")</f>
+      <c r="H103" s="150" t="str">
+        <f>IF(D103=G103, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="7"/>
-      <c r="B95" s="7"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="190"/>
-      <c r="E95" s="12"/>
-      <c r="F95" s="7"/>
-      <c r="H95" s="150"/>
-    </row>
-    <row r="96" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="99" t="s">
+    <row r="104" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="7"/>
+      <c r="B104" s="7"/>
+      <c r="C104" s="7"/>
+      <c r="D104" s="190"/>
+      <c r="E104" s="12"/>
+      <c r="F104" s="7"/>
+      <c r="H104" s="150"/>
+    </row>
+    <row r="105" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="99" t="s">
         <v>134</v>
       </c>
-      <c r="B96" s="99"/>
-      <c r="C96" s="99"/>
-      <c r="D96" s="191"/>
-      <c r="E96" s="118">
-        <f>D96*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F96" s="136">
-        <f>D96*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G96" s="109">
-        <f>E96+F96</f>
-        <v>0</v>
-      </c>
-      <c r="H96" s="150" t="str">
-        <f>IF(D96=G96, "", "Error")</f>
+      <c r="B105" s="99"/>
+      <c r="C105" s="99"/>
+      <c r="D105" s="191"/>
+      <c r="E105" s="118">
+        <f>D105*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F105" s="136">
+        <f>D105*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="G105" s="109">
+        <f>E105+F105</f>
+        <v>0</v>
+      </c>
+      <c r="H105" s="150" t="str">
+        <f>IF(D105=G105, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="1"/>
-      <c r="D97" s="188"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="10"/>
-      <c r="G97" s="157">
-        <f>SUM(G27:G96)</f>
-        <v>8586911.8399999999</v>
-      </c>
-      <c r="H97" s="150"/>
-    </row>
-    <row r="98" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="4" t="s">
+    <row r="106" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="1"/>
+      <c r="D106" s="188"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="10"/>
+      <c r="G106" s="157">
+        <f>SUM(G27:G105)</f>
+        <v>8796045.7599999998</v>
+      </c>
+      <c r="H106" s="150"/>
+    </row>
+    <row r="107" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B98" s="60"/>
-      <c r="C98" s="5"/>
-      <c r="D98" s="192">
-        <f>SUM(D96+D94+D90+D83+D76+D55+D35+D30+D48)</f>
-        <v>5277698.88</v>
-      </c>
-      <c r="E98" s="148">
-        <f>SUM(E96+E94+E90+E83+E76+E55+E35+E30+E48)</f>
-        <v>4946534.4161080001</v>
-      </c>
-      <c r="F98" s="148">
-        <f>SUM(F96+F94+F90+F83+F76+F55+F35+F30+F48)</f>
-        <v>331164.46389200003</v>
-      </c>
-      <c r="G98" s="109">
-        <f>E98+F98</f>
-        <v>5277698.88</v>
-      </c>
-      <c r="H98" s="150" t="str">
-        <f>IF(D98=G98, "", "Error")</f>
+      <c r="B107" s="60"/>
+      <c r="C107" s="5"/>
+      <c r="D107" s="192">
+        <f>SUM(D105+D103+D99+D92+D85+D55+D35+D30+D48)</f>
+        <v>5848392.3399999999</v>
+      </c>
+      <c r="E107" s="148">
+        <f>SUM(E105+E103+E99+E92+E85+E55+E35+E30+E48)</f>
+        <v>5317471.9837839995</v>
+      </c>
+      <c r="F107" s="148">
+        <f>SUM(F105+F103+F99+F92+F85+F55+F35+F30+F48)</f>
+        <v>333498.29621600005</v>
+      </c>
+      <c r="G107" s="109">
+        <f>E107+F107</f>
+        <v>5650970.2799999993</v>
+      </c>
+      <c r="H107" s="150" t="str">
+        <f>IF(D107=G107, "", "Error")</f>
+        <v>Error</v>
+      </c>
+      <c r="I107" s="181">
+        <f>D107-G107</f>
+        <v>197422.06000000052</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D108" s="188"/>
+      <c r="E108" s="109"/>
+    </row>
+    <row r="109" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="142" t="s">
+        <v>121</v>
+      </c>
+      <c r="B109" s="141"/>
+      <c r="C109" s="141"/>
+      <c r="E109" s="109"/>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A110" s="1"/>
+      <c r="C110" s="139"/>
+      <c r="E110" s="109"/>
+    </row>
+    <row r="111" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="1"/>
+      <c r="C111" s="139"/>
+      <c r="E111" s="109"/>
+    </row>
+    <row r="112" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="143" t="s">
+        <v>30</v>
+      </c>
+      <c r="B112" s="144"/>
+      <c r="C112" s="140">
+        <f>SUM(C110:C111)</f>
+        <v>0</v>
+      </c>
+      <c r="E112" s="109"/>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E113" s="109"/>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E114" s="137"/>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A115" s="225" t="s">
+        <v>114</v>
+      </c>
+      <c r="B115" s="226"/>
+      <c r="C115" s="226"/>
+      <c r="D115" s="226"/>
+      <c r="E115" s="172" t="s">
+        <v>22</v>
+      </c>
+      <c r="F115" s="173" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="222"/>
+      <c r="B116" s="223"/>
+      <c r="C116" s="224"/>
+      <c r="D116" s="167"/>
+      <c r="E116" s="149"/>
+      <c r="F116" s="134"/>
+    </row>
+    <row r="117" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="219"/>
+      <c r="B117" s="220"/>
+      <c r="C117" s="221"/>
+      <c r="D117" s="182"/>
+      <c r="E117" s="149"/>
+      <c r="F117" s="134"/>
+    </row>
+    <row r="118" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="174"/>
+      <c r="B118" s="175"/>
+      <c r="C118" s="176"/>
+      <c r="D118" s="182"/>
+      <c r="E118" s="149"/>
+      <c r="F118" s="134"/>
+    </row>
+    <row r="119" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="219"/>
+      <c r="B119" s="220"/>
+      <c r="C119" s="221"/>
+      <c r="D119" s="113"/>
+      <c r="E119" s="149">
+        <f>D119*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F119" s="134">
+        <f>D119*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A120" s="213" t="s">
+        <v>30</v>
+      </c>
+      <c r="B120" s="214"/>
+      <c r="C120" s="215"/>
+      <c r="D120" s="171">
+        <f>SUM(D116:D119)</f>
+        <v>0</v>
+      </c>
+      <c r="E120" s="171">
+        <f>SUM(E116:E119)</f>
+        <v>0</v>
+      </c>
+      <c r="F120" s="171">
+        <f>SUM(F116:F119)</f>
+        <v>0</v>
+      </c>
+      <c r="H120" s="109">
+        <f>E120+F120</f>
+        <v>0</v>
+      </c>
+      <c r="I120" s="150" t="str">
+        <f>IF(D120=H120, "", "Error")</f>
         <v/>
       </c>
-      <c r="I98" s="181">
-        <f>D98-G98</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D99" s="188"/>
-      <c r="E99" s="109"/>
-    </row>
-    <row r="100" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="142" t="s">
-        <v>121</v>
-      </c>
-      <c r="B100" s="141"/>
-      <c r="C100" s="141"/>
-      <c r="E100" s="109"/>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A101" s="1"/>
-      <c r="C101" s="139"/>
-      <c r="E101" s="109"/>
-    </row>
-    <row r="102" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="1"/>
-      <c r="C102" s="139"/>
-      <c r="E102" s="109"/>
-    </row>
-    <row r="103" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="143" t="s">
-        <v>30</v>
-      </c>
-      <c r="B103" s="144"/>
-      <c r="C103" s="140">
-        <f>SUM(C101:C102)</f>
-        <v>0</v>
-      </c>
-      <c r="E103" s="109"/>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E104" s="109"/>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E105" s="137"/>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A106" s="224" t="s">
-        <v>114</v>
-      </c>
-      <c r="B106" s="225"/>
-      <c r="C106" s="225"/>
-      <c r="D106" s="225"/>
-      <c r="E106" s="172" t="s">
-        <v>22</v>
-      </c>
-      <c r="F106" s="173" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="221"/>
-      <c r="B107" s="222"/>
-      <c r="C107" s="223"/>
-      <c r="D107" s="167"/>
-      <c r="E107" s="149"/>
-      <c r="F107" s="134"/>
-    </row>
-    <row r="108" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="218"/>
-      <c r="B108" s="219"/>
-      <c r="C108" s="220"/>
-      <c r="D108" s="182"/>
-      <c r="E108" s="149"/>
-      <c r="F108" s="134"/>
-    </row>
-    <row r="109" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="174"/>
-      <c r="B109" s="175"/>
-      <c r="C109" s="176"/>
-      <c r="D109" s="182"/>
-      <c r="E109" s="149"/>
-      <c r="F109" s="134"/>
-    </row>
-    <row r="110" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="218"/>
-      <c r="B110" s="219"/>
-      <c r="C110" s="220"/>
-      <c r="D110" s="113"/>
-      <c r="E110" s="149">
-        <f>D110*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F110" s="134">
-        <f>D110*8.09%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A111" s="212" t="s">
-        <v>30</v>
-      </c>
-      <c r="B111" s="213"/>
-      <c r="C111" s="214"/>
-      <c r="D111" s="171">
-        <f>SUM(D107:D110)</f>
-        <v>0</v>
-      </c>
-      <c r="E111" s="171">
-        <f>SUM(E107:E110)</f>
-        <v>0</v>
-      </c>
-      <c r="F111" s="171">
-        <f>SUM(F107:F110)</f>
-        <v>0</v>
-      </c>
-      <c r="H111" s="109">
-        <f>E111+F111</f>
-        <v>0</v>
-      </c>
-      <c r="I111" s="150" t="str">
-        <f>IF(D111=H111, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E113" s="109"/>
-    </row>
-    <row r="114" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="102" t="s">
+    </row>
+    <row r="122" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E122" s="109"/>
+    </row>
+    <row r="123" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="102" t="s">
         <v>105</v>
       </c>
-      <c r="B114" s="103">
-        <f>D98</f>
-        <v>5277698.88</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="104" t="s">
+      <c r="B123" s="103">
+        <f>D107</f>
+        <v>5848392.3399999999</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="104" t="s">
         <v>107</v>
       </c>
-      <c r="B115" s="105">
-        <f>D98-D96</f>
-        <v>5277698.88</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D116" s="202"/>
-      <c r="E116" s="202"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A117" s="74" t="s">
+      <c r="B124" s="105">
+        <f>D107-D105</f>
+        <v>5848392.3399999999</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D125" s="233"/>
+      <c r="E125" s="233"/>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A126" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="B117" s="75"/>
-      <c r="C117" s="76"/>
-      <c r="D117" s="202"/>
-      <c r="E117" s="202"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A118" s="77" t="s">
+      <c r="B126" s="75"/>
+      <c r="C126" s="76"/>
+      <c r="D126" s="233"/>
+      <c r="E126" s="233"/>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A127" s="77" t="s">
         <v>92</v>
       </c>
-      <c r="B118" s="78">
+      <c r="B127" s="78">
         <v>4452323.820828055</v>
       </c>
-      <c r="C118" s="78"/>
-      <c r="D118" s="202"/>
-      <c r="E118" s="202"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" s="79" t="s">
+      <c r="C127" s="78"/>
+      <c r="D127" s="233"/>
+      <c r="E127" s="233"/>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A128" s="79" t="s">
         <v>93</v>
       </c>
-      <c r="B119" s="92">
+      <c r="B128" s="92">
         <f>PRORRATEO!G52</f>
         <v>6849105.1357215978</v>
       </c>
-      <c r="C119" s="78" t="s">
+      <c r="C128" s="78" t="s">
         <v>94</v>
       </c>
-      <c r="D119" s="202"/>
-      <c r="E119" s="202"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" s="79" t="s">
+      <c r="D128" s="233"/>
+      <c r="E128" s="233"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" s="79" t="s">
         <v>116</v>
       </c>
-      <c r="B120" s="178">
-        <f>-B115</f>
-        <v>-5277698.88</v>
-      </c>
-      <c r="C120" s="76"/>
-      <c r="D120" s="202"/>
-      <c r="E120" s="202"/>
-      <c r="G120" s="113"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" s="79" t="s">
+      <c r="B129" s="178">
+        <f>-B124</f>
+        <v>-5848392.3399999999</v>
+      </c>
+      <c r="C129" s="76"/>
+      <c r="D129" s="233"/>
+      <c r="E129" s="233"/>
+      <c r="G129" s="113"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" s="79" t="s">
         <v>115</v>
       </c>
-      <c r="B121" s="178">
-        <f>-D111</f>
-        <v>0</v>
-      </c>
-      <c r="C121" s="76"/>
-      <c r="D121" s="202"/>
-      <c r="E121" s="202"/>
-      <c r="G121" s="125"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" s="79" t="s">
+      <c r="B130" s="178">
+        <f>-D120</f>
+        <v>0</v>
+      </c>
+      <c r="C130" s="76"/>
+      <c r="D130" s="233"/>
+      <c r="E130" s="233"/>
+      <c r="G130" s="125"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="B122" s="178">
-        <f>-B129</f>
-        <v>0</v>
-      </c>
-      <c r="C122" s="80"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A123" s="79" t="s">
+      <c r="B131" s="178">
+        <f>-B138</f>
+        <v>0</v>
+      </c>
+      <c r="C131" s="80"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A132" s="79" t="s">
         <v>121</v>
       </c>
-      <c r="B123" s="93">
-        <f>-C103</f>
-        <v>0</v>
-      </c>
-      <c r="C123" s="80"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" s="79"/>
-      <c r="B124" s="75"/>
-      <c r="C124" s="80"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" s="77" t="s">
+      <c r="B132" s="93">
+        <f>-C112</f>
+        <v>0</v>
+      </c>
+      <c r="C132" s="80"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" s="79"/>
+      <c r="B133" s="75"/>
+      <c r="C133" s="80"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B125" s="81">
-        <f>SUM(B118:B124)</f>
-        <v>6023730.076549652</v>
-      </c>
-      <c r="C125" s="154"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" s="80"/>
-      <c r="C126" s="76"/>
-      <c r="D126" s="83"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C127" s="76"/>
-      <c r="D127" s="109"/>
-      <c r="E127" s="181"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" s="74" t="s">
+      <c r="B134" s="81">
+        <f>SUM(B127:B133)</f>
+        <v>5453036.6165496521</v>
+      </c>
+      <c r="C134" s="154"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" s="80"/>
+      <c r="C135" s="76"/>
+      <c r="D135" s="83"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C136" s="76"/>
+      <c r="D136" s="109"/>
+      <c r="E136" s="181"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="B128" s="11">
+      <c r="B137" s="11">
         <v>-310694.54000000004</v>
       </c>
-      <c r="C128" s="82"/>
-    </row>
-    <row r="129" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="77" t="s">
-        <v>164</v>
-      </c>
-      <c r="B129" s="93"/>
-      <c r="C129" s="82"/>
-      <c r="D129" s="181"/>
-      <c r="E129" s="109"/>
-    </row>
-    <row r="130" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="77"/>
-      <c r="B130" s="178"/>
-      <c r="C130" s="82"/>
-      <c r="E130" s="109"/>
-    </row>
-    <row r="131" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="77"/>
-      <c r="B131" s="178"/>
-      <c r="C131" s="82"/>
-      <c r="E131" s="109"/>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A132" s="77"/>
-      <c r="B132" s="178"/>
-      <c r="C132" s="82"/>
-      <c r="E132" s="109"/>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A133" s="100" t="s">
+      <c r="C137" s="82"/>
+    </row>
+    <row r="138" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="77" t="s">
+        <v>156</v>
+      </c>
+      <c r="B138" s="93"/>
+      <c r="C138" s="82"/>
+      <c r="D138" s="181"/>
+      <c r="E138" s="109"/>
+    </row>
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="77"/>
+      <c r="B139" s="178"/>
+      <c r="C139" s="82"/>
+      <c r="E139" s="109"/>
+    </row>
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="77"/>
+      <c r="B140" s="178"/>
+      <c r="C140" s="82"/>
+      <c r="E140" s="109"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141" s="77"/>
+      <c r="B141" s="178"/>
+      <c r="C141" s="82"/>
+      <c r="E141" s="109"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A142" s="100" t="s">
         <v>30</v>
       </c>
-      <c r="B133" s="101">
-        <f>SUM(B128:B132)</f>
+      <c r="B142" s="101">
+        <f>SUM(B137:B141)</f>
         <v>-310694.54000000004</v>
       </c>
-      <c r="C133" s="82"/>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C134" s="83"/>
-      <c r="D134" s="181"/>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B135" s="80"/>
-      <c r="C135" s="76"/>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N137" s="12"/>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B140" s="201" t="s">
-        <v>163</v>
-      </c>
-      <c r="C140" s="201"/>
-      <c r="D140" s="201"/>
-      <c r="E140" s="201"/>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B141" s="201"/>
-      <c r="C141" s="201"/>
-      <c r="D141" s="201"/>
-      <c r="E141" s="201"/>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B142" s="201"/>
-      <c r="C142" s="201"/>
-      <c r="D142" s="201"/>
-      <c r="E142" s="201"/>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B143" s="201"/>
-      <c r="C143" s="201"/>
-      <c r="D143" s="201"/>
-      <c r="E143" s="201"/>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B144" s="201"/>
-      <c r="C144" s="201"/>
-      <c r="D144" s="201"/>
-      <c r="E144" s="201"/>
+      <c r="C142" s="82"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C143" s="83"/>
+      <c r="D143" s="181"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B144" s="80"/>
+      <c r="C144" s="76"/>
+    </row>
+    <row r="146" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="N146" s="12"/>
+    </row>
+    <row r="149" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B149" s="232" t="s">
+        <v>155</v>
+      </c>
+      <c r="C149" s="232"/>
+      <c r="D149" s="232"/>
+      <c r="E149" s="232"/>
+    </row>
+    <row r="150" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B150" s="232"/>
+      <c r="C150" s="232"/>
+      <c r="D150" s="232"/>
+      <c r="E150" s="232"/>
+    </row>
+    <row r="151" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B151" s="232"/>
+      <c r="C151" s="232"/>
+      <c r="D151" s="232"/>
+      <c r="E151" s="232"/>
+    </row>
+    <row r="152" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B152" s="232"/>
+      <c r="C152" s="232"/>
+      <c r="D152" s="232"/>
+      <c r="E152" s="232"/>
+    </row>
+    <row r="153" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B153" s="232"/>
+      <c r="C153" s="232"/>
+      <c r="D153" s="232"/>
+      <c r="E153" s="232"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B140:E144"/>
-    <mergeCell ref="D116:E121"/>
+  <mergeCells count="17">
+    <mergeCell ref="B149:E153"/>
+    <mergeCell ref="D125:E130"/>
     <mergeCell ref="B14:D17"/>
-    <mergeCell ref="A111:C111"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="A108:C108"/>
-    <mergeCell ref="A110:C110"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A106:D106"/>
+    <mergeCell ref="A120:C120"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A117:C117"/>
+    <mergeCell ref="A119:C119"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="A77:C77"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A74:C74"/>
     <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A75:C75"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3996,15 +4176,15 @@
       <c r="K1" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="L1" s="228">
-        <f>RESUMEN!D98</f>
-        <v>5277698.88</v>
-      </c>
-      <c r="M1" s="229"/>
+      <c r="L1" s="240">
+        <f>RESUMEN!D107</f>
+        <v>5848392.3399999999</v>
+      </c>
+      <c r="M1" s="241"/>
       <c r="N1" s="152"/>
       <c r="O1" s="135">
         <f>L1*8.09%</f>
-        <v>426965.83939199999</v>
+        <v>473134.940306</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -4029,7 +4209,7 @@
       <c r="N2" s="153"/>
       <c r="O2" s="135">
         <f>O1-K7-553-50-86-8</f>
-        <v>95338.539740999986</v>
+        <v>141507.640655</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -4076,64 +4256,64 @@
       <c r="N4" s="124"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="226" t="s">
+      <c r="A5" s="234" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="239" t="s">
+      <c r="B5" s="236" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="226" t="s">
+      <c r="C5" s="234" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="237" t="s">
+      <c r="D5" s="238" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="226" t="s">
+      <c r="E5" s="234" t="s">
         <v>98</v>
       </c>
-      <c r="F5" s="226" t="s">
+      <c r="F5" s="234" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="226" t="s">
+      <c r="G5" s="234" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="232" t="s">
+      <c r="H5" s="244" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="237" t="s">
+      <c r="I5" s="238" t="s">
         <v>109</v>
       </c>
-      <c r="J5" s="230" t="s">
+      <c r="J5" s="242" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="230" t="s">
+      <c r="K5" s="242" t="s">
         <v>70</v>
       </c>
-      <c r="L5" s="235" t="s">
+      <c r="L5" s="247" t="s">
         <v>124</v>
       </c>
-      <c r="M5" s="230" t="s">
+      <c r="M5" s="242" t="s">
         <v>68</v>
       </c>
-      <c r="N5" s="230" t="s">
+      <c r="N5" s="242" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="227"/>
-      <c r="B6" s="240"/>
-      <c r="C6" s="227"/>
-      <c r="D6" s="241"/>
-      <c r="E6" s="227"/>
-      <c r="F6" s="227"/>
-      <c r="G6" s="227"/>
-      <c r="H6" s="233"/>
-      <c r="I6" s="238"/>
-      <c r="J6" s="231"/>
-      <c r="K6" s="234"/>
-      <c r="L6" s="236"/>
-      <c r="M6" s="234"/>
-      <c r="N6" s="231"/>
+      <c r="A6" s="235"/>
+      <c r="B6" s="237"/>
+      <c r="C6" s="235"/>
+      <c r="D6" s="239"/>
+      <c r="E6" s="235"/>
+      <c r="F6" s="235"/>
+      <c r="G6" s="235"/>
+      <c r="H6" s="245"/>
+      <c r="I6" s="249"/>
+      <c r="J6" s="243"/>
+      <c r="K6" s="246"/>
+      <c r="L6" s="248"/>
+      <c r="M6" s="246"/>
+      <c r="N6" s="243"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
@@ -4579,7 +4759,7 @@
         <v>32</v>
       </c>
       <c r="D16" s="133" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E16" s="7">
         <v>2.84</v>
@@ -5911,7 +6091,7 @@
       </c>
       <c r="P43" s="109">
         <f>L1-K52</f>
-        <v>32595.47104900144</v>
+        <v>603288.9310490014</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
@@ -6340,36 +6520,36 @@
     <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="K53" s="138">
         <f>K52-L1</f>
-        <v>-32595.47104900144</v>
+        <v>-603288.9310490014</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="202"/>
-      <c r="D54" s="202"/>
-      <c r="E54" s="202"/>
-      <c r="F54" s="202"/>
-      <c r="G54" s="202"/>
-      <c r="H54" s="202"/>
-      <c r="I54" s="202"/>
-      <c r="J54" s="202"/>
-      <c r="K54" s="202"/>
-      <c r="L54" s="202"/>
-      <c r="M54" s="202"/>
-      <c r="N54" s="202"/>
+      <c r="C54" s="233"/>
+      <c r="D54" s="233"/>
+      <c r="E54" s="233"/>
+      <c r="F54" s="233"/>
+      <c r="G54" s="233"/>
+      <c r="H54" s="233"/>
+      <c r="I54" s="233"/>
+      <c r="J54" s="233"/>
+      <c r="K54" s="233"/>
+      <c r="L54" s="233"/>
+      <c r="M54" s="233"/>
+      <c r="N54" s="233"/>
     </row>
     <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="202"/>
-      <c r="D55" s="202"/>
-      <c r="E55" s="202"/>
-      <c r="F55" s="202"/>
-      <c r="G55" s="202"/>
-      <c r="H55" s="202"/>
-      <c r="I55" s="202"/>
-      <c r="J55" s="202"/>
-      <c r="K55" s="202"/>
-      <c r="L55" s="202"/>
-      <c r="M55" s="202"/>
-      <c r="N55" s="202"/>
+      <c r="C55" s="233"/>
+      <c r="D55" s="233"/>
+      <c r="E55" s="233"/>
+      <c r="F55" s="233"/>
+      <c r="G55" s="233"/>
+      <c r="H55" s="233"/>
+      <c r="I55" s="233"/>
+      <c r="J55" s="233"/>
+      <c r="K55" s="233"/>
+      <c r="L55" s="233"/>
+      <c r="M55" s="233"/>
+      <c r="N55" s="233"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C56" s="169"/>
@@ -6386,112 +6566,107 @@
       <c r="N56" s="169"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C57" s="202" t="s">
+      <c r="C57" s="233" t="s">
         <v>130</v>
       </c>
-      <c r="D57" s="202"/>
-      <c r="E57" s="202"/>
-      <c r="F57" s="202"/>
-      <c r="G57" s="202"/>
-      <c r="H57" s="202"/>
-      <c r="I57" s="202"/>
-      <c r="J57" s="202"/>
-      <c r="K57" s="202"/>
-      <c r="L57" s="202"/>
-      <c r="M57" s="202"/>
-      <c r="N57" s="202"/>
+      <c r="D57" s="233"/>
+      <c r="E57" s="233"/>
+      <c r="F57" s="233"/>
+      <c r="G57" s="233"/>
+      <c r="H57" s="233"/>
+      <c r="I57" s="233"/>
+      <c r="J57" s="233"/>
+      <c r="K57" s="233"/>
+      <c r="L57" s="233"/>
+      <c r="M57" s="233"/>
+      <c r="N57" s="233"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C58" s="202"/>
-      <c r="D58" s="202"/>
-      <c r="E58" s="202"/>
-      <c r="F58" s="202"/>
-      <c r="G58" s="202"/>
-      <c r="H58" s="202"/>
-      <c r="I58" s="202"/>
-      <c r="J58" s="202"/>
-      <c r="K58" s="202"/>
-      <c r="L58" s="202"/>
-      <c r="M58" s="202"/>
-      <c r="N58" s="202"/>
+      <c r="C58" s="233"/>
+      <c r="D58" s="233"/>
+      <c r="E58" s="233"/>
+      <c r="F58" s="233"/>
+      <c r="G58" s="233"/>
+      <c r="H58" s="233"/>
+      <c r="I58" s="233"/>
+      <c r="J58" s="233"/>
+      <c r="K58" s="233"/>
+      <c r="L58" s="233"/>
+      <c r="M58" s="233"/>
+      <c r="N58" s="233"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C59" s="202"/>
-      <c r="D59" s="202"/>
-      <c r="E59" s="202"/>
-      <c r="F59" s="202"/>
-      <c r="G59" s="202"/>
-      <c r="H59" s="202"/>
-      <c r="I59" s="202"/>
-      <c r="J59" s="202"/>
-      <c r="K59" s="202"/>
-      <c r="L59" s="202"/>
-      <c r="M59" s="202"/>
-      <c r="N59" s="202"/>
+      <c r="C59" s="233"/>
+      <c r="D59" s="233"/>
+      <c r="E59" s="233"/>
+      <c r="F59" s="233"/>
+      <c r="G59" s="233"/>
+      <c r="H59" s="233"/>
+      <c r="I59" s="233"/>
+      <c r="J59" s="233"/>
+      <c r="K59" s="233"/>
+      <c r="L59" s="233"/>
+      <c r="M59" s="233"/>
+      <c r="N59" s="233"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C60" s="202"/>
-      <c r="D60" s="202"/>
-      <c r="E60" s="202"/>
-      <c r="F60" s="202"/>
-      <c r="G60" s="202"/>
-      <c r="H60" s="202"/>
-      <c r="I60" s="202"/>
-      <c r="J60" s="202"/>
-      <c r="K60" s="202"/>
-      <c r="L60" s="202"/>
-      <c r="M60" s="202"/>
-      <c r="N60" s="202"/>
+      <c r="C60" s="233"/>
+      <c r="D60" s="233"/>
+      <c r="E60" s="233"/>
+      <c r="F60" s="233"/>
+      <c r="G60" s="233"/>
+      <c r="H60" s="233"/>
+      <c r="I60" s="233"/>
+      <c r="J60" s="233"/>
+      <c r="K60" s="233"/>
+      <c r="L60" s="233"/>
+      <c r="M60" s="233"/>
+      <c r="N60" s="233"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C61" s="202"/>
-      <c r="D61" s="202"/>
-      <c r="E61" s="202"/>
-      <c r="F61" s="202"/>
-      <c r="G61" s="202"/>
-      <c r="H61" s="202"/>
-      <c r="I61" s="202"/>
-      <c r="J61" s="202"/>
-      <c r="K61" s="202"/>
-      <c r="L61" s="202"/>
-      <c r="M61" s="202"/>
-      <c r="N61" s="202"/>
+      <c r="C61" s="233"/>
+      <c r="D61" s="233"/>
+      <c r="E61" s="233"/>
+      <c r="F61" s="233"/>
+      <c r="G61" s="233"/>
+      <c r="H61" s="233"/>
+      <c r="I61" s="233"/>
+      <c r="J61" s="233"/>
+      <c r="K61" s="233"/>
+      <c r="L61" s="233"/>
+      <c r="M61" s="233"/>
+      <c r="N61" s="233"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C62" s="202"/>
-      <c r="D62" s="202"/>
-      <c r="E62" s="202"/>
-      <c r="F62" s="202"/>
-      <c r="G62" s="202"/>
-      <c r="H62" s="202"/>
-      <c r="I62" s="202"/>
-      <c r="J62" s="202"/>
-      <c r="K62" s="202"/>
-      <c r="L62" s="202"/>
-      <c r="M62" s="202"/>
-      <c r="N62" s="202"/>
+      <c r="C62" s="233"/>
+      <c r="D62" s="233"/>
+      <c r="E62" s="233"/>
+      <c r="F62" s="233"/>
+      <c r="G62" s="233"/>
+      <c r="H62" s="233"/>
+      <c r="I62" s="233"/>
+      <c r="J62" s="233"/>
+      <c r="K62" s="233"/>
+      <c r="L62" s="233"/>
+      <c r="M62" s="233"/>
+      <c r="N62" s="233"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C63" s="202"/>
-      <c r="D63" s="202"/>
-      <c r="E63" s="202"/>
-      <c r="F63" s="202"/>
-      <c r="G63" s="202"/>
-      <c r="H63" s="202"/>
-      <c r="I63" s="202"/>
-      <c r="J63" s="202"/>
-      <c r="K63" s="202"/>
-      <c r="L63" s="202"/>
-      <c r="M63" s="202"/>
-      <c r="N63" s="202"/>
+      <c r="C63" s="233"/>
+      <c r="D63" s="233"/>
+      <c r="E63" s="233"/>
+      <c r="F63" s="233"/>
+      <c r="G63" s="233"/>
+      <c r="H63" s="233"/>
+      <c r="I63" s="233"/>
+      <c r="J63" s="233"/>
+      <c r="K63" s="233"/>
+      <c r="L63" s="233"/>
+      <c r="M63" s="233"/>
+      <c r="N63" s="233"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
@@ -6504,6 +6679,11 @@
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="I5:I6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -6610,10 +6790,10 @@
       <c r="O4" s="49"/>
     </row>
     <row r="5" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="242" t="s">
+      <c r="A5" s="250" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="242" t="s">
+      <c r="B5" s="250" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="55" t="s">
@@ -6625,7 +6805,7 @@
       <c r="E5" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="242" t="s">
+      <c r="F5" s="250" t="s">
         <v>76</v>
       </c>
       <c r="G5" s="37" t="s">
@@ -6647,16 +6827,16 @@
         <v>30</v>
       </c>
       <c r="M5" s="41"/>
-      <c r="N5" s="242" t="s">
+      <c r="N5" s="250" t="s">
         <v>79</v>
       </c>
-      <c r="O5" s="242" t="s">
+      <c r="O5" s="250" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="243"/>
-      <c r="B6" s="243"/>
+      <c r="A6" s="251"/>
+      <c r="B6" s="251"/>
       <c r="C6" s="56" t="s">
         <v>81</v>
       </c>
@@ -6666,7 +6846,7 @@
       <c r="E6" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="243"/>
+      <c r="F6" s="251"/>
       <c r="G6" s="44" t="s">
         <v>82</v>
       </c>
@@ -6686,8 +6866,8 @@
         <v>85</v>
       </c>
       <c r="M6" s="47"/>
-      <c r="N6" s="243"/>
-      <c r="O6" s="243"/>
+      <c r="N6" s="251"/>
+      <c r="O6" s="251"/>
     </row>
     <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15">

--- a/BELGRANO 1646/Mayo/MAYO-BLG1646.xlsx
+++ b/BELGRANO 1646/Mayo/MAYO-BLG1646.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BELGRANO 1646\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB448BAD-8ACD-49C0-B26B-10029C718689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759F3AA1-DCA6-4031-9B59-47DC16388C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$143</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$144</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="170">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -568,6 +568,9 @@
   </si>
   <si>
     <t xml:space="preserve">Camaras del sur 19/05 </t>
+  </si>
+  <si>
+    <t>Doartero Julio - Emergencia 26/05</t>
   </si>
 </sst>
 </file>
@@ -1594,6 +1597,12 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1678,58 +1687,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2103,7 +2106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N153"/>
+  <dimension ref="A1:N154"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.44140625" customWidth="1"/>
@@ -2191,26 +2194,26 @@
     <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="204" t="s">
+      <c r="B14" s="206" t="s">
         <v>135</v>
       </c>
-      <c r="C14" s="205"/>
-      <c r="D14" s="206"/>
+      <c r="C14" s="207"/>
+      <c r="D14" s="208"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="207"/>
-      <c r="C15" s="208"/>
-      <c r="D15" s="209"/>
+      <c r="B15" s="209"/>
+      <c r="C15" s="210"/>
+      <c r="D15" s="211"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="207"/>
-      <c r="C16" s="208"/>
-      <c r="D16" s="209"/>
+      <c r="B16" s="209"/>
+      <c r="C16" s="210"/>
+      <c r="D16" s="211"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="210"/>
-      <c r="C17" s="211"/>
-      <c r="D17" s="212"/>
+      <c r="B17" s="212"/>
+      <c r="C17" s="213"/>
+      <c r="D17" s="214"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
@@ -2826,15 +2829,15 @@
         <v>9603.5281670000004</v>
       </c>
       <c r="G60" s="109">
-        <f t="shared" ref="G60:G84" si="10">D60</f>
+        <f t="shared" ref="G60:G85" si="10">D60</f>
         <v>118708.63</v>
       </c>
       <c r="H60" s="161">
-        <f t="shared" ref="H60:H84" si="11">E60+F60</f>
+        <f t="shared" ref="H60:H85" si="11">E60+F60</f>
         <v>118708.62999999999</v>
       </c>
       <c r="I60" t="str">
-        <f t="shared" ref="I60:I83" si="12">IF(G60=H60, "", "Error")</f>
+        <f t="shared" ref="I60:I84" si="12">IF(G60=H60, "", "Error")</f>
         <v/>
       </c>
     </row>
@@ -3009,11 +3012,11 @@
       <c r="I66" s="181"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="216" t="s">
+      <c r="A67" s="218" t="s">
         <v>157</v>
       </c>
-      <c r="B67" s="217"/>
-      <c r="C67" s="218"/>
+      <c r="B67" s="219"/>
+      <c r="C67" s="220"/>
       <c r="D67" s="198">
         <v>111026</v>
       </c>
@@ -3032,11 +3035,11 @@
       </c>
     </row>
     <row r="68" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="216" t="s">
+      <c r="A68" s="218" t="s">
         <v>160</v>
       </c>
-      <c r="B68" s="217"/>
-      <c r="C68" s="218"/>
+      <c r="B68" s="219"/>
+      <c r="C68" s="220"/>
       <c r="D68" s="198">
         <f>104002.96</f>
         <v>104002.96</v>
@@ -3060,11 +3063,11 @@
       </c>
     </row>
     <row r="69" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="216" t="s">
+      <c r="A69" s="218" t="s">
         <v>160</v>
       </c>
-      <c r="B69" s="217"/>
-      <c r="C69" s="218"/>
+      <c r="B69" s="219"/>
+      <c r="C69" s="220"/>
       <c r="D69" s="198">
         <f>104002.96</f>
         <v>104002.96</v>
@@ -3078,11 +3081,11 @@
       <c r="H69" s="161"/>
     </row>
     <row r="70" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="216" t="s">
+      <c r="A70" s="218" t="s">
         <v>160</v>
       </c>
-      <c r="B70" s="217"/>
-      <c r="C70" s="218"/>
+      <c r="B70" s="219"/>
+      <c r="C70" s="220"/>
       <c r="D70" s="198">
         <f>104002.96</f>
         <v>104002.96</v>
@@ -3096,11 +3099,11 @@
       <c r="H70" s="161"/>
     </row>
     <row r="71" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="216" t="s">
+      <c r="A71" s="218" t="s">
         <v>160</v>
       </c>
-      <c r="B71" s="217"/>
-      <c r="C71" s="218"/>
+      <c r="B71" s="219"/>
+      <c r="C71" s="220"/>
       <c r="D71" s="198">
         <f>104002.96</f>
         <v>104002.96</v>
@@ -3142,11 +3145,11 @@
       <c r="H73" s="161"/>
     </row>
     <row r="74" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="227" t="s">
+      <c r="A74" s="229" t="s">
         <v>150</v>
       </c>
-      <c r="B74" s="228"/>
-      <c r="C74" s="229"/>
+      <c r="B74" s="230"/>
+      <c r="C74" s="231"/>
       <c r="D74" s="198">
         <v>6000</v>
       </c>
@@ -3165,11 +3168,11 @@
       </c>
     </row>
     <row r="75" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="227" t="s">
+      <c r="A75" s="229" t="s">
         <v>165</v>
       </c>
-      <c r="B75" s="228"/>
-      <c r="C75" s="229"/>
+      <c r="B75" s="230"/>
+      <c r="C75" s="231"/>
       <c r="D75" s="198">
         <v>7000</v>
       </c>
@@ -3203,11 +3206,11 @@
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A77" s="227" t="s">
+      <c r="A77" s="229" t="s">
         <v>147</v>
       </c>
-      <c r="B77" s="228"/>
-      <c r="C77" s="229"/>
+      <c r="B77" s="230"/>
+      <c r="C77" s="231"/>
       <c r="D77" s="198">
         <v>66000</v>
       </c>
@@ -3230,10 +3233,10 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="230" t="s">
+      <c r="A78" s="232" t="s">
         <v>164</v>
       </c>
-      <c r="B78" s="231"/>
+      <c r="B78" s="233"/>
       <c r="C78" s="194"/>
       <c r="D78" s="198">
         <v>218400</v>
@@ -3258,7 +3261,7 @@
         <v>79895</v>
       </c>
       <c r="E79" s="149">
-        <f t="shared" ref="E79:E84" si="14">D79</f>
+        <f t="shared" ref="E79:E85" si="14">D79</f>
         <v>79895</v>
       </c>
       <c r="F79" s="7"/>
@@ -3323,116 +3326,127 @@
     </row>
     <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
       <c r="D82" s="198">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="E82" s="149">
         <f t="shared" si="14"/>
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="F82" s="7"/>
       <c r="G82" s="109">
         <f t="shared" si="10"/>
+        <v>150000</v>
+      </c>
+      <c r="H82" s="161"/>
+    </row>
+    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B83" s="7"/>
+      <c r="C83" s="7"/>
+      <c r="D83" s="198">
         <v>120000</v>
-      </c>
-      <c r="H82" s="161"/>
-    </row>
-    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="98" t="s">
-        <v>159</v>
-      </c>
-      <c r="B83" s="114"/>
-      <c r="C83" s="163"/>
-      <c r="D83" s="198">
-        <v>80000</v>
       </c>
       <c r="E83" s="149">
         <f t="shared" si="14"/>
-        <v>80000</v>
-      </c>
-      <c r="F83" s="134"/>
+        <v>120000</v>
+      </c>
+      <c r="F83" s="7"/>
       <c r="G83" s="109">
         <f t="shared" si="10"/>
+        <v>120000</v>
+      </c>
+      <c r="H83" s="161"/>
+    </row>
+    <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="98" t="s">
+        <v>159</v>
+      </c>
+      <c r="B84" s="114"/>
+      <c r="C84" s="163"/>
+      <c r="D84" s="198">
         <v>80000</v>
       </c>
-      <c r="H83" s="161">
-        <f t="shared" si="11"/>
-        <v>80000</v>
-      </c>
-      <c r="I83" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A84" s="155"/>
-      <c r="B84" s="156"/>
-      <c r="C84" s="156"/>
-      <c r="D84" s="167"/>
       <c r="E84" s="149">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="F84" s="134"/>
       <c r="G84" s="109">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="H84" s="161">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="I84" t="str">
-        <f>IF(G84=H84, "", "Error")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A85" s="96" t="s">
+      <c r="A85" s="155"/>
+      <c r="B85" s="156"/>
+      <c r="C85" s="156"/>
+      <c r="D85" s="167"/>
+      <c r="E85" s="149">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="F85" s="134"/>
+      <c r="G85" s="109">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H85" s="161">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I85" t="str">
+        <f>IF(G85=H85, "", "Error")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="B85" s="96"/>
-      <c r="C85" s="96"/>
-      <c r="D85" s="108">
-        <f>SUM(D60:D84)</f>
-        <v>3549906.42</v>
-      </c>
-      <c r="E85" s="108">
-        <f>SUM(E60:E84)</f>
-        <v>3198461.5747119999</v>
-      </c>
-      <c r="F85" s="108">
-        <f>SUM(F60:F84)</f>
+      <c r="B86" s="96"/>
+      <c r="C86" s="96"/>
+      <c r="D86" s="108">
+        <f>SUM(D60:D85)</f>
+        <v>3699906.42</v>
+      </c>
+      <c r="E86" s="108">
+        <f>SUM(E60:E85)</f>
+        <v>3348461.5747119999</v>
+      </c>
+      <c r="F86" s="108">
+        <f>SUM(F60:F85)</f>
         <v>154022.78528800001</v>
       </c>
-      <c r="G85" s="109">
-        <f>E85+F85</f>
-        <v>3352484.36</v>
-      </c>
-      <c r="H85" s="150" t="str">
-        <f>IF(D85=G85, "", "Error")</f>
+      <c r="G86" s="109">
+        <f>E86+F86</f>
+        <v>3502484.36</v>
+      </c>
+      <c r="H86" s="150" t="str">
+        <f>IF(D86=G86, "", "Error")</f>
         <v>Error</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="7"/>
-      <c r="B86" s="7"/>
-      <c r="C86" s="7"/>
-      <c r="D86" s="189"/>
-      <c r="E86" s="115"/>
-      <c r="F86" s="7"/>
-      <c r="H86" s="150"/>
     </row>
     <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
       <c r="D87" s="189"/>
-      <c r="E87" s="114"/>
+      <c r="E87" s="115"/>
       <c r="F87" s="7"/>
       <c r="H87" s="150"/>
     </row>
@@ -3445,101 +3459,99 @@
       <c r="F88" s="7"/>
       <c r="H88" s="150"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A89" s="94" t="s">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="7"/>
+      <c r="B89" s="7"/>
+      <c r="C89" s="7"/>
+      <c r="D89" s="189"/>
+      <c r="E89" s="114"/>
+      <c r="F89" s="7"/>
+      <c r="H89" s="150"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A90" s="94" t="s">
         <v>146</v>
       </c>
-      <c r="B89" s="98"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="113">
+      <c r="B90" s="98"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="113">
         <v>186900</v>
       </c>
-      <c r="E89" s="149">
-        <f>D89*91.91%</f>
+      <c r="E90" s="149">
+        <f>D90*91.91%</f>
         <v>171779.78999999998</v>
       </c>
-      <c r="F89" s="134">
-        <f>D89*8.09%</f>
+      <c r="F90" s="134">
+        <f>D90*8.09%</f>
         <v>15120.21</v>
       </c>
-      <c r="G89" s="160"/>
-      <c r="H89" s="150"/>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A90" s="98"/>
-      <c r="B90" s="162"/>
-      <c r="C90" s="7"/>
-      <c r="D90" s="113"/>
-      <c r="E90" s="149">
-        <f>D90</f>
-        <v>0</v>
-      </c>
-      <c r="F90" s="134"/>
+      <c r="G90" s="160"/>
       <c r="H90" s="150"/>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A91" s="7"/>
-      <c r="B91" s="7"/>
+      <c r="A91" s="98"/>
+      <c r="B91" s="162"/>
       <c r="C91" s="7"/>
       <c r="D91" s="113"/>
-      <c r="E91" s="165">
+      <c r="E91" s="149">
         <f>D91</f>
         <v>0</v>
       </c>
-      <c r="F91" s="7"/>
+      <c r="F91" s="134"/>
       <c r="H91" s="150"/>
-      <c r="I91" s="109"/>
-    </row>
-    <row r="92" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="95" t="s">
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A92" s="7"/>
+      <c r="B92" s="7"/>
+      <c r="C92" s="7"/>
+      <c r="D92" s="113"/>
+      <c r="E92" s="165">
+        <f>D92</f>
+        <v>0</v>
+      </c>
+      <c r="F92" s="7"/>
+      <c r="H92" s="150"/>
+      <c r="I92" s="109"/>
+    </row>
+    <row r="93" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="B92" s="95"/>
-      <c r="C92" s="95"/>
-      <c r="D92" s="107">
-        <f>SUM(D89:D91)</f>
+      <c r="B93" s="95"/>
+      <c r="C93" s="95"/>
+      <c r="D93" s="107">
+        <f>SUM(D90:D92)</f>
         <v>186900</v>
       </c>
-      <c r="E92" s="107">
-        <f>SUM(E89:E91)</f>
+      <c r="E93" s="107">
+        <f>SUM(E90:E92)</f>
         <v>171779.78999999998</v>
       </c>
-      <c r="F92" s="107">
-        <f>SUM(F89:F91)</f>
+      <c r="F93" s="107">
+        <f>SUM(F90:F92)</f>
         <v>15120.21</v>
       </c>
-      <c r="G92" s="109">
-        <f>E92+F92</f>
+      <c r="G93" s="109">
+        <f>E93+F93</f>
         <v>186899.99999999997</v>
       </c>
-      <c r="H92" s="150" t="str">
-        <f>IF(D92=G92, "", "Error")</f>
+      <c r="H93" s="150" t="str">
+        <f>IF(D93=G93, "", "Error")</f>
         <v/>
       </c>
-      <c r="J92" s="109"/>
-    </row>
-    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="7"/>
-      <c r="B93" s="7"/>
-      <c r="C93" s="7"/>
-      <c r="D93" s="189"/>
-      <c r="E93" s="115"/>
-      <c r="F93" s="7"/>
-      <c r="H93" s="150"/>
+      <c r="J93" s="109"/>
     </row>
     <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
       <c r="D94" s="189"/>
-      <c r="E94" s="114"/>
+      <c r="E94" s="115"/>
       <c r="F94" s="7"/>
       <c r="H94" s="150"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A95" s="94" t="s">
-        <v>13</v>
-      </c>
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="7"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
       <c r="D95" s="189"/>
@@ -3547,504 +3559,509 @@
       <c r="F95" s="7"/>
       <c r="H95" s="150"/>
     </row>
-    <row r="96" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="94" t="s">
+        <v>13</v>
+      </c>
+      <c r="B96" s="7"/>
+      <c r="C96" s="7"/>
+      <c r="D96" s="189"/>
+      <c r="E96" s="114"/>
+      <c r="F96" s="7"/>
+      <c r="H96" s="150"/>
+    </row>
+    <row r="97" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="B96" s="7" t="s">
+      <c r="B97" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C96" s="7"/>
-      <c r="D96" s="198">
-        <v>222264.92</v>
-      </c>
-      <c r="E96" s="149">
-        <f>D96*91.91%</f>
-        <v>204283.68797199999</v>
-      </c>
-      <c r="F96" s="134">
-        <f>D96*8.09%</f>
-        <v>17981.232028000002</v>
-      </c>
-      <c r="H96" s="150"/>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A97" s="94" t="s">
-        <v>108</v>
-      </c>
-      <c r="B97" s="7"/>
       <c r="C97" s="7"/>
       <c r="D97" s="198">
-        <v>28000</v>
+        <v>222264.92</v>
       </c>
       <c r="E97" s="149">
         <f>D97*91.91%</f>
-        <v>25734.799999999999</v>
+        <v>204283.68797199999</v>
       </c>
       <c r="F97" s="134">
         <f>D97*8.09%</f>
-        <v>2265.1999999999998</v>
+        <v>17981.232028000002</v>
       </c>
       <c r="H97" s="150"/>
-      <c r="J97" s="113"/>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A98" s="7"/>
+      <c r="A98" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
-      <c r="D98" s="189"/>
-      <c r="E98" s="116"/>
-      <c r="F98" s="7"/>
+      <c r="D98" s="198">
+        <v>28000</v>
+      </c>
+      <c r="E98" s="149">
+        <f>D98*91.91%</f>
+        <v>25734.799999999999</v>
+      </c>
+      <c r="F98" s="134">
+        <f>D98*8.09%</f>
+        <v>2265.1999999999998</v>
+      </c>
       <c r="H98" s="150"/>
-      <c r="J98" s="109"/>
+      <c r="J98" s="113"/>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A99" s="95" t="s">
+      <c r="A99" s="7"/>
+      <c r="B99" s="7"/>
+      <c r="C99" s="7"/>
+      <c r="D99" s="189"/>
+      <c r="E99" s="116"/>
+      <c r="F99" s="7"/>
+      <c r="H99" s="150"/>
+      <c r="J99" s="109"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A100" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="B99" s="95"/>
-      <c r="C99" s="95"/>
-      <c r="D99" s="107">
-        <f>SUM(D96:D98)</f>
+      <c r="B100" s="95"/>
+      <c r="C100" s="95"/>
+      <c r="D100" s="107">
+        <f>SUM(D97:D99)</f>
         <v>250264.92</v>
       </c>
-      <c r="E99" s="107">
-        <f>SUM(E96:E98)</f>
+      <c r="E100" s="107">
+        <f>SUM(E97:E99)</f>
         <v>230018.48797199997</v>
       </c>
-      <c r="F99" s="107">
-        <f>SUM(F96:F98)</f>
+      <c r="F100" s="107">
+        <f>SUM(F97:F99)</f>
         <v>20246.432028000003</v>
       </c>
-      <c r="G99" s="109">
-        <f>E99+F99</f>
+      <c r="G100" s="109">
+        <f>E100+F100</f>
         <v>250264.91999999998</v>
       </c>
-      <c r="H99" s="150" t="str">
-        <f>IF(D99=G99, "", "Error")</f>
+      <c r="H100" s="150" t="str">
+        <f>IF(D100=G100, "", "Error")</f>
         <v/>
       </c>
-      <c r="J99" s="109"/>
-    </row>
-    <row r="100" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="7"/>
-      <c r="B100" s="7"/>
-      <c r="C100" s="7"/>
-      <c r="D100" s="113"/>
-      <c r="E100" s="117"/>
-      <c r="F100" s="7"/>
-      <c r="H100" s="150"/>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A101" s="94" t="s">
-        <v>102</v>
-      </c>
+      <c r="J100" s="109"/>
+    </row>
+    <row r="101" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="7"/>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
-      <c r="D101" s="113">
-        <v>96626.92</v>
-      </c>
-      <c r="E101" s="149">
-        <f>D101*91.91%</f>
-        <v>88809.802171999996</v>
-      </c>
-      <c r="F101" s="134">
-        <f>D101*8.09%</f>
-        <v>7817.1178279999995</v>
-      </c>
+      <c r="D101" s="113"/>
+      <c r="E101" s="117"/>
+      <c r="F101" s="7"/>
       <c r="H101" s="150"/>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="94" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B102" s="7"/>
-      <c r="C102" s="122"/>
+      <c r="C102" s="7"/>
       <c r="D102" s="113">
-        <v>44400</v>
+        <v>96626.92</v>
       </c>
       <c r="E102" s="149">
         <f>D102*91.91%</f>
-        <v>40808.039999999994</v>
+        <v>88809.802171999996</v>
       </c>
       <c r="F102" s="134">
         <f>D102*8.09%</f>
+        <v>7817.1178279999995</v>
+      </c>
+      <c r="H102" s="150"/>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A103" s="94" t="s">
+        <v>103</v>
+      </c>
+      <c r="B103" s="7"/>
+      <c r="C103" s="122"/>
+      <c r="D103" s="113">
+        <v>44400</v>
+      </c>
+      <c r="E103" s="149">
+        <f>D103*91.91%</f>
+        <v>40808.039999999994</v>
+      </c>
+      <c r="F103" s="134">
+        <f>D103*8.09%</f>
         <v>3591.96</v>
       </c>
-      <c r="H102" s="150"/>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A103" s="95" t="s">
+      <c r="H103" s="150"/>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A104" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="B103" s="95"/>
-      <c r="C103" s="95"/>
-      <c r="D103" s="158">
-        <f>SUM(D101:D102)</f>
+      <c r="B104" s="95"/>
+      <c r="C104" s="95"/>
+      <c r="D104" s="158">
+        <f>SUM(D102:D103)</f>
         <v>141026.91999999998</v>
       </c>
-      <c r="E103" s="147">
-        <f t="shared" ref="E103:F103" si="17">SUM(E101:E102)</f>
+      <c r="E104" s="147">
+        <f t="shared" ref="E104:F104" si="17">SUM(E102:E103)</f>
         <v>129617.84217199999</v>
       </c>
-      <c r="F103" s="147">
+      <c r="F104" s="147">
         <f t="shared" si="17"/>
         <v>11409.077827999999</v>
       </c>
-      <c r="G103" s="109">
-        <f>E103+F103</f>
+      <c r="G104" s="109">
+        <f>E104+F104</f>
         <v>141026.91999999998</v>
       </c>
-      <c r="H103" s="150" t="str">
-        <f>IF(D103=G103, "", "Error")</f>
+      <c r="H104" s="150" t="str">
+        <f>IF(D104=G104, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="7"/>
-      <c r="B104" s="7"/>
-      <c r="C104" s="7"/>
-      <c r="D104" s="190"/>
-      <c r="E104" s="12"/>
-      <c r="F104" s="7"/>
-      <c r="H104" s="150"/>
-    </row>
     <row r="105" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="99" t="s">
+      <c r="A105" s="7"/>
+      <c r="B105" s="7"/>
+      <c r="C105" s="7"/>
+      <c r="D105" s="190"/>
+      <c r="E105" s="12"/>
+      <c r="F105" s="7"/>
+      <c r="H105" s="150"/>
+    </row>
+    <row r="106" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="99" t="s">
         <v>134</v>
       </c>
-      <c r="B105" s="99"/>
-      <c r="C105" s="99"/>
-      <c r="D105" s="191"/>
-      <c r="E105" s="118">
-        <f>D105*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F105" s="136">
-        <f>D105*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G105" s="109">
-        <f>E105+F105</f>
-        <v>0</v>
-      </c>
-      <c r="H105" s="150" t="str">
-        <f>IF(D105=G105, "", "Error")</f>
+      <c r="B106" s="99"/>
+      <c r="C106" s="99"/>
+      <c r="D106" s="191"/>
+      <c r="E106" s="118">
+        <f>D106*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F106" s="136">
+        <f>D106*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="G106" s="109">
+        <f>E106+F106</f>
+        <v>0</v>
+      </c>
+      <c r="H106" s="150" t="str">
+        <f>IF(D106=G106, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="1"/>
-      <c r="D106" s="188"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="10"/>
-      <c r="G106" s="157">
-        <f>SUM(G27:G105)</f>
-        <v>8796045.7599999998</v>
-      </c>
-      <c r="H106" s="150"/>
-    </row>
     <row r="107" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="4" t="s">
+      <c r="A107" s="1"/>
+      <c r="D107" s="188"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="10"/>
+      <c r="G107" s="157">
+        <f>SUM(G27:G106)</f>
+        <v>9096045.7599999998</v>
+      </c>
+      <c r="H107" s="150"/>
+    </row>
+    <row r="108" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B107" s="60"/>
-      <c r="C107" s="5"/>
-      <c r="D107" s="192">
-        <f>SUM(D105+D103+D99+D92+D85+D55+D35+D30+D48)</f>
-        <v>5848392.3399999999</v>
-      </c>
-      <c r="E107" s="148">
-        <f>SUM(E105+E103+E99+E92+E85+E55+E35+E30+E48)</f>
-        <v>5317471.9837839995</v>
-      </c>
-      <c r="F107" s="148">
-        <f>SUM(F105+F103+F99+F92+F85+F55+F35+F30+F48)</f>
+      <c r="B108" s="60"/>
+      <c r="C108" s="5"/>
+      <c r="D108" s="192">
+        <f>SUM(D106+D104+D100+D93+D86+D55+D35+D30+D48)</f>
+        <v>5998392.3399999999</v>
+      </c>
+      <c r="E108" s="148">
+        <f>SUM(E106+E104+E100+E93+E86+E55+E35+E30+E48)</f>
+        <v>5467471.9837839995</v>
+      </c>
+      <c r="F108" s="148">
+        <f>SUM(F106+F104+F100+F93+F86+F55+F35+F30+F48)</f>
         <v>333498.29621600005</v>
       </c>
-      <c r="G107" s="109">
-        <f>E107+F107</f>
-        <v>5650970.2799999993</v>
-      </c>
-      <c r="H107" s="150" t="str">
-        <f>IF(D107=G107, "", "Error")</f>
+      <c r="G108" s="109">
+        <f>E108+F108</f>
+        <v>5800970.2799999993</v>
+      </c>
+      <c r="H108" s="150" t="str">
+        <f>IF(D108=G108, "", "Error")</f>
         <v>Error</v>
       </c>
-      <c r="I107" s="181">
-        <f>D107-G107</f>
+      <c r="I108" s="181">
+        <f>D108-G108</f>
         <v>197422.06000000052</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D108" s="188"/>
-      <c r="E108" s="109"/>
-    </row>
     <row r="109" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="142" t="s">
+      <c r="D109" s="188"/>
+      <c r="E109" s="109"/>
+    </row>
+    <row r="110" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="142" t="s">
         <v>121</v>
       </c>
-      <c r="B109" s="141"/>
-      <c r="C109" s="141"/>
-      <c r="E109" s="109"/>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A110" s="1"/>
-      <c r="C110" s="139"/>
+      <c r="B110" s="141"/>
+      <c r="C110" s="141"/>
       <c r="E110" s="109"/>
     </row>
-    <row r="111" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="C111" s="139"/>
       <c r="E111" s="109"/>
     </row>
     <row r="112" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="143" t="s">
+      <c r="A112" s="1"/>
+      <c r="C112" s="139"/>
+      <c r="E112" s="109"/>
+    </row>
+    <row r="113" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="143" t="s">
         <v>30</v>
       </c>
-      <c r="B112" s="144"/>
-      <c r="C112" s="140">
-        <f>SUM(C110:C111)</f>
-        <v>0</v>
-      </c>
-      <c r="E112" s="109"/>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B113" s="144"/>
+      <c r="C113" s="140">
+        <f>SUM(C111:C112)</f>
+        <v>0</v>
+      </c>
       <c r="E113" s="109"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E114" s="137"/>
+      <c r="E114" s="109"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A115" s="225" t="s">
+      <c r="E115" s="137"/>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A116" s="227" t="s">
         <v>114</v>
       </c>
-      <c r="B115" s="226"/>
-      <c r="C115" s="226"/>
-      <c r="D115" s="226"/>
-      <c r="E115" s="172" t="s">
+      <c r="B116" s="228"/>
+      <c r="C116" s="228"/>
+      <c r="D116" s="228"/>
+      <c r="E116" s="172" t="s">
         <v>22</v>
       </c>
-      <c r="F115" s="173" t="s">
+      <c r="F116" s="173" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="222"/>
-      <c r="B116" s="223"/>
-      <c r="C116" s="224"/>
-      <c r="D116" s="167"/>
-      <c r="E116" s="149"/>
-      <c r="F116" s="134"/>
-    </row>
-    <row r="117" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="219"/>
-      <c r="B117" s="220"/>
-      <c r="C117" s="221"/>
-      <c r="D117" s="182"/>
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="224"/>
+      <c r="B117" s="225"/>
+      <c r="C117" s="226"/>
+      <c r="D117" s="167"/>
       <c r="E117" s="149"/>
       <c r="F117" s="134"/>
     </row>
     <row r="118" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="174"/>
-      <c r="B118" s="175"/>
-      <c r="C118" s="176"/>
+      <c r="A118" s="221"/>
+      <c r="B118" s="222"/>
+      <c r="C118" s="223"/>
       <c r="D118" s="182"/>
       <c r="E118" s="149"/>
       <c r="F118" s="134"/>
     </row>
-    <row r="119" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="219"/>
-      <c r="B119" s="220"/>
-      <c r="C119" s="221"/>
-      <c r="D119" s="113"/>
-      <c r="E119" s="149">
-        <f>D119*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F119" s="134">
-        <f>D119*8.09%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A120" s="213" t="s">
+    <row r="119" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="174"/>
+      <c r="B119" s="175"/>
+      <c r="C119" s="176"/>
+      <c r="D119" s="182"/>
+      <c r="E119" s="149"/>
+      <c r="F119" s="134"/>
+    </row>
+    <row r="120" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="221"/>
+      <c r="B120" s="222"/>
+      <c r="C120" s="223"/>
+      <c r="D120" s="113"/>
+      <c r="E120" s="149">
+        <f>D120*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F120" s="134">
+        <f>D120*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A121" s="215" t="s">
         <v>30</v>
       </c>
-      <c r="B120" s="214"/>
-      <c r="C120" s="215"/>
-      <c r="D120" s="171">
-        <f>SUM(D116:D119)</f>
-        <v>0</v>
-      </c>
-      <c r="E120" s="171">
-        <f>SUM(E116:E119)</f>
-        <v>0</v>
-      </c>
-      <c r="F120" s="171">
-        <f>SUM(F116:F119)</f>
-        <v>0</v>
-      </c>
-      <c r="H120" s="109">
-        <f>E120+F120</f>
-        <v>0</v>
-      </c>
-      <c r="I120" s="150" t="str">
-        <f>IF(D120=H120, "", "Error")</f>
+      <c r="B121" s="216"/>
+      <c r="C121" s="217"/>
+      <c r="D121" s="171">
+        <f>SUM(D117:D120)</f>
+        <v>0</v>
+      </c>
+      <c r="E121" s="171">
+        <f>SUM(E117:E120)</f>
+        <v>0</v>
+      </c>
+      <c r="F121" s="171">
+        <f>SUM(F117:F120)</f>
+        <v>0</v>
+      </c>
+      <c r="H121" s="109">
+        <f>E121+F121</f>
+        <v>0</v>
+      </c>
+      <c r="I121" s="150" t="str">
+        <f>IF(D121=H121, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E122" s="109"/>
-    </row>
     <row r="123" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="102" t="s">
+      <c r="E123" s="109"/>
+    </row>
+    <row r="124" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="102" t="s">
         <v>105</v>
       </c>
-      <c r="B123" s="103">
-        <f>D107</f>
-        <v>5848392.3399999999</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="104" t="s">
+      <c r="B124" s="103">
+        <f>D108</f>
+        <v>5998392.3399999999</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="104" t="s">
         <v>107</v>
       </c>
-      <c r="B124" s="105">
-        <f>D107-D105</f>
-        <v>5848392.3399999999</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D125" s="233"/>
-      <c r="E125" s="233"/>
+      <c r="B125" s="105">
+        <f>D108-D106</f>
+        <v>5998392.3399999999</v>
+      </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A126" s="74" t="s">
+      <c r="D126" s="205"/>
+      <c r="E126" s="205"/>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A127" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="B126" s="75"/>
-      <c r="C126" s="76"/>
-      <c r="D126" s="233"/>
-      <c r="E126" s="233"/>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A127" s="77" t="s">
+      <c r="B127" s="75"/>
+      <c r="C127" s="76"/>
+      <c r="D127" s="205"/>
+      <c r="E127" s="205"/>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A128" s="77" t="s">
         <v>92</v>
       </c>
-      <c r="B127" s="78">
+      <c r="B128" s="78">
         <v>4452323.820828055</v>
       </c>
-      <c r="C127" s="78"/>
-      <c r="D127" s="233"/>
-      <c r="E127" s="233"/>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A128" s="79" t="s">
+      <c r="C128" s="78"/>
+      <c r="D128" s="205"/>
+      <c r="E128" s="205"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" s="79" t="s">
         <v>93</v>
       </c>
-      <c r="B128" s="92">
+      <c r="B129" s="92">
         <f>PRORRATEO!G52</f>
         <v>6849105.1357215978</v>
       </c>
-      <c r="C128" s="78" t="s">
+      <c r="C129" s="78" t="s">
         <v>94</v>
       </c>
-      <c r="D128" s="233"/>
-      <c r="E128" s="233"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A129" s="79" t="s">
-        <v>116</v>
-      </c>
-      <c r="B129" s="178">
-        <f>-B124</f>
-        <v>-5848392.3399999999</v>
-      </c>
-      <c r="C129" s="76"/>
-      <c r="D129" s="233"/>
-      <c r="E129" s="233"/>
-      <c r="G129" s="113"/>
+      <c r="D129" s="205"/>
+      <c r="E129" s="205"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="79" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B130" s="178">
-        <f>-D120</f>
-        <v>0</v>
+        <f>-B125</f>
+        <v>-5998392.3399999999</v>
       </c>
       <c r="C130" s="76"/>
-      <c r="D130" s="233"/>
-      <c r="E130" s="233"/>
-      <c r="G130" s="125"/>
+      <c r="D130" s="205"/>
+      <c r="E130" s="205"/>
+      <c r="G130" s="113"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="79" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B131" s="178">
-        <f>-B138</f>
-        <v>0</v>
-      </c>
-      <c r="C131" s="80"/>
+        <f>-D121</f>
+        <v>0</v>
+      </c>
+      <c r="C131" s="76"/>
+      <c r="D131" s="205"/>
+      <c r="E131" s="205"/>
+      <c r="G131" s="125"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="79" t="s">
+        <v>106</v>
+      </c>
+      <c r="B132" s="178">
+        <f>-B139</f>
+        <v>0</v>
+      </c>
+      <c r="C132" s="80"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" s="79" t="s">
         <v>121</v>
       </c>
-      <c r="B132" s="93">
-        <f>-C112</f>
-        <v>0</v>
-      </c>
-      <c r="C132" s="80"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A133" s="79"/>
-      <c r="B133" s="75"/>
+      <c r="B133" s="93">
+        <f>-C113</f>
+        <v>0</v>
+      </c>
       <c r="C133" s="80"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A134" s="77" t="s">
+      <c r="A134" s="79"/>
+      <c r="B134" s="75"/>
+      <c r="C134" s="80"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B134" s="81">
-        <f>SUM(B127:B133)</f>
-        <v>5453036.6165496521</v>
-      </c>
-      <c r="C134" s="154"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A135" s="80"/>
-      <c r="C135" s="76"/>
-      <c r="D135" s="83"/>
+      <c r="B135" s="81">
+        <f>SUM(B128:B134)</f>
+        <v>5303036.6165496521</v>
+      </c>
+      <c r="C135" s="154"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136" s="80"/>
       <c r="C136" s="76"/>
-      <c r="D136" s="109"/>
-      <c r="E136" s="181"/>
+      <c r="D136" s="83"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A137" s="74" t="s">
+      <c r="C137" s="76"/>
+      <c r="D137" s="109"/>
+      <c r="E137" s="181"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="B137" s="11">
+      <c r="B138" s="11">
         <v>-310694.54000000004</v>
       </c>
-      <c r="C137" s="82"/>
-    </row>
-    <row r="138" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="77" t="s">
+      <c r="C138" s="82"/>
+    </row>
+    <row r="139" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="77" t="s">
         <v>156</v>
       </c>
-      <c r="B138" s="93"/>
-      <c r="C138" s="82"/>
-      <c r="D138" s="181"/>
-      <c r="E138" s="109"/>
-    </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="77"/>
-      <c r="B139" s="178"/>
+      <c r="B139" s="93"/>
       <c r="C139" s="82"/>
+      <c r="D139" s="181"/>
       <c r="E139" s="109"/>
     </row>
     <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
@@ -4053,76 +4070,83 @@
       <c r="C140" s="82"/>
       <c r="E140" s="109"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="77"/>
       <c r="B141" s="178"/>
       <c r="C141" s="82"/>
       <c r="E141" s="109"/>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A142" s="100" t="s">
+      <c r="A142" s="77"/>
+      <c r="B142" s="178"/>
+      <c r="C142" s="82"/>
+      <c r="E142" s="109"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A143" s="100" t="s">
         <v>30</v>
       </c>
-      <c r="B142" s="101">
-        <f>SUM(B137:B141)</f>
+      <c r="B143" s="101">
+        <f>SUM(B138:B142)</f>
         <v>-310694.54000000004</v>
       </c>
-      <c r="C142" s="82"/>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C143" s="83"/>
-      <c r="D143" s="181"/>
+      <c r="C143" s="82"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B144" s="80"/>
-      <c r="C144" s="76"/>
-    </row>
-    <row r="146" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="N146" s="12"/>
-    </row>
-    <row r="149" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B149" s="232" t="s">
+      <c r="C144" s="83"/>
+      <c r="D144" s="181"/>
+    </row>
+    <row r="145" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B145" s="80"/>
+      <c r="C145" s="76"/>
+    </row>
+    <row r="147" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="N147" s="12"/>
+    </row>
+    <row r="150" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B150" s="204" t="s">
         <v>155</v>
       </c>
-      <c r="C149" s="232"/>
-      <c r="D149" s="232"/>
-      <c r="E149" s="232"/>
-    </row>
-    <row r="150" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B150" s="232"/>
-      <c r="C150" s="232"/>
-      <c r="D150" s="232"/>
-      <c r="E150" s="232"/>
+      <c r="C150" s="204"/>
+      <c r="D150" s="204"/>
+      <c r="E150" s="204"/>
     </row>
     <row r="151" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B151" s="232"/>
-      <c r="C151" s="232"/>
-      <c r="D151" s="232"/>
-      <c r="E151" s="232"/>
+      <c r="B151" s="204"/>
+      <c r="C151" s="204"/>
+      <c r="D151" s="204"/>
+      <c r="E151" s="204"/>
     </row>
     <row r="152" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B152" s="232"/>
-      <c r="C152" s="232"/>
-      <c r="D152" s="232"/>
-      <c r="E152" s="232"/>
+      <c r="B152" s="204"/>
+      <c r="C152" s="204"/>
+      <c r="D152" s="204"/>
+      <c r="E152" s="204"/>
     </row>
     <row r="153" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B153" s="232"/>
-      <c r="C153" s="232"/>
-      <c r="D153" s="232"/>
-      <c r="E153" s="232"/>
+      <c r="B153" s="204"/>
+      <c r="C153" s="204"/>
+      <c r="D153" s="204"/>
+      <c r="E153" s="204"/>
+    </row>
+    <row r="154" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B154" s="204"/>
+      <c r="C154" s="204"/>
+      <c r="D154" s="204"/>
+      <c r="E154" s="204"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B149:E153"/>
-    <mergeCell ref="D125:E130"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="B150:E154"/>
+    <mergeCell ref="D126:E131"/>
     <mergeCell ref="B14:D17"/>
+    <mergeCell ref="A121:C121"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A118:C118"/>
     <mergeCell ref="A120:C120"/>
-    <mergeCell ref="A68:C68"/>
     <mergeCell ref="A117:C117"/>
-    <mergeCell ref="A119:C119"/>
-    <mergeCell ref="A116:C116"/>
-    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="A116:D116"/>
     <mergeCell ref="A77:C77"/>
     <mergeCell ref="A67:C67"/>
     <mergeCell ref="A74:C74"/>
@@ -4130,7 +4154,6 @@
     <mergeCell ref="A70:C70"/>
     <mergeCell ref="A71:C71"/>
     <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A75:C75"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4176,15 +4199,15 @@
       <c r="K1" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="L1" s="240">
-        <f>RESUMEN!D107</f>
-        <v>5848392.3399999999</v>
-      </c>
-      <c r="M1" s="241"/>
+      <c r="L1" s="236">
+        <f>RESUMEN!D108</f>
+        <v>5998392.3399999999</v>
+      </c>
+      <c r="M1" s="237"/>
       <c r="N1" s="152"/>
       <c r="O1" s="135">
         <f>L1*8.09%</f>
-        <v>473134.940306</v>
+        <v>485269.940306</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -4209,7 +4232,7 @@
       <c r="N2" s="153"/>
       <c r="O2" s="135">
         <f>O1-K7-553-50-86-8</f>
-        <v>141507.640655</v>
+        <v>153642.640655</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -4259,13 +4282,13 @@
       <c r="A5" s="234" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="236" t="s">
+      <c r="B5" s="247" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="234" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="238" t="s">
+      <c r="D5" s="245" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="234" t="s">
@@ -4277,43 +4300,43 @@
       <c r="G5" s="234" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="244" t="s">
+      <c r="H5" s="240" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="238" t="s">
+      <c r="I5" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="J5" s="242" t="s">
+      <c r="J5" s="238" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="242" t="s">
+      <c r="K5" s="238" t="s">
         <v>70</v>
       </c>
-      <c r="L5" s="247" t="s">
+      <c r="L5" s="243" t="s">
         <v>124</v>
       </c>
-      <c r="M5" s="242" t="s">
+      <c r="M5" s="238" t="s">
         <v>68</v>
       </c>
-      <c r="N5" s="242" t="s">
+      <c r="N5" s="238" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="235"/>
-      <c r="B6" s="237"/>
+      <c r="B6" s="248"/>
       <c r="C6" s="235"/>
-      <c r="D6" s="239"/>
+      <c r="D6" s="249"/>
       <c r="E6" s="235"/>
       <c r="F6" s="235"/>
       <c r="G6" s="235"/>
-      <c r="H6" s="245"/>
-      <c r="I6" s="249"/>
-      <c r="J6" s="243"/>
-      <c r="K6" s="246"/>
-      <c r="L6" s="248"/>
-      <c r="M6" s="246"/>
-      <c r="N6" s="243"/>
+      <c r="H6" s="241"/>
+      <c r="I6" s="246"/>
+      <c r="J6" s="239"/>
+      <c r="K6" s="242"/>
+      <c r="L6" s="244"/>
+      <c r="M6" s="242"/>
+      <c r="N6" s="239"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
@@ -6091,7 +6114,7 @@
       </c>
       <c r="P43" s="109">
         <f>L1-K52</f>
-        <v>603288.9310490014</v>
+        <v>753288.9310490014</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
@@ -6520,36 +6543,36 @@
     <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="K53" s="138">
         <f>K52-L1</f>
-        <v>-603288.9310490014</v>
+        <v>-753288.9310490014</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="233"/>
-      <c r="D54" s="233"/>
-      <c r="E54" s="233"/>
-      <c r="F54" s="233"/>
-      <c r="G54" s="233"/>
-      <c r="H54" s="233"/>
-      <c r="I54" s="233"/>
-      <c r="J54" s="233"/>
-      <c r="K54" s="233"/>
-      <c r="L54" s="233"/>
-      <c r="M54" s="233"/>
-      <c r="N54" s="233"/>
+      <c r="C54" s="205"/>
+      <c r="D54" s="205"/>
+      <c r="E54" s="205"/>
+      <c r="F54" s="205"/>
+      <c r="G54" s="205"/>
+      <c r="H54" s="205"/>
+      <c r="I54" s="205"/>
+      <c r="J54" s="205"/>
+      <c r="K54" s="205"/>
+      <c r="L54" s="205"/>
+      <c r="M54" s="205"/>
+      <c r="N54" s="205"/>
     </row>
     <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="233"/>
-      <c r="D55" s="233"/>
-      <c r="E55" s="233"/>
-      <c r="F55" s="233"/>
-      <c r="G55" s="233"/>
-      <c r="H55" s="233"/>
-      <c r="I55" s="233"/>
-      <c r="J55" s="233"/>
-      <c r="K55" s="233"/>
-      <c r="L55" s="233"/>
-      <c r="M55" s="233"/>
-      <c r="N55" s="233"/>
+      <c r="C55" s="205"/>
+      <c r="D55" s="205"/>
+      <c r="E55" s="205"/>
+      <c r="F55" s="205"/>
+      <c r="G55" s="205"/>
+      <c r="H55" s="205"/>
+      <c r="I55" s="205"/>
+      <c r="J55" s="205"/>
+      <c r="K55" s="205"/>
+      <c r="L55" s="205"/>
+      <c r="M55" s="205"/>
+      <c r="N55" s="205"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C56" s="169"/>
@@ -6566,107 +6589,112 @@
       <c r="N56" s="169"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C57" s="233" t="s">
+      <c r="C57" s="205" t="s">
         <v>130</v>
       </c>
-      <c r="D57" s="233"/>
-      <c r="E57" s="233"/>
-      <c r="F57" s="233"/>
-      <c r="G57" s="233"/>
-      <c r="H57" s="233"/>
-      <c r="I57" s="233"/>
-      <c r="J57" s="233"/>
-      <c r="K57" s="233"/>
-      <c r="L57" s="233"/>
-      <c r="M57" s="233"/>
-      <c r="N57" s="233"/>
+      <c r="D57" s="205"/>
+      <c r="E57" s="205"/>
+      <c r="F57" s="205"/>
+      <c r="G57" s="205"/>
+      <c r="H57" s="205"/>
+      <c r="I57" s="205"/>
+      <c r="J57" s="205"/>
+      <c r="K57" s="205"/>
+      <c r="L57" s="205"/>
+      <c r="M57" s="205"/>
+      <c r="N57" s="205"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C58" s="233"/>
-      <c r="D58" s="233"/>
-      <c r="E58" s="233"/>
-      <c r="F58" s="233"/>
-      <c r="G58" s="233"/>
-      <c r="H58" s="233"/>
-      <c r="I58" s="233"/>
-      <c r="J58" s="233"/>
-      <c r="K58" s="233"/>
-      <c r="L58" s="233"/>
-      <c r="M58" s="233"/>
-      <c r="N58" s="233"/>
+      <c r="C58" s="205"/>
+      <c r="D58" s="205"/>
+      <c r="E58" s="205"/>
+      <c r="F58" s="205"/>
+      <c r="G58" s="205"/>
+      <c r="H58" s="205"/>
+      <c r="I58" s="205"/>
+      <c r="J58" s="205"/>
+      <c r="K58" s="205"/>
+      <c r="L58" s="205"/>
+      <c r="M58" s="205"/>
+      <c r="N58" s="205"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C59" s="233"/>
-      <c r="D59" s="233"/>
-      <c r="E59" s="233"/>
-      <c r="F59" s="233"/>
-      <c r="G59" s="233"/>
-      <c r="H59" s="233"/>
-      <c r="I59" s="233"/>
-      <c r="J59" s="233"/>
-      <c r="K59" s="233"/>
-      <c r="L59" s="233"/>
-      <c r="M59" s="233"/>
-      <c r="N59" s="233"/>
+      <c r="C59" s="205"/>
+      <c r="D59" s="205"/>
+      <c r="E59" s="205"/>
+      <c r="F59" s="205"/>
+      <c r="G59" s="205"/>
+      <c r="H59" s="205"/>
+      <c r="I59" s="205"/>
+      <c r="J59" s="205"/>
+      <c r="K59" s="205"/>
+      <c r="L59" s="205"/>
+      <c r="M59" s="205"/>
+      <c r="N59" s="205"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C60" s="233"/>
-      <c r="D60" s="233"/>
-      <c r="E60" s="233"/>
-      <c r="F60" s="233"/>
-      <c r="G60" s="233"/>
-      <c r="H60" s="233"/>
-      <c r="I60" s="233"/>
-      <c r="J60" s="233"/>
-      <c r="K60" s="233"/>
-      <c r="L60" s="233"/>
-      <c r="M60" s="233"/>
-      <c r="N60" s="233"/>
+      <c r="C60" s="205"/>
+      <c r="D60" s="205"/>
+      <c r="E60" s="205"/>
+      <c r="F60" s="205"/>
+      <c r="G60" s="205"/>
+      <c r="H60" s="205"/>
+      <c r="I60" s="205"/>
+      <c r="J60" s="205"/>
+      <c r="K60" s="205"/>
+      <c r="L60" s="205"/>
+      <c r="M60" s="205"/>
+      <c r="N60" s="205"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C61" s="233"/>
-      <c r="D61" s="233"/>
-      <c r="E61" s="233"/>
-      <c r="F61" s="233"/>
-      <c r="G61" s="233"/>
-      <c r="H61" s="233"/>
-      <c r="I61" s="233"/>
-      <c r="J61" s="233"/>
-      <c r="K61" s="233"/>
-      <c r="L61" s="233"/>
-      <c r="M61" s="233"/>
-      <c r="N61" s="233"/>
+      <c r="C61" s="205"/>
+      <c r="D61" s="205"/>
+      <c r="E61" s="205"/>
+      <c r="F61" s="205"/>
+      <c r="G61" s="205"/>
+      <c r="H61" s="205"/>
+      <c r="I61" s="205"/>
+      <c r="J61" s="205"/>
+      <c r="K61" s="205"/>
+      <c r="L61" s="205"/>
+      <c r="M61" s="205"/>
+      <c r="N61" s="205"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C62" s="233"/>
-      <c r="D62" s="233"/>
-      <c r="E62" s="233"/>
-      <c r="F62" s="233"/>
-      <c r="G62" s="233"/>
-      <c r="H62" s="233"/>
-      <c r="I62" s="233"/>
-      <c r="J62" s="233"/>
-      <c r="K62" s="233"/>
-      <c r="L62" s="233"/>
-      <c r="M62" s="233"/>
-      <c r="N62" s="233"/>
+      <c r="C62" s="205"/>
+      <c r="D62" s="205"/>
+      <c r="E62" s="205"/>
+      <c r="F62" s="205"/>
+      <c r="G62" s="205"/>
+      <c r="H62" s="205"/>
+      <c r="I62" s="205"/>
+      <c r="J62" s="205"/>
+      <c r="K62" s="205"/>
+      <c r="L62" s="205"/>
+      <c r="M62" s="205"/>
+      <c r="N62" s="205"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C63" s="233"/>
-      <c r="D63" s="233"/>
-      <c r="E63" s="233"/>
-      <c r="F63" s="233"/>
-      <c r="G63" s="233"/>
-      <c r="H63" s="233"/>
-      <c r="I63" s="233"/>
-      <c r="J63" s="233"/>
-      <c r="K63" s="233"/>
-      <c r="L63" s="233"/>
-      <c r="M63" s="233"/>
-      <c r="N63" s="233"/>
+      <c r="C63" s="205"/>
+      <c r="D63" s="205"/>
+      <c r="E63" s="205"/>
+      <c r="F63" s="205"/>
+      <c r="G63" s="205"/>
+      <c r="H63" s="205"/>
+      <c r="I63" s="205"/>
+      <c r="J63" s="205"/>
+      <c r="K63" s="205"/>
+      <c r="L63" s="205"/>
+      <c r="M63" s="205"/>
+      <c r="N63" s="205"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
@@ -6679,11 +6707,6 @@
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="I5:I6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/BELGRANO 1646/Mayo/MAYO-BLG1646.xlsx
+++ b/BELGRANO 1646/Mayo/MAYO-BLG1646.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BELGRANO 1646\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BELGRANO 1646\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759F3AA1-DCA6-4031-9B59-47DC16388C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE51B6C-4409-4BBB-B402-61920C61DD6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$144</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$146</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="177">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -474,48 +474,12 @@
     <t>ARCA</t>
   </si>
   <si>
-    <t>Piletero Sr Dario - puesta a punto y mantenimiento de pileta- ultimo mes</t>
-  </si>
-  <si>
-    <t>SEGURO OBLIGATORIO SR DIEGO BRITEZ FEDERACION PATRONAL DEBITO AUTOMATICO 4/4</t>
-  </si>
-  <si>
-    <t>Pago mis cuentas 9/4</t>
-  </si>
-  <si>
-    <t>Debito 14/04</t>
-  </si>
-  <si>
     <t xml:space="preserve">Contessi - Mantenimiento de ascensores </t>
   </si>
   <si>
-    <t>Debito 30/04</t>
-  </si>
-  <si>
-    <t>PMC 07/04</t>
-  </si>
-  <si>
-    <t>Numero 1859135 Debito automatico 1/04</t>
-  </si>
-  <si>
-    <t>AySa Destapaciones - 24/04</t>
-  </si>
-  <si>
-    <t>JPL - Articulos de limpieza 14/04</t>
-  </si>
-  <si>
-    <t>Fumigacion 9/04</t>
-  </si>
-  <si>
     <t>FEUILLANT, GASTON</t>
   </si>
   <si>
-    <t>Doartero Julio - Ajuste de todas las puertas y reparacion de la puerta principal</t>
-  </si>
-  <si>
-    <t>Remis Sr. Dario - Dia de paro</t>
-  </si>
-  <si>
     <t>VTO. 16/06</t>
   </si>
   <si>
@@ -528,24 +492,9 @@
     <t>Energoup MES DE MAYO</t>
   </si>
   <si>
-    <t>EN TEORIA EN ESTE PUNTO (MAYO DEL 2025) LA CAJA NOS DA BIEN, TENEMOS 1,4M EN EL BANCO Y CERCA DE 120MIL PESOS EN EFECTIVO</t>
-  </si>
-  <si>
     <t>Ingreso mes de ABRIL</t>
   </si>
   <si>
-    <t>Ruso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kromacolor  -  Recuplast </t>
-  </si>
-  <si>
-    <t>Lucas</t>
-  </si>
-  <si>
-    <t>Sur Energy</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mes de MAYO </t>
   </si>
   <si>
@@ -555,22 +504,94 @@
     <t>Contessi provision y colocacion de 60 lts de aceite hidraulico en la sede del monta auto</t>
   </si>
   <si>
-    <t>Salvatierra limpieza de columna de baño desde piso 3 (inclusive) hasta el piso 10 (inclusive)</t>
-  </si>
-  <si>
-    <t>Remis Sr. Diego - Dia de paro</t>
-  </si>
-  <si>
-    <t>Alejandro 1646</t>
-  </si>
-  <si>
-    <t>Contessi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camaras del sur 19/05 </t>
-  </si>
-  <si>
-    <t>Doartero Julio - Emergencia 26/05</t>
+    <t>SEGURO OBLIGATORIO SR DIEGO BRITEZ FEDERACION PATRONAL DEBITO AUTOMATICO 05/05</t>
+  </si>
+  <si>
+    <t>Arreglo de motor retirado y reemplazado por uno nuevo en montavehiculos</t>
+  </si>
+  <si>
+    <t>Debito 12/05</t>
+  </si>
+  <si>
+    <t>Pago mis cuentas 12/05</t>
+  </si>
+  <si>
+    <t>Fumigacion 12/05</t>
+  </si>
+  <si>
+    <t>Doartero Julio - Ajuste de todas las puertas y reparacion de la puerta principal 16/05</t>
+  </si>
+  <si>
+    <t>Camaras del sur 19/05 - compra y colocacion camaras de entradas (pileta y gimnasio)</t>
+  </si>
+  <si>
+    <t>Servisur - cambio de luminarias 19/05</t>
+  </si>
+  <si>
+    <t>Numero 1859135 Debito automatico 5/05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antonio santillan plomero - Arreglo tanque </t>
+  </si>
+  <si>
+    <t>Salvatierra limpieza de columna de baño desde piso 3 (inclusive) hasta el piso 10 (inclusive) - 20/05</t>
+  </si>
+  <si>
+    <t>Guido Alterini - Jardineria : Adelanto compra pasto</t>
+  </si>
+  <si>
+    <t>Kromacolor  -  Compra de materiales : Sellador Sika 23/05</t>
+  </si>
+  <si>
+    <t>Doartero Julio - Emergencia purga de grupo electrogeno por falta de combustible 26/05</t>
+  </si>
+  <si>
+    <t>Compra Fabio Tolosa - Combustible 19/05</t>
+  </si>
+  <si>
+    <t>Compra Alejandro Davin - Combustible 17/05</t>
+  </si>
+  <si>
+    <t>Combustible comprado por el Sr Lucas - remisero 24/05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas - viajes entregas de combustible </t>
+  </si>
+  <si>
+    <t>Remis Sr. Diego - Dias de paro</t>
+  </si>
+  <si>
+    <t>Silletero - Sr Oscar Colmeiro - Sellado de grieta medianera piso 11 26/05</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza</t>
+  </si>
+  <si>
+    <t>Combustible comprado por el Sr Ruso - remisero 23/05</t>
+  </si>
+  <si>
+    <t>Reparacion puerta SUM 02/05</t>
+  </si>
+  <si>
+    <t>Preinstalacion nueva aire acondicionado SUM - Leandro Gomez 27/5</t>
+  </si>
+  <si>
+    <t>Compra de Juan Manuel Villa - Combustible 23/05</t>
+  </si>
+  <si>
+    <t>Debito 27/05</t>
+  </si>
+  <si>
+    <t>Gabriel Villegas - Envio carte documento Edesur</t>
+  </si>
+  <si>
+    <t>ADS - Imputado en el mes de Marzo y transferido finalizada las charlas por la desvinculacion</t>
+  </si>
+  <si>
+    <t>Contessi - Imputado en el mes de Abril y transferido una vez en la municipalidad se asento el contrato</t>
+  </si>
+  <si>
+    <t>EN TEORIA EN ESTE PUNTO (MAYO DEL 2025) LA CAJA NO NOS DA BIEN, TENEMOS 173MIL PESOS DE DIFERENCIA</t>
   </si>
 </sst>
 </file>
@@ -578,14 +599,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="168" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="169" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -1294,11 +1315,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="252">
+  <cellXfs count="255">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
@@ -1308,7 +1329,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
@@ -1320,7 +1341,7 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1331,12 +1352,12 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="2" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1388,7 +1409,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1396,7 +1417,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1412,17 +1433,17 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1435,12 +1456,12 @@
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1448,54 +1469,54 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="9" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="9" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="14" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="8" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="39" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="10" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="10" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
@@ -1506,197 +1527,219 @@
     <xf numFmtId="10" fontId="2" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="6" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="6" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="14" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="14" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="15" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="15" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="10" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="10" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1720,26 +1763,23 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2106,23 +2146,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N154"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N156"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
     <col min="8" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="18.33203125" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8"/>
       <c r="B1" s="97" t="s">
         <v>119</v>
@@ -2131,7 +2171,7 @@
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="64"/>
       <c r="B2" s="65" t="s">
         <v>0</v>
@@ -2140,7 +2180,7 @@
       <c r="D2" s="65"/>
       <c r="E2" s="66"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="67"/>
       <c r="B3" s="68" t="s">
         <v>89</v>
@@ -2149,7 +2189,7 @@
       <c r="D3" s="68"/>
       <c r="E3" s="69"/>
     </row>
-    <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="67"/>
       <c r="B4" s="68" t="s">
         <v>90</v>
@@ -2158,20 +2198,20 @@
       <c r="D4" s="68"/>
       <c r="E4" s="69"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C5" s="71" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D5" s="71"/>
       <c r="E5" s="72"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="67" t="s">
         <v>100</v>
       </c>
@@ -2180,7 +2220,7 @@
       <c r="D6" s="68"/>
       <c r="E6" s="69"/>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="70" t="s">
         <v>99</v>
       </c>
@@ -2189,37 +2229,37 @@
       <c r="D7" s="71"/>
       <c r="E7" s="72"/>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="206" t="s">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="201" t="s">
         <v>135</v>
       </c>
-      <c r="C14" s="207"/>
-      <c r="D14" s="208"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="209"/>
-      <c r="C15" s="210"/>
-      <c r="D15" s="211"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="209"/>
-      <c r="C16" s="210"/>
-      <c r="D16" s="211"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="212"/>
-      <c r="C17" s="213"/>
-      <c r="D17" s="214"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C14" s="202"/>
+      <c r="D14" s="203"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="204"/>
+      <c r="C15" s="205"/>
+      <c r="D15" s="206"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="204"/>
+      <c r="C16" s="205"/>
+      <c r="D16" s="206"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="207"/>
+      <c r="C17" s="208"/>
+      <c r="D17" s="209"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="61" t="s">
         <v>87</v>
       </c>
@@ -2233,105 +2273,115 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="121" t="s">
         <v>16</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="130"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="121" t="s">
         <v>127</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="186">
-        <v>1202204.23</v>
+      <c r="D23" s="182">
+        <v>1234864.1000000001</v>
       </c>
       <c r="E23" s="134">
         <f>D23*91.91%</f>
-        <v>1104945.9077929999</v>
+        <v>1134963.5943100001</v>
       </c>
       <c r="F23" s="134">
         <f>D23*8.09%</f>
-        <v>97258.322207000005</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+        <v>99900.505690000005</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="121" t="s">
         <v>2</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="186">
-        <v>-261479.42</v>
+      <c r="D24" s="182">
+        <v>-268582.93</v>
       </c>
       <c r="E24" s="134">
-        <f t="shared" ref="E24:E25" si="0">D24*91.91%</f>
-        <v>-240325.734922</v>
+        <f t="shared" ref="E24:E26" si="0">D24*91.91%</f>
+        <v>-246854.57096299998</v>
       </c>
       <c r="F24" s="134">
-        <f t="shared" ref="F24:F25" si="1">D24*8.09%</f>
-        <v>-21153.685078000002</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" ref="F24:F26" si="1">D24*8.09%</f>
+        <v>-21728.359036999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="121" t="s">
         <v>113</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="186">
-        <v>0.19</v>
+      <c r="D25" s="182">
+        <v>0.83</v>
       </c>
       <c r="E25" s="134">
         <f t="shared" si="0"/>
-        <v>0.17462899999999998</v>
+        <v>0.76285299999999989</v>
       </c>
       <c r="F25" s="134">
         <f t="shared" si="1"/>
-        <v>1.5371000000000001E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="121"/>
+        <v>6.7146999999999998E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="121" t="s">
+        <v>165</v>
+      </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="186"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-    </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D26" s="182">
+        <v>13000</v>
+      </c>
+      <c r="E26" s="134">
+        <f t="shared" si="0"/>
+        <v>11948.3</v>
+      </c>
+      <c r="F26" s="134">
+        <f t="shared" si="1"/>
+        <v>1051.7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="121"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
-      <c r="D27" s="186"/>
+      <c r="D27" s="182"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="121"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="186"/>
+      <c r="D28" s="182"/>
       <c r="E28" s="134"/>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="121"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="186"/>
+      <c r="D29" s="182"/>
       <c r="E29" s="134"/>
       <c r="F29" s="7"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="95" t="s">
         <v>3</v>
       </c>
@@ -2339,32 +2389,32 @@
       <c r="C30" s="95"/>
       <c r="D30" s="107">
         <f>SUM(D23:D29)</f>
-        <v>940724.99999999988</v>
+        <v>979282.00000000012</v>
       </c>
       <c r="E30" s="107">
         <f t="shared" ref="E30" si="2">SUM(E23:E29)</f>
-        <v>864620.34749999992</v>
+        <v>900058.08620000014</v>
       </c>
       <c r="F30" s="107">
         <f>SUM(F23:F29)</f>
-        <v>76104.652500000011</v>
+        <v>79223.913799999995</v>
       </c>
       <c r="G30" s="109">
         <f>E30+F30</f>
-        <v>940724.99999999988</v>
+        <v>979282.00000000012</v>
       </c>
       <c r="H30" s="150" t="str">
         <f>IF(D30=G30, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="94" t="s">
         <v>110</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="187">
+      <c r="D31" s="183">
         <v>0</v>
       </c>
       <c r="E31" s="134">
@@ -2377,11 +2427,11 @@
       </c>
       <c r="H31" s="150"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="94"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="186">
+      <c r="D32" s="182">
         <v>0</v>
       </c>
       <c r="E32" s="134">
@@ -2394,25 +2444,25 @@
       </c>
       <c r="H32" s="150"/>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="94"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="186"/>
+      <c r="D33" s="182"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="H33" s="150"/>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="94"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="186"/>
+      <c r="D34" s="182"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="H34" s="150"/>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="95" t="s">
         <v>118</v>
       </c>
@@ -2439,13 +2489,13 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="94" t="s">
         <v>110</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
-      <c r="D36" s="187"/>
+      <c r="D36" s="183"/>
       <c r="E36" s="134">
         <f>D36*91.91%</f>
         <v>0</v>
@@ -2456,13 +2506,13 @@
       </c>
       <c r="H36" s="150"/>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>131</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="186"/>
+      <c r="D37" s="182"/>
       <c r="E37" s="134">
         <f t="shared" ref="E37:E38" si="4">D37*91.91%</f>
         <v>0</v>
@@ -2473,13 +2523,13 @@
       </c>
       <c r="H37" s="150"/>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="94" t="s">
         <v>2</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="186"/>
+      <c r="D38" s="182"/>
       <c r="E38" s="134">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -2490,7 +2540,7 @@
       </c>
       <c r="H38" s="150"/>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="95" t="s">
         <v>111</v>
       </c>
@@ -2510,34 +2560,34 @@
       </c>
       <c r="H39" s="150"/>
     </row>
-    <row r="40" spans="1:8" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="129"/>
       <c r="B40" s="98"/>
       <c r="C40" s="98"/>
-      <c r="D40" s="186"/>
+      <c r="D40" s="182"/>
       <c r="E40" s="120"/>
       <c r="F40" s="120"/>
       <c r="H40" s="150"/>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="129"/>
       <c r="B41" s="98"/>
       <c r="C41" s="98"/>
-      <c r="D41" s="186"/>
+      <c r="D41" s="182"/>
       <c r="E41" s="120"/>
       <c r="F41" s="120"/>
       <c r="H41" s="150"/>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="98"/>
       <c r="B42" s="98"/>
       <c r="C42" s="111"/>
-      <c r="D42" s="186"/>
+      <c r="D42" s="182"/>
       <c r="E42" s="120"/>
       <c r="F42" s="120"/>
       <c r="H42" s="150"/>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="95" t="s">
         <v>118</v>
       </c>
@@ -2554,32 +2604,28 @@
       </c>
       <c r="H43" s="150"/>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="94"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="188"/>
+      <c r="D44" s="184"/>
       <c r="E44" s="114"/>
       <c r="F44" s="7"/>
       <c r="H44" s="150"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="7" t="s">
-        <v>137</v>
-      </c>
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="113">
-        <v>80000</v>
-      </c>
+      <c r="D45" s="113"/>
       <c r="E45" s="149">
         <f>D45</f>
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="F45" s="7"/>
       <c r="H45" s="150"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="94"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -2594,11 +2640,11 @@
       </c>
       <c r="H46" s="150"/>
     </row>
-    <row r="47" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="94"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
-      <c r="D47" s="189"/>
+      <c r="D47" s="185"/>
       <c r="E47" s="134">
         <f>D47*91.91%</f>
         <v>0</v>
@@ -2609,7 +2655,7 @@
       </c>
       <c r="H47" s="150"/>
     </row>
-    <row r="48" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="95" t="s">
         <v>128</v>
       </c>
@@ -2617,54 +2663,54 @@
       <c r="C48" s="95"/>
       <c r="D48" s="107">
         <f>SUM(D45:D47)</f>
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="E48" s="159">
         <f>SUM(E45:E47)</f>
-        <v>80000</v>
-      </c>
-      <c r="F48" s="170">
+        <v>0</v>
+      </c>
+      <c r="F48" s="169">
         <f>SUM(F45:F47)</f>
         <v>0</v>
       </c>
       <c r="G48" s="109">
         <f>E48+F48</f>
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="H48" s="150"/>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
-      <c r="D49" s="189"/>
+      <c r="D49" s="185"/>
       <c r="E49" s="115"/>
       <c r="F49" s="100"/>
       <c r="H49" s="150"/>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="189"/>
+      <c r="D50" s="185"/>
       <c r="E50" s="114"/>
       <c r="F50" s="100"/>
       <c r="H50" s="150"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="94" t="s">
         <v>4</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
-      <c r="D51" s="189"/>
+      <c r="D51" s="185"/>
       <c r="E51" s="114"/>
       <c r="F51" s="100"/>
       <c r="H51" s="150"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="94" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B52" s="7"/>
       <c r="C52" s="98"/>
@@ -2681,15 +2727,15 @@
       </c>
       <c r="H52" s="150"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="94" t="s">
         <v>5</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C53" s="7"/>
-      <c r="D53" s="198">
+      <c r="D53" s="113">
         <f>102143.27+6011.02+54099.18</f>
         <v>162253.47</v>
       </c>
@@ -2703,15 +2749,15 @@
       </c>
       <c r="H53" s="150"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="94" t="s">
         <v>136</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="C54" s="7"/>
-      <c r="D54" s="198">
+      <c r="D54" s="113">
         <v>532295.61</v>
       </c>
       <c r="E54" s="134">
@@ -2724,7 +2770,7 @@
       </c>
       <c r="H54" s="150"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="95" t="s">
         <v>6</v>
       </c>
@@ -2751,1409 +2797,1796 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="189"/>
+      <c r="D56" s="185"/>
       <c r="E56" s="115"/>
       <c r="F56" s="7"/>
       <c r="H56" s="150"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="114" t="s">
+        <v>146</v>
+      </c>
+      <c r="B57" s="176"/>
+      <c r="C57" s="177"/>
+      <c r="D57" s="185">
+        <v>700000</v>
+      </c>
+      <c r="E57" s="149">
+        <f t="shared" ref="E57" si="8">D57</f>
+        <v>700000</v>
+      </c>
+      <c r="F57" s="7"/>
+      <c r="G57" s="109">
+        <f t="shared" ref="G57" si="9">D57</f>
+        <v>700000</v>
+      </c>
+      <c r="H57" s="161">
+        <f t="shared" ref="H57" si="10">E57+F57</f>
+        <v>700000</v>
+      </c>
+      <c r="I57" s="178">
+        <f>H57-D57</f>
+        <v>0</v>
+      </c>
+      <c r="J57" s="178">
+        <f>G57-D57</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="190" t="s">
+        <v>137</v>
+      </c>
+      <c r="B58" s="176"/>
+      <c r="C58" s="177"/>
+      <c r="D58" s="113">
+        <v>330000</v>
+      </c>
+      <c r="E58" s="149">
+        <f>D58</f>
+        <v>330000</v>
+      </c>
+      <c r="F58" s="7"/>
+      <c r="G58" s="109">
+        <f>D58</f>
+        <v>330000</v>
+      </c>
+      <c r="H58" s="161">
+        <f>E58+F58</f>
+        <v>330000</v>
+      </c>
+      <c r="I58" s="178">
+        <f t="shared" ref="I58:I86" si="11">H58-D58</f>
+        <v>0</v>
+      </c>
+      <c r="J58" s="178">
+        <f t="shared" ref="J58:J86" si="12">G58-D58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="B59" s="163"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="113">
+        <v>143638</v>
+      </c>
+      <c r="E59" s="149">
+        <f t="shared" ref="E59:E63" si="13">D59*91.91%</f>
+        <v>132017.68579999998</v>
+      </c>
+      <c r="F59" s="134">
+        <f t="shared" ref="F59:F63" si="14">D59*8.09%</f>
+        <v>11620.314200000001</v>
+      </c>
+      <c r="G59" s="109">
+        <f t="shared" ref="G59:G86" si="15">D59</f>
+        <v>143638</v>
+      </c>
+      <c r="H59" s="161">
+        <f t="shared" ref="H59:H86" si="16">E59+F59</f>
+        <v>143637.99999999997</v>
+      </c>
+      <c r="I59" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="94" t="s">
+        <v>142</v>
+      </c>
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="113">
+        <v>129675</v>
+      </c>
+      <c r="E60" s="149">
+        <f t="shared" si="13"/>
+        <v>119184.2925</v>
+      </c>
+      <c r="F60" s="134">
+        <f t="shared" si="14"/>
+        <v>10490.7075</v>
+      </c>
+      <c r="G60" s="109">
+        <f t="shared" si="15"/>
+        <v>129675</v>
+      </c>
+      <c r="H60" s="161">
+        <f t="shared" si="16"/>
+        <v>129675</v>
+      </c>
+      <c r="I60" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C61" s="7"/>
+      <c r="D61" s="113">
+        <v>74622</v>
+      </c>
+      <c r="E61" s="149">
+        <f>D61*91.91%</f>
+        <v>68585.080199999997</v>
+      </c>
+      <c r="F61" s="134">
+        <f t="shared" si="14"/>
+        <v>6036.9197999999997</v>
+      </c>
+      <c r="G61" s="109">
+        <f t="shared" si="15"/>
+        <v>74622</v>
+      </c>
+      <c r="H61" s="161">
+        <f>E61+F61</f>
+        <v>74622</v>
+      </c>
+      <c r="I61" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="94" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" s="7"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="113"/>
+      <c r="E62" s="149">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="F62" s="134">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="G62" s="109">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="H62" s="161">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="I62" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J62" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="129" t="s">
+        <v>10</v>
+      </c>
+      <c r="B63" s="98" t="s">
+        <v>172</v>
+      </c>
+      <c r="C63" s="98"/>
+      <c r="D63" s="113">
+        <v>846331.1</v>
+      </c>
+      <c r="E63" s="149">
+        <f t="shared" si="13"/>
+        <v>777862.91400999995</v>
+      </c>
+      <c r="F63" s="134">
+        <f t="shared" si="14"/>
+        <v>68468.185989999998</v>
+      </c>
+      <c r="G63" s="109">
+        <f t="shared" si="15"/>
+        <v>846331.1</v>
+      </c>
+      <c r="H63" s="161">
+        <f t="shared" si="16"/>
+        <v>846331.1</v>
+      </c>
+      <c r="I63" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J63" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="98" t="s">
+        <v>153</v>
+      </c>
+      <c r="B64" s="179"/>
+      <c r="C64" s="180"/>
+      <c r="D64" s="113">
+        <v>235500</v>
+      </c>
+      <c r="E64" s="149">
+        <f t="shared" ref="E64:E76" si="17">D64</f>
+        <v>235500</v>
+      </c>
+      <c r="F64" s="134"/>
+      <c r="G64" s="109">
+        <f t="shared" si="15"/>
+        <v>235500</v>
+      </c>
+      <c r="H64" s="161">
+        <f t="shared" si="16"/>
+        <v>235500</v>
+      </c>
+      <c r="I64" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J64" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="213" t="s">
+        <v>168</v>
+      </c>
+      <c r="B65" s="214"/>
+      <c r="C65" s="215"/>
+      <c r="D65" s="113">
+        <v>111026</v>
+      </c>
+      <c r="E65" s="149">
+        <f>D65*91.91%</f>
+        <v>102043.99659999998</v>
+      </c>
+      <c r="F65" s="149">
+        <f>D65*8.09%</f>
+        <v>8982.0033999999996</v>
+      </c>
+      <c r="G65" s="109">
+        <f t="shared" si="15"/>
+        <v>111026</v>
+      </c>
+      <c r="H65" s="161">
+        <f>E65+F65</f>
+        <v>111025.99999999999</v>
+      </c>
+      <c r="I65" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J65" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="213" t="s">
         <v>163</v>
       </c>
-      <c r="B57" s="179"/>
-      <c r="C57" s="180"/>
-      <c r="D57" s="200">
-        <v>700000</v>
-      </c>
-      <c r="E57" s="115"/>
-      <c r="F57" s="7"/>
-      <c r="H57" s="150"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="114" t="s">
-        <v>167</v>
-      </c>
-      <c r="B58" s="179"/>
-      <c r="C58" s="180"/>
-      <c r="D58" s="200">
-        <v>300000</v>
-      </c>
-      <c r="E58" s="115"/>
-      <c r="F58" s="7"/>
-      <c r="H58" s="150"/>
-    </row>
-    <row r="59" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="195" t="s">
-        <v>141</v>
-      </c>
-      <c r="B59" s="179"/>
-      <c r="C59" s="180"/>
-      <c r="D59" s="199">
-        <v>330000</v>
-      </c>
-      <c r="E59" s="149">
-        <f>D59</f>
-        <v>330000</v>
-      </c>
-      <c r="F59" s="7"/>
-      <c r="G59" s="109">
-        <f>D59</f>
-        <v>330000</v>
-      </c>
-      <c r="H59" s="161">
-        <f>E59+F59</f>
-        <v>330000</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="121" t="s">
-        <v>8</v>
-      </c>
-      <c r="B60" s="164"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="198">
-        <v>118708.63</v>
-      </c>
-      <c r="E60" s="149">
-        <f t="shared" ref="E60:E65" si="8">D60*91.91%</f>
-        <v>109105.10183299999</v>
-      </c>
-      <c r="F60" s="134">
-        <f t="shared" ref="F60:F65" si="9">D60*8.09%</f>
-        <v>9603.5281670000004</v>
-      </c>
-      <c r="G60" s="109">
-        <f t="shared" ref="G60:G85" si="10">D60</f>
-        <v>118708.63</v>
-      </c>
-      <c r="H60" s="161">
-        <f t="shared" ref="H60:H85" si="11">E60+F60</f>
-        <v>118708.62999999999</v>
-      </c>
-      <c r="I60" t="str">
-        <f t="shared" ref="I60:I84" si="12">IF(G60=H60, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="94" t="s">
-        <v>154</v>
-      </c>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="198">
-        <v>129675</v>
-      </c>
-      <c r="E61" s="149">
-        <f t="shared" si="8"/>
-        <v>119184.2925</v>
-      </c>
-      <c r="F61" s="134">
-        <f t="shared" si="9"/>
-        <v>10490.7075</v>
-      </c>
-      <c r="G61" s="109">
-        <f t="shared" si="10"/>
-        <v>129675</v>
-      </c>
-      <c r="H61" s="161">
+      <c r="B66" s="214"/>
+      <c r="C66" s="215"/>
+      <c r="D66" s="113">
+        <v>104006.06</v>
+      </c>
+      <c r="E66" s="149">
+        <f t="shared" ref="E66:E73" si="18">D66*91.91%</f>
+        <v>95591.969745999988</v>
+      </c>
+      <c r="F66" s="149">
+        <f t="shared" ref="F66:F73" si="19">D66*8.09%</f>
+        <v>8414.0902540000006</v>
+      </c>
+      <c r="G66" s="109">
+        <f>D66</f>
+        <v>104006.06</v>
+      </c>
+      <c r="H66" s="161">
+        <f t="shared" si="16"/>
+        <v>104006.05999999998</v>
+      </c>
+      <c r="I66" s="178">
         <f t="shared" si="11"/>
-        <v>129675</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="94" t="s">
-        <v>9</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="113">
-        <v>74622</v>
-      </c>
-      <c r="E62" s="149">
-        <f t="shared" si="8"/>
-        <v>68585.080199999997</v>
-      </c>
-      <c r="F62" s="134">
-        <f t="shared" si="9"/>
-        <v>6036.9197999999997</v>
-      </c>
-      <c r="G62" s="109">
-        <f t="shared" si="10"/>
-        <v>74622</v>
-      </c>
-      <c r="H62" s="161">
-        <f t="shared" si="11"/>
-        <v>74622</v>
-      </c>
-      <c r="I62" t="str">
+        <v>0</v>
+      </c>
+      <c r="J66" s="178">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="94" t="s">
-        <v>11</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C63" s="7"/>
-      <c r="D63" s="113">
-        <f>314851+309690.68</f>
-        <v>624541.67999999993</v>
-      </c>
-      <c r="E63" s="149">
-        <f t="shared" si="8"/>
-        <v>574016.25808799989</v>
-      </c>
-      <c r="F63" s="134">
-        <f t="shared" si="9"/>
-        <v>50525.421911999998</v>
-      </c>
-      <c r="G63" s="109">
-        <f t="shared" si="10"/>
-        <v>624541.67999999993</v>
-      </c>
-      <c r="H63" s="161"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="129" t="s">
-        <v>10</v>
-      </c>
-      <c r="B64" s="98" t="s">
-        <v>142</v>
-      </c>
-      <c r="C64" s="98"/>
-      <c r="D64" s="198">
-        <v>909788.31</v>
-      </c>
-      <c r="E64" s="149">
-        <f t="shared" si="8"/>
-        <v>836186.43572099996</v>
-      </c>
-      <c r="F64" s="134">
-        <f t="shared" si="9"/>
-        <v>73601.874279000011</v>
-      </c>
-      <c r="G64" s="109">
-        <f t="shared" si="10"/>
-        <v>909788.31</v>
-      </c>
-      <c r="H64" s="161">
-        <f t="shared" si="11"/>
-        <v>909788.30999999994</v>
-      </c>
-      <c r="I64" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="129" t="s">
-        <v>145</v>
-      </c>
-      <c r="B65" s="98"/>
-      <c r="C65" s="98"/>
-      <c r="D65" s="113">
-        <v>40000</v>
-      </c>
-      <c r="E65" s="149">
-        <f t="shared" si="8"/>
-        <v>36764</v>
-      </c>
-      <c r="F65" s="134">
-        <f t="shared" si="9"/>
-        <v>3236</v>
-      </c>
-      <c r="G65" s="109">
-        <f t="shared" si="10"/>
-        <v>40000</v>
-      </c>
-      <c r="H65" s="161">
-        <f t="shared" si="11"/>
-        <v>40000</v>
-      </c>
-      <c r="I65" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="98" t="s">
-        <v>168</v>
-      </c>
-      <c r="B66" s="183"/>
-      <c r="C66" s="184"/>
-      <c r="D66" s="198">
-        <v>235500</v>
-      </c>
-      <c r="E66" s="149">
-        <f t="shared" ref="E66:E78" si="13">D66</f>
-        <v>235500</v>
-      </c>
-      <c r="F66" s="134"/>
-      <c r="G66" s="109">
-        <f t="shared" si="10"/>
-        <v>235500</v>
-      </c>
-      <c r="H66" s="161">
-        <f t="shared" si="11"/>
-        <v>235500</v>
-      </c>
-      <c r="I66" s="181"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="218" t="s">
-        <v>157</v>
-      </c>
-      <c r="B67" s="219"/>
-      <c r="C67" s="220"/>
-      <c r="D67" s="198">
-        <v>111026</v>
-      </c>
-      <c r="E67" s="149">
-        <f t="shared" si="13"/>
-        <v>111026</v>
-      </c>
-      <c r="F67" s="134"/>
-      <c r="G67" s="109">
-        <f t="shared" si="10"/>
-        <v>111026</v>
-      </c>
-      <c r="H67" s="161">
-        <f t="shared" si="11"/>
-        <v>111026</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="218" t="s">
-        <v>160</v>
-      </c>
-      <c r="B68" s="219"/>
-      <c r="C68" s="220"/>
-      <c r="D68" s="198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="213" t="s">
+        <v>163</v>
+      </c>
+      <c r="B67" s="214"/>
+      <c r="C67" s="215"/>
+      <c r="D67" s="113">
         <f>104002.96</f>
         <v>104002.96</v>
       </c>
-      <c r="E68" s="149">
-        <f t="shared" si="13"/>
+      <c r="E67" s="149">
+        <f t="shared" si="18"/>
+        <v>95589.120536000002</v>
+      </c>
+      <c r="F67" s="149">
+        <f t="shared" si="19"/>
+        <v>8413.8394640000006</v>
+      </c>
+      <c r="G67" s="109">
+        <f t="shared" ref="G67:G73" si="20">D67</f>
         <v>104002.96</v>
       </c>
-      <c r="F68" s="134"/>
-      <c r="G68" s="109">
-        <f>D68</f>
+      <c r="H67" s="161">
+        <f t="shared" si="16"/>
         <v>104002.96</v>
       </c>
-      <c r="H68" s="161">
+      <c r="I67" s="178">
         <f t="shared" si="11"/>
-        <v>104002.96</v>
-      </c>
-      <c r="I68" t="str">
-        <f>IF(G68=H68, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="218" t="s">
-        <v>160</v>
-      </c>
-      <c r="B69" s="219"/>
-      <c r="C69" s="220"/>
-      <c r="D69" s="198">
+        <v>0</v>
+      </c>
+      <c r="J67" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="213" t="s">
+        <v>163</v>
+      </c>
+      <c r="B68" s="214"/>
+      <c r="C68" s="215"/>
+      <c r="D68" s="113">
         <f>104002.96</f>
         <v>104002.96</v>
       </c>
-      <c r="E69" s="149">
-        <f t="shared" si="13"/>
+      <c r="E68" s="149">
+        <f t="shared" si="18"/>
+        <v>95589.120536000002</v>
+      </c>
+      <c r="F68" s="149">
+        <f t="shared" si="19"/>
+        <v>8413.8394640000006</v>
+      </c>
+      <c r="G68" s="109">
+        <f t="shared" si="20"/>
         <v>104002.96</v>
       </c>
-      <c r="F69" s="134"/>
-      <c r="G69" s="109"/>
-      <c r="H69" s="161"/>
-    </row>
-    <row r="70" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="218" t="s">
-        <v>160</v>
-      </c>
-      <c r="B70" s="219"/>
-      <c r="C70" s="220"/>
-      <c r="D70" s="198">
+      <c r="H68" s="161">
+        <f t="shared" si="16"/>
+        <v>104002.96</v>
+      </c>
+      <c r="I68" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J68" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="213" t="s">
+        <v>163</v>
+      </c>
+      <c r="B69" s="214"/>
+      <c r="C69" s="215"/>
+      <c r="D69" s="113">
         <f>104002.96</f>
         <v>104002.96</v>
       </c>
+      <c r="E69" s="149">
+        <f t="shared" si="18"/>
+        <v>95589.120536000002</v>
+      </c>
+      <c r="F69" s="149">
+        <f t="shared" si="19"/>
+        <v>8413.8394640000006</v>
+      </c>
+      <c r="G69" s="109">
+        <f t="shared" si="20"/>
+        <v>104002.96</v>
+      </c>
+      <c r="H69" s="161">
+        <f t="shared" si="16"/>
+        <v>104002.96</v>
+      </c>
+      <c r="I69" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J69" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="227" t="s">
+        <v>162</v>
+      </c>
+      <c r="B70" s="228"/>
+      <c r="C70" s="229"/>
+      <c r="D70" s="113">
+        <v>100419.01</v>
+      </c>
       <c r="E70" s="149">
-        <f t="shared" si="13"/>
-        <v>104002.96</v>
-      </c>
-      <c r="F70" s="134"/>
-      <c r="G70" s="109"/>
-      <c r="H70" s="161"/>
-    </row>
-    <row r="71" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="218" t="s">
-        <v>160</v>
-      </c>
-      <c r="B71" s="219"/>
-      <c r="C71" s="220"/>
-      <c r="D71" s="198">
-        <f>104002.96</f>
-        <v>104002.96</v>
+        <f t="shared" si="18"/>
+        <v>92295.112090999988</v>
+      </c>
+      <c r="F70" s="149">
+        <f t="shared" si="19"/>
+        <v>8123.8979089999993</v>
+      </c>
+      <c r="G70" s="109">
+        <f t="shared" si="20"/>
+        <v>100419.01</v>
+      </c>
+      <c r="H70" s="161">
+        <f t="shared" si="16"/>
+        <v>100419.00999999998</v>
+      </c>
+      <c r="I70" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J70" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="227" t="s">
+        <v>162</v>
+      </c>
+      <c r="B71" s="228"/>
+      <c r="C71" s="229"/>
+      <c r="D71" s="113">
+        <v>97003.05</v>
       </c>
       <c r="E71" s="149">
-        <f t="shared" si="13"/>
-        <v>104002.96</v>
-      </c>
-      <c r="F71" s="134"/>
-      <c r="G71" s="109"/>
-      <c r="H71" s="161"/>
-    </row>
-    <row r="72" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="201" t="s">
-        <v>166</v>
-      </c>
-      <c r="B72" s="175"/>
-      <c r="C72" s="202"/>
-      <c r="D72" s="198">
-        <v>100419.01</v>
-      </c>
-      <c r="E72" s="149"/>
-      <c r="F72" s="134"/>
-      <c r="G72" s="109"/>
-      <c r="H72" s="161"/>
-    </row>
-    <row r="73" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="201" t="s">
-        <v>166</v>
-      </c>
-      <c r="B73" s="175"/>
-      <c r="C73" s="202"/>
-      <c r="D73" s="198">
+        <f t="shared" si="18"/>
+        <v>89155.503254999989</v>
+      </c>
+      <c r="F71" s="149">
+        <f t="shared" si="19"/>
+        <v>7847.5467450000006</v>
+      </c>
+      <c r="G71" s="109">
+        <f t="shared" si="20"/>
         <v>97003.05</v>
       </c>
-      <c r="E73" s="149"/>
-      <c r="F73" s="134"/>
-      <c r="G73" s="109"/>
-      <c r="H73" s="161"/>
-    </row>
-    <row r="74" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="229" t="s">
-        <v>150</v>
-      </c>
-      <c r="B74" s="230"/>
-      <c r="C74" s="231"/>
-      <c r="D74" s="198">
-        <v>6000</v>
+      <c r="H71" s="161">
+        <f t="shared" si="16"/>
+        <v>97003.049999999988</v>
+      </c>
+      <c r="I71" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J71" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="227" t="s">
+        <v>161</v>
+      </c>
+      <c r="B72" s="228"/>
+      <c r="C72" s="229"/>
+      <c r="D72" s="113">
+        <v>98393.96</v>
+      </c>
+      <c r="E72" s="149">
+        <f t="shared" si="18"/>
+        <v>90433.888636000003</v>
+      </c>
+      <c r="F72" s="149">
+        <f t="shared" si="19"/>
+        <v>7960.0713640000004</v>
+      </c>
+      <c r="G72" s="109">
+        <f t="shared" si="20"/>
+        <v>98393.96</v>
+      </c>
+      <c r="H72" s="161">
+        <f t="shared" si="16"/>
+        <v>98393.96</v>
+      </c>
+      <c r="I72" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J72" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="197" t="s">
+        <v>171</v>
+      </c>
+      <c r="B73" s="195"/>
+      <c r="C73" s="196"/>
+      <c r="D73" s="113">
+        <v>99259.05</v>
+      </c>
+      <c r="E73" s="149">
+        <f t="shared" si="18"/>
+        <v>91228.99285499999</v>
+      </c>
+      <c r="F73" s="149">
+        <f t="shared" si="19"/>
+        <v>8030.0571449999998</v>
+      </c>
+      <c r="G73" s="109">
+        <f t="shared" si="20"/>
+        <v>99259.05</v>
+      </c>
+      <c r="H73" s="161">
+        <f t="shared" si="16"/>
+        <v>99259.049999999988</v>
+      </c>
+      <c r="I73" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J73" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="224" t="s">
+        <v>151</v>
+      </c>
+      <c r="B74" s="225"/>
+      <c r="C74" s="226"/>
+      <c r="D74" s="113">
+        <v>66000</v>
       </c>
       <c r="E74" s="149">
-        <f t="shared" si="13"/>
-        <v>6000</v>
+        <f t="shared" si="17"/>
+        <v>66000</v>
       </c>
       <c r="F74" s="134"/>
       <c r="G74" s="109">
-        <f>D74</f>
-        <v>6000</v>
+        <f t="shared" si="15"/>
+        <v>66000</v>
       </c>
       <c r="H74" s="161">
+        <f t="shared" si="16"/>
+        <v>66000</v>
+      </c>
+      <c r="I74" s="178">
         <f t="shared" si="11"/>
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="229" t="s">
-        <v>165</v>
-      </c>
-      <c r="B75" s="230"/>
-      <c r="C75" s="231"/>
-      <c r="D75" s="198">
-        <v>7000</v>
+        <v>0</v>
+      </c>
+      <c r="J74" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="230" t="s">
+        <v>157</v>
+      </c>
+      <c r="B75" s="231"/>
+      <c r="C75" s="232"/>
+      <c r="D75" s="113">
+        <v>218400</v>
       </c>
       <c r="E75" s="149">
-        <f t="shared" si="13"/>
-        <v>7000</v>
+        <f t="shared" si="17"/>
+        <v>218400</v>
       </c>
       <c r="F75" s="134"/>
-      <c r="G75" s="109"/>
-      <c r="H75" s="161"/>
-    </row>
-    <row r="76" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="203"/>
-      <c r="B76" s="193"/>
-      <c r="C76" s="194"/>
-      <c r="D76" s="198">
-        <v>98393.96</v>
+      <c r="G75" s="109">
+        <f t="shared" si="15"/>
+        <v>218400</v>
+      </c>
+      <c r="H75" s="161">
+        <f t="shared" si="16"/>
+        <v>218400</v>
+      </c>
+      <c r="I75" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J75" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="193" t="s">
+        <v>154</v>
+      </c>
+      <c r="B76" s="194"/>
+      <c r="C76" s="189"/>
+      <c r="D76" s="113">
+        <v>35000</v>
       </c>
       <c r="E76" s="149">
-        <f t="shared" si="13"/>
-        <v>98393.96</v>
+        <f t="shared" si="17"/>
+        <v>35000</v>
       </c>
       <c r="F76" s="134"/>
       <c r="G76" s="109">
-        <f>D76</f>
-        <v>98393.96</v>
+        <f t="shared" si="15"/>
+        <v>35000</v>
       </c>
       <c r="H76" s="161">
+        <f t="shared" si="16"/>
+        <v>35000</v>
+      </c>
+      <c r="I76" s="178">
         <f t="shared" si="11"/>
-        <v>98393.96</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A77" s="229" t="s">
-        <v>147</v>
-      </c>
-      <c r="B77" s="230"/>
-      <c r="C77" s="231"/>
-      <c r="D77" s="198">
-        <v>66000</v>
+        <v>0</v>
+      </c>
+      <c r="J76" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C77" s="7"/>
+      <c r="D77" s="113">
+        <v>79895</v>
       </c>
       <c r="E77" s="149">
-        <f t="shared" si="13"/>
-        <v>66000</v>
-      </c>
-      <c r="F77" s="134"/>
+        <f t="shared" ref="E77:E84" si="21">D77</f>
+        <v>79895</v>
+      </c>
+      <c r="F77" s="7"/>
       <c r="G77" s="109">
-        <f t="shared" si="10"/>
-        <v>66000</v>
+        <f t="shared" si="15"/>
+        <v>79895</v>
       </c>
       <c r="H77" s="161">
+        <f t="shared" si="16"/>
+        <v>79895</v>
+      </c>
+      <c r="I77" s="178">
         <f t="shared" si="11"/>
-        <v>66000</v>
-      </c>
-      <c r="I77" t="str">
+        <v>0</v>
+      </c>
+      <c r="J77" s="178">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="232" t="s">
-        <v>164</v>
-      </c>
-      <c r="B78" s="233"/>
-      <c r="C78" s="194"/>
-      <c r="D78" s="198">
-        <v>218400</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="94" t="s">
+        <v>145</v>
+      </c>
+      <c r="B78" s="7"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="113">
+        <v>6530.7</v>
       </c>
       <c r="E78" s="149">
-        <f t="shared" si="13"/>
-        <v>218400</v>
-      </c>
-      <c r="F78" s="134"/>
-      <c r="G78" s="109"/>
-      <c r="H78" s="161"/>
-    </row>
-    <row r="79" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>161</v>
-      </c>
+        <f t="shared" ref="E78:E82" si="22">D78*91.91%</f>
+        <v>6002.3663699999997</v>
+      </c>
+      <c r="F78" s="134">
+        <f t="shared" ref="F78:F82" si="23">D78*8.09%</f>
+        <v>528.33362999999997</v>
+      </c>
+      <c r="G78" s="109">
+        <f t="shared" si="15"/>
+        <v>6530.7</v>
+      </c>
+      <c r="H78" s="161">
+        <f t="shared" si="16"/>
+        <v>6530.7</v>
+      </c>
+      <c r="I78" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J78" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="94" t="s">
+        <v>156</v>
+      </c>
+      <c r="B79" s="7"/>
       <c r="C79" s="7"/>
-      <c r="D79" s="198">
-        <v>79895</v>
+      <c r="D79" s="113">
+        <v>220000</v>
       </c>
       <c r="E79" s="149">
-        <f t="shared" ref="E79:E85" si="14">D79</f>
-        <v>79895</v>
-      </c>
-      <c r="F79" s="7"/>
+        <f t="shared" si="22"/>
+        <v>202201.99999999997</v>
+      </c>
+      <c r="F79" s="134">
+        <f t="shared" si="23"/>
+        <v>17798</v>
+      </c>
       <c r="G79" s="109">
-        <f t="shared" si="10"/>
-        <v>79895</v>
+        <f t="shared" si="15"/>
+        <v>220000</v>
       </c>
       <c r="H79" s="161">
-        <f t="shared" si="11"/>
-        <v>79895</v>
-      </c>
-      <c r="I79" t="str">
+        <f t="shared" si="16"/>
+        <v>219999.99999999997</v>
+      </c>
+      <c r="I79" s="178">
+        <f>H79-D79</f>
+        <v>0</v>
+      </c>
+      <c r="J79" s="178">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="94" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
-      <c r="D80" s="198">
-        <v>6530.7</v>
+      <c r="D80" s="113">
+        <v>150000</v>
       </c>
       <c r="E80" s="149">
-        <f t="shared" ref="E80" si="15">D80*91.91%</f>
-        <v>6002.3663699999997</v>
+        <f t="shared" si="22"/>
+        <v>137865</v>
       </c>
       <c r="F80" s="134">
-        <f t="shared" ref="F80" si="16">D80*8.09%</f>
-        <v>528.33362999999997</v>
+        <f t="shared" si="23"/>
+        <v>12135</v>
       </c>
       <c r="G80" s="109">
-        <f t="shared" si="10"/>
-        <v>6530.7</v>
+        <f t="shared" si="15"/>
+        <v>150000</v>
       </c>
       <c r="H80" s="161">
+        <f t="shared" si="16"/>
+        <v>150000</v>
+      </c>
+      <c r="I80" s="178">
         <f t="shared" si="11"/>
-        <v>6530.7</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J80" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
-      <c r="D81" s="198">
-        <v>10391.24</v>
+      <c r="D81" s="113">
+        <v>120000</v>
       </c>
       <c r="E81" s="149">
-        <f t="shared" si="14"/>
-        <v>10391.24</v>
+        <f t="shared" si="21"/>
+        <v>120000</v>
       </c>
       <c r="F81" s="7"/>
       <c r="G81" s="109">
-        <f t="shared" si="10"/>
-        <v>10391.24</v>
-      </c>
-      <c r="H81" s="161"/>
-    </row>
-    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="B82" s="7"/>
+        <f t="shared" si="15"/>
+        <v>120000</v>
+      </c>
+      <c r="H81" s="161">
+        <f t="shared" si="16"/>
+        <v>120000</v>
+      </c>
+      <c r="I81" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J81" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="94" t="s">
+        <v>158</v>
+      </c>
+      <c r="B82" s="114"/>
       <c r="C82" s="7"/>
-      <c r="D82" s="198">
-        <v>150000</v>
+      <c r="D82" s="113">
+        <v>245000</v>
       </c>
       <c r="E82" s="149">
-        <f t="shared" si="14"/>
-        <v>150000</v>
-      </c>
-      <c r="F82" s="7"/>
+        <f t="shared" si="22"/>
+        <v>225179.49999999997</v>
+      </c>
+      <c r="F82" s="134">
+        <f t="shared" si="23"/>
+        <v>19820.5</v>
+      </c>
       <c r="G82" s="109">
-        <f t="shared" si="10"/>
-        <v>150000</v>
-      </c>
-      <c r="H82" s="161"/>
-    </row>
-    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="15"/>
+        <v>245000</v>
+      </c>
+      <c r="H82" s="161">
+        <f t="shared" si="16"/>
+        <v>244999.99999999997</v>
+      </c>
+      <c r="I82" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J82" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B83" s="7"/>
+        <v>148</v>
+      </c>
+      <c r="B83" s="114"/>
       <c r="C83" s="7"/>
-      <c r="D83" s="198">
+      <c r="D83" s="113">
         <v>120000</v>
       </c>
       <c r="E83" s="149">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>120000</v>
       </c>
       <c r="F83" s="7"/>
       <c r="G83" s="109">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>120000</v>
       </c>
-      <c r="H83" s="161"/>
-    </row>
-    <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="98" t="s">
-        <v>159</v>
+      <c r="H83" s="161">
+        <f t="shared" si="16"/>
+        <v>120000</v>
+      </c>
+      <c r="I83" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J83" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="7" t="s">
+        <v>170</v>
       </c>
       <c r="B84" s="114"/>
-      <c r="C84" s="163"/>
-      <c r="D84" s="198">
-        <v>80000</v>
+      <c r="C84" s="7"/>
+      <c r="D84" s="113">
+        <v>480000</v>
       </c>
       <c r="E84" s="149">
-        <f t="shared" si="14"/>
-        <v>80000</v>
-      </c>
-      <c r="F84" s="134"/>
+        <f t="shared" si="21"/>
+        <v>480000</v>
+      </c>
+      <c r="F84" s="7"/>
       <c r="G84" s="109">
-        <f t="shared" si="10"/>
-        <v>80000</v>
+        <f t="shared" si="15"/>
+        <v>480000</v>
       </c>
       <c r="H84" s="161">
+        <f t="shared" si="16"/>
+        <v>480000</v>
+      </c>
+      <c r="I84" s="178">
         <f t="shared" si="11"/>
-        <v>80000</v>
-      </c>
-      <c r="I84" t="str">
+        <v>0</v>
+      </c>
+      <c r="J84" s="178">
         <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="94" t="s">
+        <v>173</v>
+      </c>
+      <c r="B85" s="114"/>
+      <c r="C85" s="7"/>
+      <c r="D85" s="113">
+        <v>250000</v>
+      </c>
+      <c r="E85" s="149">
+        <f t="shared" ref="E85:E86" si="24">D85*91.91%</f>
+        <v>229774.99999999997</v>
+      </c>
+      <c r="F85" s="134">
+        <f t="shared" ref="F85:F86" si="25">D85*8.09%</f>
+        <v>20225</v>
+      </c>
+      <c r="G85" s="109">
+        <f t="shared" si="15"/>
+        <v>250000</v>
+      </c>
+      <c r="H85" s="161"/>
+      <c r="I85" s="178"/>
+      <c r="J85" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="129" t="s">
+        <v>164</v>
+      </c>
+      <c r="B86" s="114"/>
+      <c r="C86" s="162"/>
+      <c r="D86" s="113">
+        <v>50000</v>
+      </c>
+      <c r="E86" s="149">
+        <f t="shared" si="24"/>
+        <v>45954.999999999993</v>
+      </c>
+      <c r="F86" s="134">
+        <f t="shared" si="25"/>
+        <v>4045</v>
+      </c>
+      <c r="G86" s="109">
+        <f t="shared" si="15"/>
+        <v>50000</v>
+      </c>
+      <c r="H86" s="161">
+        <f t="shared" si="16"/>
+        <v>49999.999999999993</v>
+      </c>
+      <c r="I86" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J86" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="155"/>
+      <c r="B87" s="156"/>
+      <c r="C87" s="156"/>
+      <c r="D87" s="166"/>
+      <c r="E87" s="149"/>
+      <c r="F87" s="134"/>
+      <c r="G87" s="109"/>
+      <c r="H87" s="161"/>
+      <c r="I87" t="str">
+        <f>IF(G87=H87, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A85" s="155"/>
-      <c r="B85" s="156"/>
-      <c r="C85" s="156"/>
-      <c r="D85" s="167"/>
-      <c r="E85" s="149">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="F85" s="134"/>
-      <c r="G85" s="109">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="H85" s="161">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I85" t="str">
-        <f>IF(G85=H85, "", "Error")</f>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="96" t="s">
+        <v>12</v>
+      </c>
+      <c r="B88" s="96"/>
+      <c r="C88" s="96"/>
+      <c r="D88" s="108">
+        <f>SUM(D57:D87)</f>
+        <v>5422707.8099999996</v>
+      </c>
+      <c r="E88" s="108">
+        <f>SUM(E57:E87)</f>
+        <v>5176940.6636709999</v>
+      </c>
+      <c r="F88" s="108">
+        <f>SUM(F57:F87)</f>
+        <v>245767.14632900001</v>
+      </c>
+      <c r="G88" s="109">
+        <f>E88+F88</f>
+        <v>5422707.8099999996</v>
+      </c>
+      <c r="H88" s="150" t="str">
+        <f>IF(D88=G88, "", "Error")</f>
         <v/>
       </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A86" s="96" t="s">
-        <v>12</v>
-      </c>
-      <c r="B86" s="96"/>
-      <c r="C86" s="96"/>
-      <c r="D86" s="108">
-        <f>SUM(D60:D85)</f>
-        <v>3699906.42</v>
-      </c>
-      <c r="E86" s="108">
-        <f>SUM(E60:E85)</f>
-        <v>3348461.5747119999</v>
-      </c>
-      <c r="F86" s="108">
-        <f>SUM(F60:F85)</f>
-        <v>154022.78528800001</v>
-      </c>
-      <c r="G86" s="109">
-        <f>E86+F86</f>
-        <v>3502484.36</v>
-      </c>
-      <c r="H86" s="150" t="str">
-        <f>IF(D86=G86, "", "Error")</f>
-        <v>Error</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="7"/>
-      <c r="B87" s="7"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="189"/>
-      <c r="E87" s="115"/>
-      <c r="F87" s="7"/>
-      <c r="H87" s="150"/>
-    </row>
-    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="7"/>
-      <c r="B88" s="7"/>
-      <c r="C88" s="7"/>
-      <c r="D88" s="189"/>
-      <c r="E88" s="114"/>
-      <c r="F88" s="7"/>
-      <c r="H88" s="150"/>
-    </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I88" s="178">
+        <f>D88-G88</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
-      <c r="D89" s="189"/>
-      <c r="E89" s="114"/>
+      <c r="D89" s="185"/>
+      <c r="E89" s="115"/>
       <c r="F89" s="7"/>
       <c r="H89" s="150"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A90" s="94" t="s">
-        <v>146</v>
-      </c>
-      <c r="B90" s="98"/>
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="7"/>
+      <c r="B90" s="7"/>
       <c r="C90" s="7"/>
-      <c r="D90" s="113">
-        <v>186900</v>
-      </c>
-      <c r="E90" s="149">
-        <f>D90*91.91%</f>
-        <v>171779.78999999998</v>
-      </c>
-      <c r="F90" s="134">
-        <f>D90*8.09%</f>
-        <v>15120.21</v>
-      </c>
-      <c r="G90" s="160"/>
+      <c r="D90" s="185"/>
+      <c r="E90" s="114"/>
+      <c r="F90" s="7"/>
       <c r="H90" s="150"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A91" s="98"/>
-      <c r="B91" s="162"/>
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="7"/>
+      <c r="B91" s="7"/>
       <c r="C91" s="7"/>
-      <c r="D91" s="113"/>
-      <c r="E91" s="149">
-        <f>D91</f>
-        <v>0</v>
-      </c>
-      <c r="F91" s="134"/>
+      <c r="D91" s="185"/>
+      <c r="E91" s="114"/>
+      <c r="F91" s="7"/>
       <c r="H91" s="150"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A92" s="7"/>
-      <c r="B92" s="7"/>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" s="94" t="s">
+        <v>167</v>
+      </c>
+      <c r="B92" s="98"/>
       <c r="C92" s="7"/>
       <c r="D92" s="113"/>
-      <c r="E92" s="165">
-        <f>D92</f>
-        <v>0</v>
-      </c>
-      <c r="F92" s="7"/>
+      <c r="E92" s="149">
+        <f>D92*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F92" s="134">
+        <f>D92*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="G92" s="160"/>
       <c r="H92" s="150"/>
-      <c r="I92" s="109"/>
-    </row>
-    <row r="93" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="95" t="s">
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" s="7"/>
+      <c r="B93" s="7"/>
+      <c r="C93" s="7"/>
+      <c r="D93" s="113"/>
+      <c r="E93" s="164">
+        <f>D93</f>
+        <v>0</v>
+      </c>
+      <c r="F93" s="7"/>
+      <c r="H93" s="150"/>
+      <c r="I93" s="109"/>
+    </row>
+    <row r="94" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="B93" s="95"/>
-      <c r="C93" s="95"/>
-      <c r="D93" s="107">
-        <f>SUM(D90:D92)</f>
-        <v>186900</v>
-      </c>
-      <c r="E93" s="107">
-        <f>SUM(E90:E92)</f>
-        <v>171779.78999999998</v>
-      </c>
-      <c r="F93" s="107">
-        <f>SUM(F90:F92)</f>
-        <v>15120.21</v>
-      </c>
-      <c r="G93" s="109">
-        <f>E93+F93</f>
-        <v>186899.99999999997</v>
-      </c>
-      <c r="H93" s="150" t="str">
-        <f>IF(D93=G93, "", "Error")</f>
+      <c r="B94" s="95"/>
+      <c r="C94" s="95"/>
+      <c r="D94" s="107">
+        <f>SUM(D92:D93)</f>
+        <v>0</v>
+      </c>
+      <c r="E94" s="107">
+        <f>SUM(E92:E93)</f>
+        <v>0</v>
+      </c>
+      <c r="F94" s="107">
+        <f>SUM(F92:F93)</f>
+        <v>0</v>
+      </c>
+      <c r="G94" s="109">
+        <f>E94+F94</f>
+        <v>0</v>
+      </c>
+      <c r="H94" s="150" t="str">
+        <f>IF(D94=G94, "", "Error")</f>
         <v/>
       </c>
-      <c r="J93" s="109"/>
-    </row>
-    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="7"/>
-      <c r="B94" s="7"/>
-      <c r="C94" s="7"/>
-      <c r="D94" s="189"/>
-      <c r="E94" s="115"/>
-      <c r="F94" s="7"/>
-      <c r="H94" s="150"/>
-    </row>
-    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="J94" s="109"/>
+    </row>
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="7"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
-      <c r="D95" s="189"/>
-      <c r="E95" s="114"/>
+      <c r="D95" s="185"/>
+      <c r="E95" s="115"/>
       <c r="F95" s="7"/>
       <c r="H95" s="150"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A96" s="94" t="s">
-        <v>13</v>
-      </c>
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
-      <c r="D96" s="189"/>
+      <c r="D96" s="185"/>
       <c r="E96" s="114"/>
       <c r="F96" s="7"/>
       <c r="H96" s="150"/>
     </row>
-    <row r="97" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="94" t="s">
+        <v>13</v>
+      </c>
+      <c r="B97" s="7"/>
+      <c r="C97" s="7"/>
+      <c r="D97" s="185"/>
+      <c r="E97" s="114"/>
+      <c r="F97" s="7"/>
+      <c r="H97" s="150"/>
+    </row>
+    <row r="98" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="B97" s="7" t="s">
+      <c r="B98" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C97" s="7"/>
-      <c r="D97" s="198">
+      <c r="C98" s="7"/>
+      <c r="D98" s="113">
         <v>222264.92</v>
-      </c>
-      <c r="E97" s="149">
-        <f>D97*91.91%</f>
-        <v>204283.68797199999</v>
-      </c>
-      <c r="F97" s="134">
-        <f>D97*8.09%</f>
-        <v>17981.232028000002</v>
-      </c>
-      <c r="H97" s="150"/>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A98" s="94" t="s">
-        <v>108</v>
-      </c>
-      <c r="B98" s="7"/>
-      <c r="C98" s="7"/>
-      <c r="D98" s="198">
-        <v>28000</v>
       </c>
       <c r="E98" s="149">
         <f>D98*91.91%</f>
-        <v>25734.799999999999</v>
+        <v>204283.68797199999</v>
       </c>
       <c r="F98" s="134">
         <f>D98*8.09%</f>
-        <v>2265.1999999999998</v>
+        <v>17981.232028000002</v>
       </c>
       <c r="H98" s="150"/>
-      <c r="J98" s="113"/>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A99" s="7"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="94" t="s">
+        <v>108</v>
+      </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
-      <c r="D99" s="189"/>
-      <c r="E99" s="116"/>
-      <c r="F99" s="7"/>
+      <c r="D99" s="113">
+        <v>28000</v>
+      </c>
+      <c r="E99" s="149">
+        <f>D99*91.91%</f>
+        <v>25734.799999999999</v>
+      </c>
+      <c r="F99" s="134">
+        <f>D99*8.09%</f>
+        <v>2265.1999999999998</v>
+      </c>
       <c r="H99" s="150"/>
-      <c r="J99" s="109"/>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A100" s="95" t="s">
+      <c r="J99" s="113"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" s="7"/>
+      <c r="B100" s="7"/>
+      <c r="C100" s="7"/>
+      <c r="D100" s="185"/>
+      <c r="E100" s="116"/>
+      <c r="F100" s="7"/>
+      <c r="H100" s="150"/>
+      <c r="J100" s="109"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="B100" s="95"/>
-      <c r="C100" s="95"/>
-      <c r="D100" s="107">
-        <f>SUM(D97:D99)</f>
+      <c r="B101" s="95"/>
+      <c r="C101" s="95"/>
+      <c r="D101" s="107">
+        <f>SUM(D98:D100)</f>
         <v>250264.92</v>
       </c>
-      <c r="E100" s="107">
-        <f>SUM(E97:E99)</f>
+      <c r="E101" s="107">
+        <f>SUM(E98:E100)</f>
         <v>230018.48797199997</v>
       </c>
-      <c r="F100" s="107">
-        <f>SUM(F97:F99)</f>
+      <c r="F101" s="107">
+        <f>SUM(F98:F100)</f>
         <v>20246.432028000003</v>
       </c>
-      <c r="G100" s="109">
-        <f>E100+F100</f>
+      <c r="G101" s="109">
+        <f>E101+F101</f>
         <v>250264.91999999998</v>
       </c>
-      <c r="H100" s="150" t="str">
-        <f>IF(D100=G100, "", "Error")</f>
+      <c r="H101" s="150" t="str">
+        <f>IF(D101=G101, "", "Error")</f>
         <v/>
       </c>
-      <c r="J100" s="109"/>
-    </row>
-    <row r="101" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="7"/>
-      <c r="B101" s="7"/>
-      <c r="C101" s="7"/>
-      <c r="D101" s="113"/>
-      <c r="E101" s="117"/>
-      <c r="F101" s="7"/>
-      <c r="H101" s="150"/>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A102" s="94" t="s">
-        <v>102</v>
-      </c>
+      <c r="J101" s="109"/>
+    </row>
+    <row r="102" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="7"/>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
-      <c r="D102" s="113">
-        <v>96626.92</v>
-      </c>
-      <c r="E102" s="149">
-        <f>D102*91.91%</f>
-        <v>88809.802171999996</v>
-      </c>
-      <c r="F102" s="134">
-        <f>D102*8.09%</f>
-        <v>7817.1178279999995</v>
-      </c>
+      <c r="D102" s="113"/>
+      <c r="E102" s="117"/>
+      <c r="F102" s="7"/>
       <c r="H102" s="150"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="94" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B103" s="7"/>
-      <c r="C103" s="122"/>
+      <c r="C103" s="7"/>
       <c r="D103" s="113">
-        <v>44400</v>
+        <v>100104.56</v>
       </c>
       <c r="E103" s="149">
         <f>D103*91.91%</f>
-        <v>40808.039999999994</v>
+        <v>92006.101095999984</v>
       </c>
       <c r="F103" s="134">
         <f>D103*8.09%</f>
+        <v>8098.4589040000001</v>
+      </c>
+      <c r="H103" s="150"/>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" s="94" t="s">
+        <v>103</v>
+      </c>
+      <c r="B104" s="7"/>
+      <c r="C104" s="122"/>
+      <c r="D104" s="113">
+        <v>44400</v>
+      </c>
+      <c r="E104" s="149">
+        <f>D104*91.91%</f>
+        <v>40808.039999999994</v>
+      </c>
+      <c r="F104" s="134">
+        <f>D104*8.09%</f>
         <v>3591.96</v>
       </c>
-      <c r="H103" s="150"/>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A104" s="95" t="s">
+      <c r="H104" s="150"/>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="B104" s="95"/>
-      <c r="C104" s="95"/>
-      <c r="D104" s="158">
-        <f>SUM(D102:D103)</f>
-        <v>141026.91999999998</v>
-      </c>
-      <c r="E104" s="147">
-        <f t="shared" ref="E104:F104" si="17">SUM(E102:E103)</f>
-        <v>129617.84217199999</v>
-      </c>
-      <c r="F104" s="147">
-        <f t="shared" si="17"/>
-        <v>11409.077827999999</v>
-      </c>
-      <c r="G104" s="109">
-        <f>E104+F104</f>
-        <v>141026.91999999998</v>
-      </c>
-      <c r="H104" s="150" t="str">
-        <f>IF(D104=G104, "", "Error")</f>
+      <c r="B105" s="95"/>
+      <c r="C105" s="95"/>
+      <c r="D105" s="158">
+        <f>SUM(D103:D104)</f>
+        <v>144504.56</v>
+      </c>
+      <c r="E105" s="147">
+        <f t="shared" ref="E105:F105" si="26">SUM(E103:E104)</f>
+        <v>132814.14109599998</v>
+      </c>
+      <c r="F105" s="147">
+        <f t="shared" si="26"/>
+        <v>11690.418904</v>
+      </c>
+      <c r="G105" s="109">
+        <f>E105+F105</f>
+        <v>144504.55999999997</v>
+      </c>
+      <c r="H105" s="150" t="str">
+        <f>IF(D105=G105, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="7"/>
-      <c r="B105" s="7"/>
-      <c r="C105" s="7"/>
-      <c r="D105" s="190"/>
-      <c r="E105" s="12"/>
-      <c r="F105" s="7"/>
-      <c r="H105" s="150"/>
-    </row>
-    <row r="106" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="99" t="s">
+    <row r="106" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="7"/>
+      <c r="B106" s="7"/>
+      <c r="C106" s="7"/>
+      <c r="D106" s="186"/>
+      <c r="E106" s="12"/>
+      <c r="F106" s="7"/>
+      <c r="H106" s="150"/>
+    </row>
+    <row r="107" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="99" t="s">
         <v>134</v>
       </c>
-      <c r="B106" s="99"/>
-      <c r="C106" s="99"/>
-      <c r="D106" s="191"/>
-      <c r="E106" s="118">
-        <f>D106*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F106" s="136">
-        <f>D106*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G106" s="109">
-        <f>E106+F106</f>
-        <v>0</v>
-      </c>
-      <c r="H106" s="150" t="str">
-        <f>IF(D106=G106, "", "Error")</f>
+      <c r="B107" s="99"/>
+      <c r="C107" s="99"/>
+      <c r="D107" s="187"/>
+      <c r="E107" s="118">
+        <f>D107*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F107" s="136">
+        <f>D107*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="G107" s="109">
+        <f>E107+F107</f>
+        <v>0</v>
+      </c>
+      <c r="H107" s="150" t="str">
+        <f>IF(D107=G107, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="1"/>
-      <c r="D107" s="188"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="10"/>
-      <c r="G107" s="157">
-        <f>SUM(G27:G106)</f>
-        <v>9096045.7599999998</v>
-      </c>
-      <c r="H107" s="150"/>
-    </row>
-    <row r="108" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="4" t="s">
+    <row r="108" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="1"/>
+      <c r="D108" s="184"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="10"/>
+      <c r="G108" s="157"/>
+      <c r="H108" s="150"/>
+    </row>
+    <row r="109" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B108" s="60"/>
-      <c r="C108" s="5"/>
-      <c r="D108" s="192">
-        <f>SUM(D106+D104+D100+D93+D86+D55+D35+D30+D48)</f>
-        <v>5998392.3399999999</v>
-      </c>
-      <c r="E108" s="148">
-        <f>SUM(E106+E104+E100+E93+E86+E55+E35+E30+E48)</f>
-        <v>5467471.9837839995</v>
-      </c>
-      <c r="F108" s="148">
-        <f>SUM(F106+F104+F100+F93+F86+F55+F35+F30+F48)</f>
-        <v>333498.29621600005</v>
-      </c>
-      <c r="G108" s="109">
-        <f>E108+F108</f>
-        <v>5800970.2799999993</v>
-      </c>
-      <c r="H108" s="150" t="str">
-        <f>IF(D108=G108, "", "Error")</f>
-        <v>Error</v>
-      </c>
-      <c r="I108" s="181">
-        <f>D108-G108</f>
-        <v>197422.06000000052</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D109" s="188"/>
-      <c r="E109" s="109"/>
-    </row>
-    <row r="110" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="142" t="s">
+      <c r="B109" s="60"/>
+      <c r="C109" s="5"/>
+      <c r="D109" s="188">
+        <f>SUM(D107+D105+D101+D94+D88+D55+D35+D30+D48)</f>
+        <v>7496328.3699999992</v>
+      </c>
+      <c r="E109" s="148">
+        <f>SUM(E107+E105+E101+E94+E88+E55+E35+E30+E48)</f>
+        <v>7082805.3203670001</v>
+      </c>
+      <c r="F109" s="148">
+        <f>SUM(F107+F105+F101+F94+F88+F55+F35+F30+F48)</f>
+        <v>413523.04963299993</v>
+      </c>
+      <c r="G109" s="109">
+        <f>E109+F109</f>
+        <v>7496328.3700000001</v>
+      </c>
+      <c r="H109" s="150" t="str">
+        <f>IF(D109=G109, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="I109" s="178">
+        <f>D109-G109</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D110" s="184"/>
+      <c r="E110" s="109"/>
+    </row>
+    <row r="111" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="142" t="s">
         <v>121</v>
       </c>
-      <c r="B110" s="141"/>
-      <c r="C110" s="141"/>
-      <c r="E110" s="109"/>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A111" s="1"/>
-      <c r="C111" s="139"/>
+      <c r="B111" s="141"/>
+      <c r="C111" s="141"/>
       <c r="E111" s="109"/>
     </row>
-    <row r="112" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="C112" s="139"/>
       <c r="E112" s="109"/>
     </row>
-    <row r="113" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="143" t="s">
+    <row r="113" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="1"/>
+      <c r="C113" s="139"/>
+      <c r="E113" s="109"/>
+    </row>
+    <row r="114" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="143" t="s">
         <v>30</v>
       </c>
-      <c r="B113" s="144"/>
-      <c r="C113" s="140">
-        <f>SUM(C111:C112)</f>
-        <v>0</v>
-      </c>
-      <c r="E113" s="109"/>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B114" s="144"/>
+      <c r="C114" s="140">
+        <f>SUM(C112:C113)</f>
+        <v>0</v>
+      </c>
       <c r="E114" s="109"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E115" s="137"/>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A116" s="227" t="s">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E115" s="109"/>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E116" s="137"/>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="222" t="s">
         <v>114</v>
       </c>
-      <c r="B116" s="228"/>
-      <c r="C116" s="228"/>
-      <c r="D116" s="228"/>
-      <c r="E116" s="172" t="s">
+      <c r="B117" s="223"/>
+      <c r="C117" s="223"/>
+      <c r="D117" s="223"/>
+      <c r="E117" s="171" t="s">
         <v>22</v>
       </c>
-      <c r="F116" s="173" t="s">
+      <c r="F117" s="172" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="224"/>
-      <c r="B117" s="225"/>
-      <c r="C117" s="226"/>
-      <c r="D117" s="167"/>
-      <c r="E117" s="149"/>
-      <c r="F117" s="134"/>
-    </row>
-    <row r="118" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="221"/>
-      <c r="B118" s="222"/>
-      <c r="C118" s="223"/>
-      <c r="D118" s="182"/>
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="219"/>
+      <c r="B118" s="220"/>
+      <c r="C118" s="221"/>
+      <c r="D118" s="166"/>
       <c r="E118" s="149"/>
       <c r="F118" s="134"/>
     </row>
-    <row r="119" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="174"/>
-      <c r="B119" s="175"/>
-      <c r="C119" s="176"/>
-      <c r="D119" s="182"/>
-      <c r="E119" s="149"/>
-      <c r="F119" s="134"/>
-    </row>
-    <row r="120" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="221"/>
-      <c r="B120" s="222"/>
-      <c r="C120" s="223"/>
-      <c r="D120" s="113"/>
+    <row r="119" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="216" t="s">
+        <v>166</v>
+      </c>
+      <c r="B119" s="217"/>
+      <c r="C119" s="173"/>
+      <c r="D119" s="113">
+        <v>300000</v>
+      </c>
+      <c r="E119" s="149">
+        <f t="shared" ref="E119:E120" si="27">D119*91.91%</f>
+        <v>275730</v>
+      </c>
+      <c r="F119" s="134">
+        <f t="shared" ref="F119:F120" si="28">D119*8.09%</f>
+        <v>24270</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="216" t="s">
+        <v>159</v>
+      </c>
+      <c r="B120" s="217"/>
+      <c r="C120" s="173"/>
+      <c r="D120" s="113">
+        <v>10391.24</v>
+      </c>
       <c r="E120" s="149">
-        <f>D120*91.91%</f>
-        <v>0</v>
+        <f t="shared" si="27"/>
+        <v>9550.5886839999985</v>
       </c>
       <c r="F120" s="134">
-        <f>D120*8.09%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A121" s="215" t="s">
+        <f t="shared" si="28"/>
+        <v>840.65131599999995</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="216"/>
+      <c r="B121" s="217"/>
+      <c r="C121" s="218"/>
+      <c r="D121" s="113"/>
+      <c r="E121" s="149">
+        <f>D121*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F121" s="134">
+        <f>D121*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="210" t="s">
         <v>30</v>
       </c>
-      <c r="B121" s="216"/>
-      <c r="C121" s="217"/>
-      <c r="D121" s="171">
-        <f>SUM(D117:D120)</f>
-        <v>0</v>
-      </c>
-      <c r="E121" s="171">
-        <f>SUM(E117:E120)</f>
-        <v>0</v>
-      </c>
-      <c r="F121" s="171">
-        <f>SUM(F117:F120)</f>
-        <v>0</v>
-      </c>
-      <c r="H121" s="109">
-        <f>E121+F121</f>
-        <v>0</v>
-      </c>
-      <c r="I121" s="150" t="str">
-        <f>IF(D121=H121, "", "Error")</f>
+      <c r="B122" s="211"/>
+      <c r="C122" s="212"/>
+      <c r="D122" s="170">
+        <f>SUM(D118:D121)</f>
+        <v>310391.24</v>
+      </c>
+      <c r="E122" s="170">
+        <f>SUM(E118:E121)</f>
+        <v>285280.58868400002</v>
+      </c>
+      <c r="F122" s="170">
+        <f>SUM(F118:F121)</f>
+        <v>25110.651315999999</v>
+      </c>
+      <c r="H122" s="109">
+        <f>E122+F122</f>
+        <v>310391.24</v>
+      </c>
+      <c r="I122" s="150" t="str">
+        <f>IF(D122=H122, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E123" s="109"/>
-    </row>
-    <row r="124" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="102" t="s">
+    <row r="124" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E124" s="109"/>
+    </row>
+    <row r="125" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="102" t="s">
         <v>105</v>
       </c>
-      <c r="B124" s="103">
-        <f>D108</f>
-        <v>5998392.3399999999</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A125" s="104" t="s">
+      <c r="B125" s="103">
+        <f>D109</f>
+        <v>7496328.3699999992</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="104" t="s">
         <v>107</v>
       </c>
-      <c r="B125" s="105">
-        <f>D108-D106</f>
-        <v>5998392.3399999999</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D126" s="205"/>
-      <c r="E126" s="205"/>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A127" s="74" t="s">
+      <c r="B126" s="105">
+        <f>D109-D107</f>
+        <v>7496328.3699999992</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D127" s="200"/>
+      <c r="E127" s="200"/>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="B127" s="75"/>
-      <c r="C127" s="76"/>
-      <c r="D127" s="205"/>
-      <c r="E127" s="205"/>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A128" s="77" t="s">
+      <c r="B128" s="75"/>
+      <c r="C128" s="76"/>
+      <c r="D128" s="200"/>
+      <c r="E128" s="200"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="77" t="s">
         <v>92</v>
       </c>
-      <c r="B128" s="78">
-        <v>4452323.820828055</v>
-      </c>
-      <c r="C128" s="78"/>
-      <c r="D128" s="205"/>
-      <c r="E128" s="205"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A129" s="79" t="s">
+      <c r="B129" s="78">
+        <v>6056324.5665496523</v>
+      </c>
+      <c r="C129" s="78"/>
+      <c r="D129" s="200"/>
+      <c r="E129" s="200"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="79" t="s">
         <v>93</v>
       </c>
-      <c r="B129" s="92">
+      <c r="B130" s="92">
         <f>PRORRATEO!G52</f>
-        <v>6849105.1357215978</v>
-      </c>
-      <c r="C129" s="78" t="s">
+        <v>6320855.3670509998</v>
+      </c>
+      <c r="C130" s="78" t="s">
         <v>94</v>
       </c>
-      <c r="D129" s="205"/>
-      <c r="E129" s="205"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A130" s="79" t="s">
+      <c r="D130" s="200"/>
+      <c r="E130" s="200"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" s="79" t="s">
         <v>116</v>
       </c>
-      <c r="B130" s="178">
-        <f>-B125</f>
-        <v>-5998392.3399999999</v>
-      </c>
-      <c r="C130" s="76"/>
-      <c r="D130" s="205"/>
-      <c r="E130" s="205"/>
-      <c r="G130" s="113"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A131" s="79" t="s">
+      <c r="B131" s="175">
+        <f>-B126</f>
+        <v>-7496328.3699999992</v>
+      </c>
+      <c r="C131" s="76"/>
+      <c r="D131" s="200"/>
+      <c r="E131" s="200"/>
+      <c r="G131" s="113"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" s="79" t="s">
         <v>115</v>
       </c>
-      <c r="B131" s="178">
-        <f>-D121</f>
-        <v>0</v>
-      </c>
-      <c r="C131" s="76"/>
-      <c r="D131" s="205"/>
-      <c r="E131" s="205"/>
-      <c r="G131" s="125"/>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A132" s="79" t="s">
+      <c r="B132" s="175">
+        <f>-D122</f>
+        <v>-310391.24</v>
+      </c>
+      <c r="C132" s="76"/>
+      <c r="D132" s="200"/>
+      <c r="E132" s="200"/>
+      <c r="G132" s="125"/>
+    </row>
+    <row r="133" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="254" t="s">
+        <v>174</v>
+      </c>
+      <c r="B133" s="175">
+        <v>-338000</v>
+      </c>
+      <c r="C133" s="76"/>
+      <c r="D133" s="198"/>
+      <c r="E133" s="198"/>
+      <c r="G133" s="125"/>
+    </row>
+    <row r="134" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="253" t="s">
+        <v>175</v>
+      </c>
+      <c r="B134" s="175">
+        <v>-308000</v>
+      </c>
+      <c r="C134" s="76"/>
+      <c r="D134" s="198"/>
+      <c r="E134" s="198"/>
+      <c r="G134" s="125"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="B132" s="178">
-        <f>-B139</f>
-        <v>0</v>
-      </c>
-      <c r="C132" s="80"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A133" s="79" t="s">
+      <c r="B135" s="175">
+        <f>-B142</f>
+        <v>0</v>
+      </c>
+      <c r="C135" s="80"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" s="79" t="s">
         <v>121</v>
       </c>
-      <c r="B133" s="93">
-        <f>-C113</f>
-        <v>0</v>
-      </c>
-      <c r="C133" s="80"/>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A134" s="79"/>
-      <c r="B134" s="75"/>
-      <c r="C134" s="80"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A135" s="77" t="s">
+      <c r="B136" s="93">
+        <f>-C114</f>
+        <v>0</v>
+      </c>
+      <c r="C136" s="80"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="79"/>
+      <c r="B137" s="75"/>
+      <c r="C137" s="80"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B135" s="81">
-        <f>SUM(B128:B134)</f>
-        <v>5303036.6165496521</v>
-      </c>
-      <c r="C135" s="154"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A136" s="80"/>
-      <c r="C136" s="76"/>
-      <c r="D136" s="83"/>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C137" s="76"/>
-      <c r="D137" s="109"/>
-      <c r="E137" s="181"/>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A138" s="74" t="s">
+      <c r="B138" s="81">
+        <f>SUM(B129:B137)</f>
+        <v>3924460.3236006536</v>
+      </c>
+      <c r="C138" s="154"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" s="80"/>
+      <c r="C139" s="76"/>
+      <c r="D139" s="83"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C140" s="76"/>
+      <c r="D140" s="109"/>
+      <c r="E140" s="178"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="B138" s="11">
+      <c r="B141" s="11">
         <v>-310694.54000000004</v>
       </c>
-      <c r="C138" s="82"/>
-    </row>
-    <row r="139" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="77" t="s">
-        <v>156</v>
-      </c>
-      <c r="B139" s="93"/>
-      <c r="C139" s="82"/>
-      <c r="D139" s="181"/>
-      <c r="E139" s="109"/>
-    </row>
-    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="77"/>
-      <c r="B140" s="178"/>
-      <c r="C140" s="82"/>
-      <c r="E140" s="109"/>
-    </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="77"/>
-      <c r="B141" s="178"/>
       <c r="C141" s="82"/>
-      <c r="E141" s="109"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A142" s="77"/>
-      <c r="B142" s="178"/>
+      <c r="D141" s="178"/>
+      <c r="E141" s="178"/>
+      <c r="F141" s="178"/>
+    </row>
+    <row r="142" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="77" t="s">
+        <v>143</v>
+      </c>
+      <c r="B142" s="93"/>
       <c r="C142" s="82"/>
-      <c r="E142" s="109"/>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A143" s="100" t="s">
+      <c r="D142" s="178"/>
+      <c r="E142" s="252"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="77"/>
+      <c r="B143" s="175"/>
+      <c r="C143" s="82"/>
+      <c r="E143" s="109"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="77" t="s">
+        <v>169</v>
+      </c>
+      <c r="B144" s="175">
+        <v>-55000</v>
+      </c>
+      <c r="C144" s="82"/>
+      <c r="E144" s="109"/>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A145" s="100" t="s">
         <v>30</v>
       </c>
-      <c r="B143" s="101">
-        <f>SUM(B138:B142)</f>
-        <v>-310694.54000000004</v>
-      </c>
-      <c r="C143" s="82"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C144" s="83"/>
-      <c r="D144" s="181"/>
-    </row>
-    <row r="145" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B145" s="80"/>
-      <c r="C145" s="76"/>
-    </row>
-    <row r="147" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="N147" s="12"/>
-    </row>
-    <row r="150" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B150" s="204" t="s">
-        <v>155</v>
-      </c>
-      <c r="C150" s="204"/>
-      <c r="D150" s="204"/>
-      <c r="E150" s="204"/>
-    </row>
-    <row r="151" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B151" s="204"/>
-      <c r="C151" s="204"/>
-      <c r="D151" s="204"/>
-      <c r="E151" s="204"/>
-    </row>
-    <row r="152" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B152" s="204"/>
-      <c r="C152" s="204"/>
-      <c r="D152" s="204"/>
-      <c r="E152" s="204"/>
-    </row>
-    <row r="153" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B153" s="204"/>
-      <c r="C153" s="204"/>
-      <c r="D153" s="204"/>
-      <c r="E153" s="204"/>
-    </row>
-    <row r="154" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B154" s="204"/>
-      <c r="C154" s="204"/>
-      <c r="D154" s="204"/>
-      <c r="E154" s="204"/>
+      <c r="B145" s="101">
+        <f>SUM(B141:B144)</f>
+        <v>-365694.54000000004</v>
+      </c>
+      <c r="C145" s="82"/>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C146" s="83"/>
+      <c r="D146" s="178"/>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B147" s="80"/>
+      <c r="C147" s="76"/>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N149" s="12"/>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B152" s="199" t="s">
+        <v>176</v>
+      </c>
+      <c r="C152" s="199"/>
+      <c r="D152" s="199"/>
+      <c r="E152" s="199"/>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B153" s="199"/>
+      <c r="C153" s="199"/>
+      <c r="D153" s="199"/>
+      <c r="E153" s="199"/>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B154" s="199"/>
+      <c r="C154" s="199"/>
+      <c r="D154" s="199"/>
+      <c r="E154" s="199"/>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B155" s="199"/>
+      <c r="C155" s="199"/>
+      <c r="D155" s="199"/>
+      <c r="E155" s="199"/>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B156" s="199"/>
+      <c r="C156" s="199"/>
+      <c r="D156" s="199"/>
+      <c r="E156" s="199"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="B150:E154"/>
-    <mergeCell ref="D126:E131"/>
+  <mergeCells count="19">
+    <mergeCell ref="A120:B120"/>
+    <mergeCell ref="A119:B119"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="B152:E156"/>
+    <mergeCell ref="D127:E132"/>
     <mergeCell ref="B14:D17"/>
+    <mergeCell ref="A122:C122"/>
+    <mergeCell ref="A66:C66"/>
     <mergeCell ref="A121:C121"/>
+    <mergeCell ref="A118:C118"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A67:C67"/>
     <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A118:C118"/>
-    <mergeCell ref="A120:C120"/>
-    <mergeCell ref="A117:C117"/>
-    <mergeCell ref="A116:D116"/>
-    <mergeCell ref="A77:C77"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A74:C74"/>
     <mergeCell ref="A69:C69"/>
     <mergeCell ref="A70:C70"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A75:C75"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4164,26 +4597,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="17.109375" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" customWidth="1"/>
     <col min="6" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
-    <col min="14" max="14" width="13.6640625" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" customWidth="1"/>
-    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4199,18 +4632,18 @@
       <c r="K1" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="L1" s="236">
-        <f>RESUMEN!D108</f>
-        <v>5998392.3399999999</v>
-      </c>
-      <c r="M1" s="237"/>
+      <c r="L1" s="240">
+        <f>RESUMEN!D109</f>
+        <v>7496328.3699999992</v>
+      </c>
+      <c r="M1" s="241"/>
       <c r="N1" s="152"/>
       <c r="O1" s="135">
         <f>L1*8.09%</f>
-        <v>485269.940306</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+        <v>606452.96513299993</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -4226,16 +4659,16 @@
       </c>
       <c r="L2" s="8"/>
       <c r="M2" s="152">
-        <f>5500000-150000-3015-250-12</f>
-        <v>5346723</v>
+        <f>5500000-150000-3015-250-12+1997000+170000+5497+450+30-1000000</f>
+        <v>6519700</v>
       </c>
       <c r="N2" s="153"/>
       <c r="O2" s="135">
         <f>O1-K7-553-50-86-8</f>
-        <v>153642.640655</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+        <v>207324.22721099993</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="str">
         <f>RESUMEN!C5</f>
         <v>VTO. 16/06</v>
@@ -4253,11 +4686,14 @@
         <v>132</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="128"/>
+      <c r="M3" s="128">
+        <f>RESUMEN!D122</f>
+        <v>310391.24</v>
+      </c>
       <c r="N3" s="151"/>
       <c r="O3" s="73"/>
     </row>
-    <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -4275,70 +4711,73 @@
         <v>126</v>
       </c>
       <c r="L4" s="8"/>
-      <c r="M4" s="128"/>
+      <c r="M4" s="128">
+        <f>25000+310391+3500-500-800+110+11</f>
+        <v>337712</v>
+      </c>
       <c r="N4" s="124"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="234" t="s">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="233" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="247" t="s">
+      <c r="B5" s="235" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="234" t="s">
+      <c r="C5" s="233" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="245" t="s">
+      <c r="D5" s="237" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="234" t="s">
+      <c r="E5" s="233" t="s">
         <v>98</v>
       </c>
-      <c r="F5" s="234" t="s">
+      <c r="F5" s="233" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="234" t="s">
+      <c r="G5" s="233" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="240" t="s">
+      <c r="H5" s="244" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="245" t="s">
+      <c r="I5" s="237" t="s">
         <v>109</v>
       </c>
-      <c r="J5" s="238" t="s">
+      <c r="J5" s="242" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="238" t="s">
+      <c r="K5" s="242" t="s">
         <v>70</v>
       </c>
-      <c r="L5" s="243" t="s">
+      <c r="L5" s="247" t="s">
         <v>124</v>
       </c>
-      <c r="M5" s="238" t="s">
+      <c r="M5" s="242" t="s">
         <v>68</v>
       </c>
-      <c r="N5" s="238" t="s">
+      <c r="N5" s="242" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="235"/>
-      <c r="B6" s="248"/>
-      <c r="C6" s="235"/>
-      <c r="D6" s="249"/>
-      <c r="E6" s="235"/>
-      <c r="F6" s="235"/>
-      <c r="G6" s="235"/>
-      <c r="H6" s="241"/>
-      <c r="I6" s="246"/>
-      <c r="J6" s="239"/>
-      <c r="K6" s="242"/>
-      <c r="L6" s="244"/>
-      <c r="M6" s="242"/>
-      <c r="N6" s="239"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="234"/>
+      <c r="B6" s="236"/>
+      <c r="C6" s="234"/>
+      <c r="D6" s="238"/>
+      <c r="E6" s="234"/>
+      <c r="F6" s="234"/>
+      <c r="G6" s="234"/>
+      <c r="H6" s="245"/>
+      <c r="I6" s="249"/>
+      <c r="J6" s="243"/>
+      <c r="K6" s="246"/>
+      <c r="L6" s="248"/>
+      <c r="M6" s="246"/>
+      <c r="N6" s="243"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>34</v>
       </c>
@@ -4353,36 +4792,38 @@
         <v>8.09</v>
       </c>
       <c r="F7" s="88">
-        <v>387209.15595160006</v>
-      </c>
-      <c r="G7" s="196">
+        <v>330930.29965100001</v>
+      </c>
+      <c r="G7" s="191">
         <f>F7</f>
-        <v>387209.15595160006</v>
+        <v>330930.29965100001</v>
       </c>
       <c r="H7" s="131">
         <f>F7-G7</f>
         <v>0</v>
       </c>
       <c r="I7" s="106">
-        <v>11</v>
-      </c>
-      <c r="J7" s="88"/>
+        <v>14</v>
+      </c>
+      <c r="J7" s="88">
+        <v>25110.651315999999</v>
+      </c>
       <c r="K7" s="88">
-        <v>330930.29965100001</v>
+        <v>398431.737922</v>
       </c>
       <c r="L7" s="98">
         <v>0</v>
       </c>
       <c r="M7" s="6">
         <f>K7+J7+H7+L7</f>
-        <v>330930.29965100001</v>
+        <v>423542.38923799997</v>
       </c>
       <c r="N7" s="11">
         <f>M7*6% + M7</f>
-        <v>350786.11763006001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+        <v>448954.93259227998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>36</v>
       </c>
@@ -4397,40 +4838,40 @@
         <v>2.21</v>
       </c>
       <c r="F8" s="88">
-        <v>152947.46151451589</v>
-      </c>
-      <c r="G8" s="196">
-        <v>153000</v>
+        <v>118110.03981451588</v>
+      </c>
+      <c r="G8" s="191">
+        <v>118500</v>
       </c>
       <c r="H8" s="131">
         <f t="shared" ref="H8:H51" si="0">F8-G8</f>
-        <v>-52.538485484110424</v>
+        <v>-389.96018548411666</v>
       </c>
       <c r="I8" s="106">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J8" s="88">
         <f>M$4*E8%</f>
-        <v>0</v>
+        <v>7463.435199999999</v>
       </c>
       <c r="K8" s="88">
         <f>M$2*E8 /100</f>
-        <v>118162.57829999999</v>
-      </c>
-      <c r="L8" s="166">
+        <v>144085.37</v>
+      </c>
+      <c r="L8" s="165">
         <f>J$3*E8%+J$4</f>
         <v>0</v>
       </c>
       <c r="M8" s="6">
         <f>K8+J8+H8+L8</f>
-        <v>118110.03981451588</v>
+        <v>151158.84501451589</v>
       </c>
       <c r="N8" s="11">
         <f t="shared" ref="N8:N51" si="1">M8*6% + M8</f>
-        <v>125196.64220338683</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+        <v>160228.37571538685</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>36</v>
       </c>
@@ -4445,41 +4886,41 @@
         <v>4.21</v>
       </c>
       <c r="F9" s="88">
-        <v>292564.51887426333</v>
-      </c>
-      <c r="G9" s="197">
-        <f>333091-G34</f>
-        <v>295564.93309000001</v>
+        <v>222096.62408426331</v>
+      </c>
+      <c r="G9" s="192">
+        <f>250969-G34+RESUMEN!D65</f>
+        <v>333122.69579999999</v>
       </c>
       <c r="H9" s="131">
         <f t="shared" si="0"/>
-        <v>-3000.4142157366732</v>
+        <v>-111026.07171573667</v>
       </c>
       <c r="I9" s="106">
         <v>7</v>
       </c>
       <c r="J9" s="88">
         <f t="shared" ref="J9:J51" si="2">M$4*E9%</f>
-        <v>0</v>
+        <v>14217.6752</v>
       </c>
       <c r="K9" s="88">
         <f t="shared" ref="K9:K51" si="3">M$2*E9 /100</f>
-        <v>225097.03829999999</v>
-      </c>
-      <c r="L9" s="166">
+        <v>274479.37</v>
+      </c>
+      <c r="L9" s="165">
         <f t="shared" ref="L9:L51" si="4">J$3*E9%+J$4</f>
         <v>0</v>
       </c>
       <c r="M9" s="6">
         <f t="shared" ref="M9:M51" si="5">K9+J9+H9+L9</f>
-        <v>222096.62408426331</v>
+        <v>177670.97348426332</v>
       </c>
       <c r="N9" s="11">
         <f t="shared" si="1"/>
-        <v>235422.42152931911</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+        <v>188331.23189331911</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>39</v>
       </c>
@@ -4494,40 +4935,40 @@
         <v>2.84</v>
       </c>
       <c r="F10" s="88">
-        <v>231949.77220596874</v>
-      </c>
-      <c r="G10" s="196">
-        <v>197350</v>
+        <v>186446.70540596871</v>
+      </c>
+      <c r="G10" s="191">
+        <v>151845</v>
       </c>
       <c r="H10" s="131">
         <f t="shared" si="0"/>
-        <v>34599.772205968737</v>
+        <v>34601.705405968707</v>
       </c>
       <c r="I10" s="106">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J10" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9591.0208000000002</v>
       </c>
       <c r="K10" s="88">
         <f t="shared" si="3"/>
-        <v>151846.93319999997</v>
-      </c>
-      <c r="L10" s="166">
+        <v>185159.48</v>
+      </c>
+      <c r="L10" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M10" s="6">
         <f t="shared" si="5"/>
-        <v>186446.70540596871</v>
+        <v>229352.20620596872</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="1"/>
-        <v>197633.50773032682</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+        <v>243113.33857832683</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>39</v>
       </c>
@@ -4542,42 +4983,42 @@
         <v>3.43</v>
       </c>
       <c r="F11" s="88">
-        <v>238360.01759500001</v>
-      </c>
-      <c r="G11" s="196">
+        <v>183392.59890000001</v>
+      </c>
+      <c r="G11" s="191">
         <f>F11</f>
-        <v>238360.01759500001</v>
+        <v>183392.59890000001</v>
       </c>
       <c r="H11" s="131">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I11" s="106">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J11" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11583.521600000002</v>
       </c>
       <c r="K11" s="88">
         <f t="shared" si="3"/>
-        <v>183392.59890000001</v>
-      </c>
-      <c r="L11" s="166">
+        <v>223625.71</v>
+      </c>
+      <c r="L11" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M11" s="6">
         <f t="shared" si="5"/>
-        <v>183392.59890000001</v>
+        <v>235209.2316</v>
       </c>
       <c r="N11" s="11">
         <f t="shared" si="1"/>
-        <v>194396.15483400002</v>
+        <v>249321.785496</v>
       </c>
       <c r="P11" s="109"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>42</v>
       </c>
@@ -4592,41 +5033,41 @@
         <v>2.84</v>
       </c>
       <c r="F12" s="88">
-        <v>207359.31485999998</v>
-      </c>
-      <c r="G12" s="197">
+        <v>151846.93319999997</v>
+      </c>
+      <c r="G12" s="192">
         <f>F12</f>
-        <v>207359.31485999998</v>
+        <v>151846.93319999997</v>
       </c>
       <c r="H12" s="131">
         <f>F12-G12</f>
         <v>0</v>
       </c>
       <c r="I12" s="106">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J12" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9591.0208000000002</v>
       </c>
       <c r="K12" s="88">
         <f t="shared" si="3"/>
-        <v>151846.93319999997</v>
-      </c>
-      <c r="L12" s="166">
+        <v>185159.48</v>
+      </c>
+      <c r="L12" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M12" s="6">
         <f t="shared" si="5"/>
-        <v>151846.93319999997</v>
+        <v>194750.50080000001</v>
       </c>
       <c r="N12" s="11">
         <f t="shared" si="1"/>
-        <v>160957.74919199996</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+        <v>206435.53084800002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>42</v>
       </c>
@@ -4641,41 +5082,41 @@
         <v>3.43</v>
       </c>
       <c r="F13" s="88">
-        <v>254643.6733842417</v>
-      </c>
-      <c r="G13" s="197">
-        <f>311928-G50</f>
-        <v>270927.297265</v>
+        <v>167108.97501924171</v>
+      </c>
+      <c r="G13" s="192">
+        <f>198655-G50</f>
+        <v>167109.33429999999</v>
       </c>
       <c r="H13" s="131">
         <f t="shared" si="0"/>
-        <v>-16283.623880758299</v>
+        <v>-0.35928075827541761</v>
       </c>
       <c r="I13" s="106">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J13" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11583.521600000002</v>
       </c>
       <c r="K13" s="88">
         <f t="shared" si="3"/>
-        <v>183392.59890000001</v>
-      </c>
-      <c r="L13" s="166">
+        <v>223625.71</v>
+      </c>
+      <c r="L13" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M13" s="6">
         <f t="shared" si="5"/>
-        <v>167108.97501924171</v>
+        <v>235208.87231924172</v>
       </c>
       <c r="N13" s="11">
         <f t="shared" si="1"/>
-        <v>177135.51352039623</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+        <v>249321.40465839623</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>44</v>
       </c>
@@ -4690,11 +5131,11 @@
         <v>2.84</v>
       </c>
       <c r="F14" s="88">
-        <v>197359.31485999998</v>
-      </c>
-      <c r="G14" s="196">
+        <v>151846.93319999997</v>
+      </c>
+      <c r="G14" s="191">
         <f>F14</f>
-        <v>197359.31485999998</v>
+        <v>151846.93319999997</v>
       </c>
       <c r="H14" s="131">
         <f t="shared" si="0"/>
@@ -4705,26 +5146,26 @@
       </c>
       <c r="J14" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9591.0208000000002</v>
       </c>
       <c r="K14" s="88">
         <f t="shared" si="3"/>
-        <v>151846.93319999997</v>
-      </c>
-      <c r="L14" s="166">
+        <v>185159.48</v>
+      </c>
+      <c r="L14" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M14" s="6">
         <f t="shared" si="5"/>
-        <v>151846.93319999997</v>
+        <v>194750.50080000001</v>
       </c>
       <c r="N14" s="11">
         <f t="shared" si="1"/>
-        <v>160957.74919199996</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+        <v>206435.53084800002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>44</v>
       </c>
@@ -4739,41 +5180,41 @@
         <v>3.43</v>
       </c>
       <c r="F15" s="88">
-        <v>252661.03080153395</v>
-      </c>
-      <c r="G15" s="197">
-        <f>273105-G35</f>
-        <v>236273.86025500001</v>
+        <v>199779.76944653396</v>
+      </c>
+      <c r="G15" s="192">
+        <f>226514-G35</f>
+        <v>199780.38500000001</v>
       </c>
       <c r="H15" s="131">
         <f t="shared" si="0"/>
-        <v>16387.170546533947</v>
+        <v>-0.61555346605018713</v>
       </c>
       <c r="I15" s="106">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J15" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11583.521600000002</v>
       </c>
       <c r="K15" s="88">
         <f t="shared" si="3"/>
-        <v>183392.59890000001</v>
-      </c>
-      <c r="L15" s="166">
+        <v>223625.71</v>
+      </c>
+      <c r="L15" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M15" s="6">
         <f t="shared" si="5"/>
-        <v>199779.76944653396</v>
+        <v>235208.61604653395</v>
       </c>
       <c r="N15" s="11">
         <f t="shared" si="1"/>
-        <v>211766.555613326</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+        <v>249321.13300932597</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>47</v>
       </c>
@@ -4782,46 +5223,46 @@
         <v>32</v>
       </c>
       <c r="D16" s="133" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E16" s="7">
         <v>2.84</v>
       </c>
       <c r="F16" s="88">
-        <v>197359.91801566072</v>
-      </c>
-      <c r="G16" s="197">
-        <f>197360-G49</f>
-        <v>163308.56891500001</v>
+        <v>201082.98230066069</v>
+      </c>
+      <c r="G16" s="192">
+        <f>201083-G49</f>
+        <v>174884.05729999999</v>
       </c>
       <c r="H16" s="131">
         <f t="shared" si="0"/>
-        <v>34051.349100660707</v>
+        <v>26198.925000660704</v>
       </c>
       <c r="I16" s="106">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J16" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9591.0208000000002</v>
       </c>
       <c r="K16" s="88">
         <f t="shared" si="3"/>
-        <v>151846.93319999997</v>
-      </c>
-      <c r="L16" s="166">
-        <v>15184.7</v>
+        <v>185159.48</v>
+      </c>
+      <c r="L16" s="165">
+        <v>0</v>
       </c>
       <c r="M16" s="6">
         <f t="shared" si="5"/>
-        <v>201082.98230066069</v>
+        <v>220949.42580066071</v>
       </c>
       <c r="N16" s="11">
         <f t="shared" si="1"/>
-        <v>213147.96123870034</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+        <v>234206.39134870036</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>47</v>
       </c>
@@ -4836,41 +5277,41 @@
         <v>3.43</v>
       </c>
       <c r="F17" s="88">
-        <v>263261.3879418007</v>
-      </c>
-      <c r="G17" s="196">
-        <f>317157-G47-G48</f>
-        <v>244231.34330490002</v>
+        <v>214568.00214911473</v>
+      </c>
+      <c r="G17" s="191">
+        <f>255356-G47-G48</f>
+        <v>199247.48883799999</v>
       </c>
       <c r="H17" s="131">
         <f t="shared" si="0"/>
-        <v>19030.044636900682</v>
+        <v>15320.513311114744</v>
       </c>
       <c r="I17" s="106">
         <v>15</v>
       </c>
       <c r="J17" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11583.521600000002</v>
       </c>
       <c r="K17" s="88">
         <f t="shared" si="3"/>
-        <v>183392.59890000001</v>
-      </c>
-      <c r="L17" s="166">
+        <v>223625.71</v>
+      </c>
+      <c r="L17" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M17" s="6">
         <f t="shared" si="5"/>
-        <v>202422.64353690069</v>
+        <v>250529.74491111474</v>
       </c>
       <c r="N17" s="11">
         <f t="shared" si="1"/>
-        <v>214568.00214911473</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+        <v>265561.5296057816</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>49</v>
       </c>
@@ -4885,41 +5326,41 @@
         <v>2.84</v>
       </c>
       <c r="F18" s="88">
-        <v>196495.89207825137</v>
-      </c>
-      <c r="G18" s="196">
-        <f>239000-G51</f>
-        <v>199389.151595</v>
+        <v>148953.67368325134</v>
+      </c>
+      <c r="G18" s="191">
+        <f>58000+76000+28000+16000+2000-G51</f>
+        <v>149523.6789</v>
       </c>
       <c r="H18" s="131">
         <f t="shared" si="0"/>
-        <v>-2893.2595167486288</v>
+        <v>-570.0052167486574</v>
       </c>
       <c r="I18" s="106">
         <v>14</v>
       </c>
       <c r="J18" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9591.0208000000002</v>
       </c>
       <c r="K18" s="88">
         <f t="shared" si="3"/>
-        <v>151846.93319999997</v>
-      </c>
-      <c r="L18" s="166">
+        <v>185159.48</v>
+      </c>
+      <c r="L18" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M18" s="6">
         <f t="shared" si="5"/>
-        <v>148953.67368325134</v>
+        <v>194180.49558325135</v>
       </c>
       <c r="N18" s="11">
         <f t="shared" si="1"/>
-        <v>157890.89410424643</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+        <v>205831.32531824644</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>49</v>
       </c>
@@ -4934,41 +5375,41 @@
         <v>3.43</v>
       </c>
       <c r="F19" s="88">
-        <v>238360.25635516795</v>
-      </c>
-      <c r="G19" s="197">
-        <f>275886-G41</f>
-        <v>238359.93309000001</v>
+        <v>183392.92216516795</v>
+      </c>
+      <c r="G19" s="192">
+        <f>212265-G41</f>
+        <v>183392.69579999999</v>
       </c>
       <c r="H19" s="131">
         <f t="shared" si="0"/>
-        <v>0.3232651679427363</v>
+        <v>0.22636516796774231</v>
       </c>
       <c r="I19" s="106">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J19" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11583.521600000002</v>
       </c>
       <c r="K19" s="88">
         <f t="shared" si="3"/>
-        <v>183392.59890000001</v>
-      </c>
-      <c r="L19" s="166">
+        <v>223625.71</v>
+      </c>
+      <c r="L19" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M19" s="6">
         <f t="shared" si="5"/>
-        <v>183392.92216516795</v>
+        <v>235209.45796516797</v>
       </c>
       <c r="N19" s="11">
         <f t="shared" si="1"/>
-        <v>194396.49749507802</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+        <v>249322.02544307805</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>52</v>
       </c>
@@ -4983,41 +5424,41 @@
         <v>2.84</v>
       </c>
       <c r="F20" s="88">
-        <v>197359.46332207473</v>
-      </c>
-      <c r="G20" s="196">
-        <f>231410-G38</f>
-        <v>197358.56891500001</v>
+        <v>151847.82760707469</v>
+      </c>
+      <c r="G20" s="191">
+        <f>178047-G38</f>
+        <v>151848.05729999999</v>
       </c>
       <c r="H20" s="131">
         <f t="shared" si="0"/>
-        <v>0.89440707472385839</v>
+        <v>-0.22969292529160157</v>
       </c>
       <c r="I20" s="106">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J20" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9591.0208000000002</v>
       </c>
       <c r="K20" s="88">
         <f t="shared" si="3"/>
-        <v>151846.93319999997</v>
-      </c>
-      <c r="L20" s="166">
+        <v>185159.48</v>
+      </c>
+      <c r="L20" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M20" s="6">
         <f t="shared" si="5"/>
-        <v>151847.82760707469</v>
+        <v>194750.27110707472</v>
       </c>
       <c r="N20" s="11">
         <f t="shared" si="1"/>
-        <v>160958.69726349917</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+        <v>206435.28737349919</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>52</v>
       </c>
@@ -5032,41 +5473,41 @@
         <v>3.43</v>
       </c>
       <c r="F21" s="88">
-        <v>239360.65868179579</v>
-      </c>
-      <c r="G21" s="196">
-        <f>276887-G45</f>
-        <v>239360.93309000001</v>
+        <v>183392.32449179579</v>
+      </c>
+      <c r="G21" s="191">
+        <f>212264-G45</f>
+        <v>183391.69579999999</v>
       </c>
       <c r="H21" s="131">
         <f t="shared" si="0"/>
-        <v>-0.27440820421907119</v>
+        <v>0.62869179580593482</v>
       </c>
       <c r="I21" s="106">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J21" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11583.521600000002</v>
       </c>
       <c r="K21" s="88">
         <f t="shared" si="3"/>
-        <v>183392.59890000001</v>
-      </c>
-      <c r="L21" s="166">
+        <v>223625.71</v>
+      </c>
+      <c r="L21" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M21" s="6">
         <f t="shared" si="5"/>
-        <v>183392.32449179579</v>
+        <v>235209.86029179581</v>
       </c>
       <c r="N21" s="11">
         <f t="shared" si="1"/>
-        <v>194395.86396130355</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+        <v>249322.45190930355</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>55</v>
       </c>
@@ -5074,48 +5515,48 @@
       <c r="C22" s="7">
         <v>38</v>
       </c>
-      <c r="D22" s="168" t="s">
+      <c r="D22" s="167" t="s">
         <v>129</v>
       </c>
       <c r="E22" s="7">
         <v>2.84</v>
       </c>
       <c r="F22" s="88">
-        <v>197359.31485999998</v>
-      </c>
-      <c r="G22" s="196">
+        <v>151846.93319999997</v>
+      </c>
+      <c r="G22" s="191">
         <f>F22</f>
-        <v>197359.31485999998</v>
+        <v>151846.93319999997</v>
       </c>
       <c r="H22" s="131">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I22" s="106">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J22" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9591.0208000000002</v>
       </c>
       <c r="K22" s="88">
         <f t="shared" si="3"/>
-        <v>151846.93319999997</v>
-      </c>
-      <c r="L22" s="166">
+        <v>185159.48</v>
+      </c>
+      <c r="L22" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M22" s="6">
         <f t="shared" si="5"/>
-        <v>151846.93319999997</v>
+        <v>194750.50080000001</v>
       </c>
       <c r="N22" s="11">
         <f t="shared" si="1"/>
-        <v>160957.74919199996</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+        <v>206435.53084800002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>55</v>
       </c>
@@ -5130,38 +5571,40 @@
         <v>3.43</v>
       </c>
       <c r="F23" s="88">
-        <v>201710.92273409516</v>
-      </c>
-      <c r="G23" s="197"/>
+        <v>385103.52163409517</v>
+      </c>
+      <c r="G23" s="192">
+        <f>447000-G46+RESUMEN!D70+RESUMEN!D71</f>
+        <v>582942.08675000002</v>
+      </c>
       <c r="H23" s="131">
         <f t="shared" si="0"/>
-        <v>201710.92273409516</v>
+        <v>-197838.56511590484</v>
       </c>
       <c r="I23" s="106">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J23" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11583.521600000002</v>
       </c>
       <c r="K23" s="88">
         <f t="shared" si="3"/>
-        <v>183392.59890000001</v>
-      </c>
-      <c r="L23" s="166">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>223625.71</v>
+      </c>
+      <c r="L23" s="165">
+        <v>20000</v>
       </c>
       <c r="M23" s="6">
         <f t="shared" si="5"/>
-        <v>385103.52163409517</v>
+        <v>57370.666484095156</v>
       </c>
       <c r="N23" s="11">
         <f t="shared" si="1"/>
-        <v>408209.73293214088</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+        <v>60812.906473140865</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>57</v>
       </c>
@@ -5176,41 +5619,41 @@
         <v>2.84</v>
       </c>
       <c r="F24" s="88">
-        <v>196636.18088607476</v>
-      </c>
-      <c r="G24" s="196">
-        <f>232000-G37</f>
-        <v>197948.56891500001</v>
+        <v>150534.54517107471</v>
+      </c>
+      <c r="G24" s="191">
+        <f>180000-G37</f>
+        <v>153801.05729999999</v>
       </c>
       <c r="H24" s="131">
         <f t="shared" si="0"/>
-        <v>-1312.3880289252556</v>
-      </c>
-      <c r="I24" s="185">
-        <v>4</v>
+        <v>-3266.5121289252711</v>
+      </c>
+      <c r="I24" s="181">
+        <v>5</v>
       </c>
       <c r="J24" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9591.0208000000002</v>
       </c>
       <c r="K24" s="88">
         <f t="shared" si="3"/>
-        <v>151846.93319999997</v>
-      </c>
-      <c r="L24" s="166">
+        <v>185159.48</v>
+      </c>
+      <c r="L24" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M24" s="6">
         <f t="shared" si="5"/>
-        <v>150534.54517107471</v>
+        <v>191483.98867107474</v>
       </c>
       <c r="N24" s="11">
         <f t="shared" si="1"/>
-        <v>159566.61788133919</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+        <v>202973.02799133922</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>57</v>
       </c>
@@ -5225,41 +5668,41 @@
         <v>3.43</v>
       </c>
       <c r="F25" s="88">
-        <v>238360.01759500001</v>
-      </c>
-      <c r="G25" s="196">
+        <v>183392.59890000001</v>
+      </c>
+      <c r="G25" s="191">
         <f>F25</f>
-        <v>238360.01759500001</v>
+        <v>183392.59890000001</v>
       </c>
       <c r="H25" s="131">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I25" s="106">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J25" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11583.521600000002</v>
       </c>
       <c r="K25" s="88">
         <f t="shared" si="3"/>
-        <v>183392.59890000001</v>
-      </c>
-      <c r="L25" s="166">
+        <v>223625.71</v>
+      </c>
+      <c r="L25" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M25" s="6">
         <f t="shared" si="5"/>
-        <v>183392.59890000001</v>
+        <v>235209.2316</v>
       </c>
       <c r="N25" s="11">
         <f t="shared" si="1"/>
-        <v>194396.15483400002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+        <v>249321.785496</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>60</v>
       </c>
@@ -5274,41 +5717,41 @@
         <v>6</v>
       </c>
       <c r="F26" s="88">
-        <v>65989.275081036845</v>
-      </c>
-      <c r="G26" s="197">
-        <f>200000+650000-G30-G31-G36</f>
-        <v>739506.58076499985</v>
-      </c>
-      <c r="H26" s="131">
+        <v>-352713.925683963</v>
+      </c>
+      <c r="G26" s="192">
+        <f>700000-G30-G31-G36</f>
+        <v>614987.10430000001</v>
+      </c>
+      <c r="H26" s="132">
         <f t="shared" si="0"/>
-        <v>-673517.305683963</v>
+        <v>-967701.029983963</v>
       </c>
       <c r="I26" s="106">
         <v>5</v>
       </c>
       <c r="J26" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>20262.719999999998</v>
       </c>
       <c r="K26" s="88">
         <f t="shared" si="3"/>
-        <v>320803.38</v>
-      </c>
-      <c r="L26" s="166">
+        <v>391182</v>
+      </c>
+      <c r="L26" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M26" s="6">
         <f t="shared" si="5"/>
-        <v>-352713.925683963</v>
+        <v>-556256.30998396303</v>
       </c>
       <c r="N26" s="11">
         <f t="shared" si="1"/>
-        <v>-373876.76122500078</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+        <v>-589631.6885830008</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>62</v>
       </c>
@@ -5323,41 +5766,41 @@
         <v>5.89</v>
       </c>
       <c r="F27" s="88">
-        <v>409312.03689526557</v>
-      </c>
-      <c r="G27" s="196">
-        <f>489924-G39-G40</f>
-        <v>409312.44886</v>
+        <v>314921.57273526554</v>
+      </c>
+      <c r="G27" s="191">
+        <f>377000-G39-G40</f>
+        <v>314978.01319999999</v>
       </c>
       <c r="H27" s="131">
         <f t="shared" si="0"/>
-        <v>-0.41196473443415016</v>
+        <v>-56.440464734449051</v>
       </c>
       <c r="I27" s="106">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J27" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>19891.236799999999</v>
       </c>
       <c r="K27" s="88">
         <f t="shared" si="3"/>
-        <v>314921.98469999997</v>
-      </c>
-      <c r="L27" s="166">
+        <v>384010.33</v>
+      </c>
+      <c r="L27" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M27" s="6">
         <f t="shared" si="5"/>
-        <v>314921.57273526554</v>
+        <v>403845.12633526558</v>
       </c>
       <c r="N27" s="11">
         <f t="shared" si="1"/>
-        <v>333816.86709938146</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+        <v>428075.83391538152</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>64</v>
       </c>
@@ -5372,41 +5815,41 @@
         <v>5.89</v>
       </c>
       <c r="F28" s="88">
-        <v>408702.15158654092</v>
-      </c>
-      <c r="G28" s="196">
-        <f>483000-G32-G33</f>
-        <v>409337.72051000001</v>
+        <v>314286.41577654087</v>
+      </c>
+      <c r="G28" s="191">
+        <f>371000-G32-G33+RESUMEN!D73</f>
+        <v>413583.78619999997</v>
       </c>
       <c r="H28" s="131">
         <f t="shared" si="0"/>
-        <v>-635.56892345909728</v>
+        <v>-99297.370423459099</v>
       </c>
       <c r="I28" s="106">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>19891.236799999999</v>
       </c>
       <c r="K28" s="88">
         <f t="shared" si="3"/>
-        <v>314921.98469999997</v>
-      </c>
-      <c r="L28" s="166">
+        <v>384010.33</v>
+      </c>
+      <c r="L28" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M28" s="6">
         <f t="shared" si="5"/>
-        <v>314286.41577654087</v>
+        <v>304604.19637654093</v>
       </c>
       <c r="N28" s="11">
         <f t="shared" si="1"/>
-        <v>333143.60072313331</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+        <v>322880.44815913338</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>66</v>
       </c>
@@ -5421,41 +5864,41 @@
         <v>5.89</v>
       </c>
       <c r="F29" s="88">
-        <v>420685.1128917</v>
-      </c>
-      <c r="G29" s="197">
-        <f>522000-G42-G43-G44</f>
-        <v>410116.72643500002</v>
+        <v>325490.37115669996</v>
+      </c>
+      <c r="G29" s="192">
+        <f>401000-G42-G43-G44+RESUMEN!D72</f>
+        <v>413311.71970000002</v>
       </c>
       <c r="H29" s="132">
         <f t="shared" si="0"/>
-        <v>10568.386456699984</v>
+        <v>-87821.348543300061</v>
       </c>
       <c r="I29" s="106">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J29" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>19891.236799999999</v>
       </c>
       <c r="K29" s="88">
         <f t="shared" si="3"/>
-        <v>314921.98469999997</v>
-      </c>
-      <c r="L29" s="166">
+        <v>384010.33</v>
+      </c>
+      <c r="L29" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M29" s="6">
         <f t="shared" si="5"/>
-        <v>325490.37115669996</v>
+        <v>316080.21825669997</v>
       </c>
       <c r="N29" s="11">
         <f t="shared" si="1"/>
-        <v>345019.79342610197</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+        <v>335045.03135210194</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="126" t="s">
         <v>97</v>
       </c>
@@ -5470,11 +5913,11 @@
         <v>0.54</v>
       </c>
       <c r="F30" s="88">
-        <v>37526.066910000001</v>
-      </c>
-      <c r="G30" s="196">
+        <v>28872.304200000002</v>
+      </c>
+      <c r="G30" s="191">
         <f t="shared" ref="G30:G34" si="6">F30</f>
-        <v>37526.066910000001</v>
+        <v>28872.304200000002</v>
       </c>
       <c r="H30" s="131">
         <f t="shared" si="0"/>
@@ -5483,26 +5926,26 @@
       <c r="I30" s="106"/>
       <c r="J30" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1823.6448</v>
       </c>
       <c r="K30" s="88">
         <f t="shared" si="3"/>
-        <v>28872.304200000002</v>
-      </c>
-      <c r="L30" s="166">
+        <v>35206.379999999997</v>
+      </c>
+      <c r="L30" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M30" s="6">
         <f t="shared" si="5"/>
-        <v>28872.304200000002</v>
+        <v>37030.024799999999</v>
       </c>
       <c r="N30" s="11">
         <f t="shared" si="1"/>
-        <v>30604.642452000004</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+        <v>39251.826287999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="126" t="s">
         <v>97</v>
       </c>
@@ -5517,11 +5960,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F31" s="88">
-        <v>38220.994075000002</v>
-      </c>
-      <c r="G31" s="196">
+        <v>29406.976500000004</v>
+      </c>
+      <c r="G31" s="191">
         <f t="shared" si="6"/>
-        <v>38220.994075000002</v>
+        <v>29406.976500000004</v>
       </c>
       <c r="H31" s="131">
         <f t="shared" si="0"/>
@@ -5530,26 +5973,26 @@
       <c r="I31" s="106"/>
       <c r="J31" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1857.4160000000002</v>
       </c>
       <c r="K31" s="88">
         <f t="shared" si="3"/>
-        <v>29406.976500000004</v>
-      </c>
-      <c r="L31" s="166">
+        <v>35858.350000000006</v>
+      </c>
+      <c r="L31" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M31" s="6">
         <f t="shared" si="5"/>
-        <v>29406.976500000004</v>
+        <v>37715.766000000003</v>
       </c>
       <c r="N31" s="11">
         <f t="shared" si="1"/>
-        <v>31171.395090000005</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+        <v>39978.711960000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="126" t="s">
         <v>97</v>
       </c>
@@ -5564,11 +6007,11 @@
         <v>0.45</v>
       </c>
       <c r="F32" s="88">
-        <v>31271.722424999996</v>
-      </c>
-      <c r="G32" s="196">
+        <v>24060.253500000003</v>
+      </c>
+      <c r="G32" s="191">
         <f>F32</f>
-        <v>31271.722424999996</v>
+        <v>24060.253500000003</v>
       </c>
       <c r="H32" s="131">
         <f t="shared" si="0"/>
@@ -5577,26 +6020,26 @@
       <c r="I32" s="106"/>
       <c r="J32" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1519.7040000000002</v>
       </c>
       <c r="K32" s="88">
         <f t="shared" si="3"/>
-        <v>24060.253500000003</v>
-      </c>
-      <c r="L32" s="166">
+        <v>29338.65</v>
+      </c>
+      <c r="L32" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M32" s="6">
         <f t="shared" si="5"/>
-        <v>24060.253500000003</v>
+        <v>30858.354000000003</v>
       </c>
       <c r="N32" s="11">
         <f t="shared" si="1"/>
-        <v>25503.868710000002</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+        <v>32709.855240000004</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="126" t="s">
         <v>97</v>
       </c>
@@ -5611,11 +6054,11 @@
         <v>0.61</v>
       </c>
       <c r="F33" s="88">
-        <v>42390.557064999994</v>
-      </c>
-      <c r="G33" s="196">
+        <v>32615.010299999998</v>
+      </c>
+      <c r="G33" s="191">
         <f t="shared" si="6"/>
-        <v>42390.557064999994</v>
+        <v>32615.010299999998</v>
       </c>
       <c r="H33" s="131">
         <f t="shared" si="0"/>
@@ -5624,26 +6067,26 @@
       <c r="I33" s="106"/>
       <c r="J33" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2060.0431999999996</v>
       </c>
       <c r="K33" s="88">
         <f t="shared" si="3"/>
-        <v>32615.010299999998</v>
-      </c>
-      <c r="L33" s="166">
+        <v>39770.17</v>
+      </c>
+      <c r="L33" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M33" s="6">
         <f t="shared" si="5"/>
-        <v>32615.010299999998</v>
+        <v>41830.213199999998</v>
       </c>
       <c r="N33" s="11">
         <f t="shared" si="1"/>
-        <v>34571.910918000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+        <v>44340.025991999995</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="126" t="s">
         <v>97</v>
       </c>
@@ -5658,11 +6101,11 @@
         <v>0.54</v>
       </c>
       <c r="F34" s="88">
-        <v>37526.066910000001</v>
-      </c>
-      <c r="G34" s="196">
+        <v>28872.304200000002</v>
+      </c>
+      <c r="G34" s="191">
         <f t="shared" si="6"/>
-        <v>37526.066910000001</v>
+        <v>28872.304200000002</v>
       </c>
       <c r="H34" s="131">
         <f t="shared" si="0"/>
@@ -5671,26 +6114,26 @@
       <c r="I34" s="106"/>
       <c r="J34" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1823.6448</v>
       </c>
       <c r="K34" s="88">
         <f t="shared" si="3"/>
-        <v>28872.304200000002</v>
-      </c>
-      <c r="L34" s="166">
+        <v>35206.379999999997</v>
+      </c>
+      <c r="L34" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M34" s="6">
         <f t="shared" si="5"/>
-        <v>28872.304200000002</v>
+        <v>37030.024799999999</v>
       </c>
       <c r="N34" s="11">
         <f t="shared" si="1"/>
-        <v>30604.642452000004</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+        <v>39251.826287999997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="126" t="s">
         <v>97</v>
       </c>
@@ -5705,11 +6148,11 @@
         <v>0.5</v>
       </c>
       <c r="F35" s="11">
-        <v>36831.139745</v>
-      </c>
-      <c r="G35" s="197">
+        <v>26733.615000000002</v>
+      </c>
+      <c r="G35" s="192">
         <f>F35</f>
-        <v>36831.139745</v>
+        <v>26733.615000000002</v>
       </c>
       <c r="H35" s="131">
         <f t="shared" si="0"/>
@@ -5718,26 +6161,26 @@
       <c r="I35" s="106"/>
       <c r="J35" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1688.56</v>
       </c>
       <c r="K35" s="88">
         <f t="shared" si="3"/>
-        <v>26733.615000000002</v>
-      </c>
-      <c r="L35" s="166">
+        <v>32598.5</v>
+      </c>
+      <c r="L35" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M35" s="6">
         <f t="shared" si="5"/>
-        <v>26733.615000000002</v>
+        <v>34287.06</v>
       </c>
       <c r="N35" s="11">
         <f t="shared" si="1"/>
-        <v>28337.6319</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+        <v>36344.283599999995</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="126" t="s">
         <v>97</v>
       </c>
@@ -5752,11 +6195,11 @@
         <v>0.5</v>
       </c>
       <c r="F36" s="88">
-        <v>34746.358249999997</v>
-      </c>
-      <c r="G36" s="196">
+        <v>26733.615000000002</v>
+      </c>
+      <c r="G36" s="191">
         <f t="shared" ref="G36:G41" si="7">F36</f>
-        <v>34746.358249999997</v>
+        <v>26733.615000000002</v>
       </c>
       <c r="H36" s="131">
         <f t="shared" si="0"/>
@@ -5765,26 +6208,26 @@
       <c r="I36" s="106"/>
       <c r="J36" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1688.56</v>
       </c>
       <c r="K36" s="88">
         <f t="shared" si="3"/>
-        <v>26733.615000000002</v>
-      </c>
-      <c r="L36" s="166">
+        <v>32598.5</v>
+      </c>
+      <c r="L36" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M36" s="6">
         <f t="shared" si="5"/>
-        <v>26733.615000000002</v>
+        <v>34287.06</v>
       </c>
       <c r="N36" s="11">
         <f t="shared" si="1"/>
-        <v>28337.6319</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+        <v>36344.283599999995</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="126" t="s">
         <v>97</v>
       </c>
@@ -5799,11 +6242,11 @@
         <v>0.49</v>
       </c>
       <c r="F37" s="88">
-        <v>34051.431084999997</v>
-      </c>
-      <c r="G37" s="196">
+        <v>26198.9427</v>
+      </c>
+      <c r="G37" s="191">
         <f t="shared" si="7"/>
-        <v>34051.431084999997</v>
+        <v>26198.9427</v>
       </c>
       <c r="H37" s="131">
         <f t="shared" si="0"/>
@@ -5812,26 +6255,26 @@
       <c r="I37" s="106"/>
       <c r="J37" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1654.7888</v>
       </c>
       <c r="K37" s="88">
         <f t="shared" si="3"/>
-        <v>26198.9427</v>
-      </c>
-      <c r="L37" s="166">
+        <v>31946.53</v>
+      </c>
+      <c r="L37" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M37" s="6">
         <f t="shared" si="5"/>
-        <v>26198.9427</v>
+        <v>33601.318800000001</v>
       </c>
       <c r="N37" s="11">
         <f t="shared" si="1"/>
-        <v>27770.879261999999</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+        <v>35617.397927999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="126" t="s">
         <v>97</v>
       </c>
@@ -5846,11 +6289,11 @@
         <v>0.49</v>
       </c>
       <c r="F38" s="88">
-        <v>34051.431084999997</v>
-      </c>
-      <c r="G38" s="196">
+        <v>26198.9427</v>
+      </c>
+      <c r="G38" s="191">
         <f t="shared" si="7"/>
-        <v>34051.431084999997</v>
+        <v>26198.9427</v>
       </c>
       <c r="H38" s="131">
         <f t="shared" si="0"/>
@@ -5859,26 +6302,26 @@
       <c r="I38" s="106"/>
       <c r="J38" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1654.7888</v>
       </c>
       <c r="K38" s="88">
         <f t="shared" si="3"/>
-        <v>26198.9427</v>
-      </c>
-      <c r="L38" s="166">
+        <v>31946.53</v>
+      </c>
+      <c r="L38" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M38" s="6">
         <f t="shared" si="5"/>
-        <v>26198.9427</v>
+        <v>33601.318800000001</v>
       </c>
       <c r="N38" s="11">
         <f t="shared" si="1"/>
-        <v>27770.879261999999</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+        <v>35617.397927999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="126" t="s">
         <v>97</v>
       </c>
@@ -5893,11 +6336,11 @@
         <v>0.59</v>
       </c>
       <c r="F39" s="88">
-        <v>41000.702734999999</v>
-      </c>
-      <c r="G39" s="196">
+        <v>31545.665699999998</v>
+      </c>
+      <c r="G39" s="191">
         <f t="shared" si="7"/>
-        <v>41000.702734999999</v>
+        <v>31545.665699999998</v>
       </c>
       <c r="H39" s="131">
         <f t="shared" si="0"/>
@@ -5906,26 +6349,26 @@
       <c r="I39" s="106"/>
       <c r="J39" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1992.5008</v>
       </c>
       <c r="K39" s="88">
         <f t="shared" si="3"/>
-        <v>31545.665699999998</v>
-      </c>
-      <c r="L39" s="166">
+        <v>38466.230000000003</v>
+      </c>
+      <c r="L39" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M39" s="6">
         <f t="shared" si="5"/>
-        <v>31545.665699999998</v>
+        <v>40458.730800000005</v>
       </c>
       <c r="N39" s="11">
         <f t="shared" si="1"/>
-        <v>33438.405641999998</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+        <v>42886.254648000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="126" t="s">
         <v>97</v>
       </c>
@@ -5940,11 +6383,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F40" s="88">
-        <v>39610.848404999997</v>
-      </c>
-      <c r="G40" s="196">
+        <v>30476.321099999997</v>
+      </c>
+      <c r="G40" s="191">
         <f t="shared" si="7"/>
-        <v>39610.848404999997</v>
+        <v>30476.321099999997</v>
       </c>
       <c r="H40" s="131">
         <f t="shared" si="0"/>
@@ -5953,26 +6396,26 @@
       <c r="I40" s="106"/>
       <c r="J40" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1924.9583999999998</v>
       </c>
       <c r="K40" s="88">
         <f t="shared" si="3"/>
-        <v>30476.321099999997</v>
-      </c>
-      <c r="L40" s="166">
+        <v>37162.289999999994</v>
+      </c>
+      <c r="L40" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M40" s="6">
         <f t="shared" si="5"/>
-        <v>30476.321099999997</v>
+        <v>39087.248399999997</v>
       </c>
       <c r="N40" s="11">
         <f t="shared" si="1"/>
-        <v>32304.900365999998</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+        <v>41432.483303999994</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="126" t="s">
         <v>97</v>
       </c>
@@ -5987,11 +6430,11 @@
         <v>0.54</v>
       </c>
       <c r="F41" s="88">
-        <v>37526.066910000001</v>
-      </c>
-      <c r="G41" s="196">
+        <v>28872.304200000002</v>
+      </c>
+      <c r="G41" s="191">
         <f t="shared" si="7"/>
-        <v>37526.066910000001</v>
+        <v>28872.304200000002</v>
       </c>
       <c r="H41" s="131">
         <f t="shared" si="0"/>
@@ -6000,26 +6443,26 @@
       <c r="I41" s="106"/>
       <c r="J41" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1823.6448</v>
       </c>
       <c r="K41" s="88">
         <f t="shared" si="3"/>
-        <v>28872.304200000002</v>
-      </c>
-      <c r="L41" s="166">
+        <v>35206.379999999997</v>
+      </c>
+      <c r="L41" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M41" s="6">
         <f t="shared" si="5"/>
-        <v>28872.304200000002</v>
+        <v>37030.024799999999</v>
       </c>
       <c r="N41" s="11">
         <f t="shared" si="1"/>
-        <v>30604.642452000004</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+        <v>39251.826287999997</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="126" t="s">
         <v>97</v>
       </c>
@@ -6034,11 +6477,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F42" s="88">
-        <v>38220.994075000002</v>
-      </c>
-      <c r="G42" s="196">
+        <v>29406.976500000004</v>
+      </c>
+      <c r="G42" s="191">
         <f>F42</f>
-        <v>38220.994075000002</v>
+        <v>29406.976500000004</v>
       </c>
       <c r="H42" s="131">
         <f t="shared" si="0"/>
@@ -6047,26 +6490,26 @@
       <c r="I42" s="106"/>
       <c r="J42" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1857.4160000000002</v>
       </c>
       <c r="K42" s="88">
         <f t="shared" si="3"/>
-        <v>29406.976500000004</v>
-      </c>
-      <c r="L42" s="166">
+        <v>35858.350000000006</v>
+      </c>
+      <c r="L42" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M42" s="6">
         <f t="shared" si="5"/>
-        <v>29406.976500000004</v>
+        <v>37715.766000000003</v>
       </c>
       <c r="N42" s="11">
         <f t="shared" si="1"/>
-        <v>31171.395090000005</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+        <v>39978.711960000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="126" t="s">
         <v>97</v>
       </c>
@@ -6081,11 +6524,11 @@
         <v>0.45</v>
       </c>
       <c r="F43" s="88">
-        <v>31271.722424999996</v>
-      </c>
-      <c r="G43" s="196">
+        <v>24060.253500000003</v>
+      </c>
+      <c r="G43" s="191">
         <f t="shared" ref="G43:G44" si="8">F43</f>
-        <v>31271.722424999996</v>
+        <v>24060.253500000003</v>
       </c>
       <c r="H43" s="131">
         <f t="shared" si="0"/>
@@ -6094,30 +6537,30 @@
       <c r="I43" s="106"/>
       <c r="J43" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1519.7040000000002</v>
       </c>
       <c r="K43" s="88">
         <f t="shared" si="3"/>
-        <v>24060.253500000003</v>
-      </c>
-      <c r="L43" s="166">
+        <v>29338.65</v>
+      </c>
+      <c r="L43" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M43" s="6">
         <f t="shared" si="5"/>
-        <v>24060.253500000003</v>
+        <v>30858.354000000003</v>
       </c>
       <c r="N43" s="11">
         <f t="shared" si="1"/>
-        <v>25503.868710000002</v>
+        <v>32709.855240000004</v>
       </c>
       <c r="P43" s="109">
         <f>L1-K52</f>
-        <v>753288.9310490014</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+        <v>1105640.362077998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="126" t="s">
         <v>97</v>
       </c>
@@ -6132,11 +6575,11 @@
         <v>0.61</v>
       </c>
       <c r="F44" s="88">
-        <v>42390.557064999994</v>
-      </c>
-      <c r="G44" s="196">
+        <v>32615.010299999998</v>
+      </c>
+      <c r="G44" s="191">
         <f t="shared" si="8"/>
-        <v>42390.557064999994</v>
+        <v>32615.010299999998</v>
       </c>
       <c r="H44" s="131">
         <f t="shared" si="0"/>
@@ -6145,26 +6588,26 @@
       <c r="I44" s="106"/>
       <c r="J44" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2060.0431999999996</v>
       </c>
       <c r="K44" s="88">
         <f t="shared" si="3"/>
-        <v>32615.010299999998</v>
-      </c>
-      <c r="L44" s="166">
+        <v>39770.17</v>
+      </c>
+      <c r="L44" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M44" s="6">
         <f t="shared" si="5"/>
-        <v>32615.010299999998</v>
+        <v>41830.213199999998</v>
       </c>
       <c r="N44" s="11">
         <f t="shared" si="1"/>
-        <v>34571.910918000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+        <v>44340.025991999995</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="126" t="s">
         <v>97</v>
       </c>
@@ -6179,11 +6622,11 @@
         <v>0.54</v>
       </c>
       <c r="F45" s="88">
-        <v>37526.066910000001</v>
-      </c>
-      <c r="G45" s="196">
+        <v>28872.304200000002</v>
+      </c>
+      <c r="G45" s="191">
         <f t="shared" ref="G45:G51" si="9">F45</f>
-        <v>37526.066910000001</v>
+        <v>28872.304200000002</v>
       </c>
       <c r="H45" s="131">
         <f t="shared" si="0"/>
@@ -6192,26 +6635,26 @@
       <c r="I45" s="106"/>
       <c r="J45" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1823.6448</v>
       </c>
       <c r="K45" s="88">
         <f t="shared" si="3"/>
-        <v>28872.304200000002</v>
-      </c>
-      <c r="L45" s="166">
+        <v>35206.379999999997</v>
+      </c>
+      <c r="L45" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M45" s="6">
         <f t="shared" si="5"/>
-        <v>28872.304200000002</v>
+        <v>37030.024799999999</v>
       </c>
       <c r="N45" s="11">
         <f t="shared" si="1"/>
-        <v>30604.642452000004</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+        <v>39251.826287999997</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="126" t="s">
         <v>97</v>
       </c>
@@ -6226,39 +6669,42 @@
         <v>0.5</v>
       </c>
       <c r="F46" s="88">
-        <v>34746.358249999997</v>
-      </c>
-      <c r="G46" s="196"/>
+        <v>61479.973249999995</v>
+      </c>
+      <c r="G46" s="191">
+        <f>F46</f>
+        <v>61479.973249999995</v>
+      </c>
       <c r="H46" s="131">
         <f t="shared" si="0"/>
-        <v>34746.358249999997</v>
+        <v>0</v>
       </c>
       <c r="I46" s="106"/>
       <c r="J46" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1688.56</v>
       </c>
       <c r="K46" s="88">
         <f t="shared" si="3"/>
-        <v>26733.615000000002</v>
-      </c>
-      <c r="L46" s="166">
+        <v>32598.5</v>
+      </c>
+      <c r="L46" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M46" s="6">
         <f t="shared" si="5"/>
-        <v>61479.973249999995</v>
+        <v>34287.06</v>
       </c>
       <c r="N46" s="11">
         <f t="shared" si="1"/>
-        <v>65168.771644999993</v>
+        <v>36344.283599999995</v>
       </c>
       <c r="Q46" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="126" t="s">
         <v>97</v>
       </c>
@@ -6273,11 +6719,11 @@
         <v>0.5</v>
       </c>
       <c r="F47" s="88">
-        <v>36831.139745</v>
-      </c>
-      <c r="G47" s="196">
+        <v>28337.6319</v>
+      </c>
+      <c r="G47" s="191">
         <f t="shared" si="9"/>
-        <v>36831.139745</v>
+        <v>28337.6319</v>
       </c>
       <c r="H47" s="131">
         <f t="shared" si="0"/>
@@ -6286,31 +6732,31 @@
       <c r="I47" s="106"/>
       <c r="J47" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1688.56</v>
       </c>
       <c r="K47" s="88">
         <f t="shared" si="3"/>
-        <v>26733.615000000002</v>
-      </c>
-      <c r="L47" s="166">
+        <v>32598.5</v>
+      </c>
+      <c r="L47" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M47" s="6">
         <f t="shared" si="5"/>
-        <v>26733.615000000002</v>
+        <v>34287.06</v>
       </c>
       <c r="N47" s="11">
         <f t="shared" si="1"/>
-        <v>28337.6319</v>
+        <v>36344.283599999995</v>
       </c>
       <c r="O47" s="138"/>
       <c r="Q47" s="135">
         <f>M3-J52</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0.14079999987734482</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="126" t="s">
         <v>97</v>
       </c>
@@ -6325,11 +6771,11 @@
         <v>0.49</v>
       </c>
       <c r="F48" s="88">
-        <v>36094.516950099998</v>
-      </c>
-      <c r="G48" s="196">
+        <v>27770.879261999999</v>
+      </c>
+      <c r="G48" s="191">
         <f t="shared" si="9"/>
-        <v>36094.516950099998</v>
+        <v>27770.879261999999</v>
       </c>
       <c r="H48" s="131">
         <f t="shared" si="0"/>
@@ -6338,26 +6784,26 @@
       <c r="I48" s="106"/>
       <c r="J48" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1654.7888</v>
       </c>
       <c r="K48" s="88">
         <f t="shared" si="3"/>
-        <v>26198.9427</v>
-      </c>
-      <c r="L48" s="166">
+        <v>31946.53</v>
+      </c>
+      <c r="L48" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M48" s="6">
         <f t="shared" si="5"/>
-        <v>26198.9427</v>
+        <v>33601.318800000001</v>
       </c>
       <c r="N48" s="11">
         <f t="shared" si="1"/>
-        <v>27770.879261999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+        <v>35617.397927999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="126" t="s">
         <v>97</v>
       </c>
@@ -6373,11 +6819,11 @@
         <v>0.49</v>
       </c>
       <c r="F49" s="88">
-        <v>34051.431084999997</v>
-      </c>
-      <c r="G49" s="196">
+        <v>26198.9427</v>
+      </c>
+      <c r="G49" s="191">
         <f>F49</f>
-        <v>34051.431084999997</v>
+        <v>26198.9427</v>
       </c>
       <c r="H49" s="131">
         <f t="shared" si="0"/>
@@ -6386,26 +6832,26 @@
       <c r="I49" s="106"/>
       <c r="J49" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1654.7888</v>
       </c>
       <c r="K49" s="88">
         <f t="shared" si="3"/>
-        <v>26198.9427</v>
-      </c>
-      <c r="L49" s="166">
+        <v>31946.53</v>
+      </c>
+      <c r="L49" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M49" s="6">
         <f t="shared" si="5"/>
-        <v>26198.9427</v>
+        <v>33601.318800000001</v>
       </c>
       <c r="N49" s="11">
         <f t="shared" si="1"/>
-        <v>27770.879261999999</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+        <v>35617.397927999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="126" t="s">
         <v>97</v>
       </c>
@@ -6420,11 +6866,11 @@
         <v>0.59</v>
       </c>
       <c r="F50" s="88">
-        <v>41000.702734999999</v>
-      </c>
-      <c r="G50" s="197">
+        <v>31545.665699999998</v>
+      </c>
+      <c r="G50" s="192">
         <f>F50</f>
-        <v>41000.702734999999</v>
+        <v>31545.665699999998</v>
       </c>
       <c r="H50" s="131">
         <f t="shared" si="0"/>
@@ -6433,26 +6879,26 @@
       <c r="I50" s="106"/>
       <c r="J50" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1992.5008</v>
       </c>
       <c r="K50" s="88">
         <f t="shared" si="3"/>
-        <v>31545.665699999998</v>
-      </c>
-      <c r="L50" s="166">
+        <v>38466.230000000003</v>
+      </c>
+      <c r="L50" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M50" s="6">
         <f t="shared" si="5"/>
-        <v>31545.665699999998</v>
+        <v>40458.730800000005</v>
       </c>
       <c r="N50" s="11">
         <f t="shared" si="1"/>
-        <v>33438.405641999998</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+        <v>42886.254648000002</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="126" t="s">
         <v>97</v>
       </c>
@@ -6467,11 +6913,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F51" s="88">
-        <v>39610.848404999997</v>
-      </c>
-      <c r="G51" s="196">
+        <v>30476.321099999997</v>
+      </c>
+      <c r="G51" s="191">
         <f t="shared" si="9"/>
-        <v>39610.848404999997</v>
+        <v>30476.321099999997</v>
       </c>
       <c r="H51" s="131">
         <f t="shared" si="0"/>
@@ -6480,26 +6926,26 @@
       <c r="I51" s="106"/>
       <c r="J51" s="88">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1924.9583999999998</v>
       </c>
       <c r="K51" s="88">
         <f t="shared" si="3"/>
-        <v>30476.321099999997</v>
-      </c>
-      <c r="L51" s="166">
+        <v>37162.289999999994</v>
+      </c>
+      <c r="L51" s="165">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M51" s="6">
         <f t="shared" si="5"/>
-        <v>30476.321099999997</v>
+        <v>39087.248399999997</v>
       </c>
       <c r="N51" s="11">
         <f t="shared" si="1"/>
-        <v>32304.900365999998</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>41432.483303999994</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="89"/>
       <c r="B52" s="89"/>
       <c r="C52" s="89"/>
@@ -6510,191 +6956,186 @@
       </c>
       <c r="F52" s="90">
         <f>SUM(F7:F51)</f>
-        <v>6502504.5722166849</v>
+        <v>4929008.8575203009</v>
       </c>
       <c r="G52" s="90">
         <f>SUM(G7:G51)</f>
-        <v>6849105.1357215978</v>
+        <v>6320855.3670509998</v>
       </c>
       <c r="H52" s="89"/>
       <c r="I52" s="89"/>
       <c r="J52" s="127">
         <f>SUM(J8:J51)</f>
-        <v>0</v>
+        <v>310391.09920000011</v>
       </c>
       <c r="K52" s="90">
         <f>SUM(K7:K51)</f>
-        <v>5245103.4089509984</v>
-      </c>
-      <c r="L52" s="177">
+        <v>6390688.0079220012</v>
+      </c>
+      <c r="L52" s="174">
         <f>SUM(L7:L51)</f>
-        <v>15184.7</v>
+        <v>20000</v>
       </c>
       <c r="M52" s="91">
         <f>SUM(M7:M51)</f>
-        <v>4913687.5454460867</v>
+        <v>5354343.2489072988</v>
       </c>
       <c r="N52" s="90">
         <f>SUM(N7:N51)</f>
-        <v>5208508.7981728548</v>
+        <v>5675603.843841739</v>
       </c>
       <c r="P52" s="135"/>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="K53" s="138">
         <f>K52-L1</f>
-        <v>-753288.9310490014</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="205"/>
-      <c r="D54" s="205"/>
-      <c r="E54" s="205"/>
-      <c r="F54" s="205"/>
-      <c r="G54" s="205"/>
-      <c r="H54" s="205"/>
-      <c r="I54" s="205"/>
-      <c r="J54" s="205"/>
-      <c r="K54" s="205"/>
-      <c r="L54" s="205"/>
-      <c r="M54" s="205"/>
-      <c r="N54" s="205"/>
-    </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="205"/>
-      <c r="D55" s="205"/>
-      <c r="E55" s="205"/>
-      <c r="F55" s="205"/>
-      <c r="G55" s="205"/>
-      <c r="H55" s="205"/>
-      <c r="I55" s="205"/>
-      <c r="J55" s="205"/>
-      <c r="K55" s="205"/>
-      <c r="L55" s="205"/>
-      <c r="M55" s="205"/>
-      <c r="N55" s="205"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C56" s="169"/>
-      <c r="D56" s="169"/>
-      <c r="E56" s="169"/>
-      <c r="F56" s="169"/>
-      <c r="G56" s="169"/>
-      <c r="H56" s="169"/>
-      <c r="I56" s="169"/>
-      <c r="J56" s="169"/>
-      <c r="K56" s="169"/>
-      <c r="L56" s="169"/>
-      <c r="M56" s="169"/>
-      <c r="N56" s="169"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C57" s="205" t="s">
+        <v>-1105640.362077998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="239"/>
+      <c r="D54" s="239"/>
+      <c r="E54" s="239"/>
+      <c r="F54" s="239"/>
+      <c r="G54" s="239"/>
+      <c r="H54" s="239"/>
+      <c r="I54" s="239"/>
+      <c r="J54" s="239"/>
+      <c r="K54" s="239"/>
+      <c r="L54" s="239"/>
+      <c r="M54" s="239"/>
+      <c r="N54" s="239"/>
+    </row>
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="239"/>
+      <c r="D55" s="239"/>
+      <c r="E55" s="239"/>
+      <c r="F55" s="239"/>
+      <c r="G55" s="239"/>
+      <c r="H55" s="239"/>
+      <c r="I55" s="239"/>
+      <c r="J55" s="239"/>
+      <c r="K55" s="239"/>
+      <c r="L55" s="239"/>
+      <c r="M55" s="239"/>
+      <c r="N55" s="239"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C56" s="168"/>
+      <c r="D56" s="168"/>
+      <c r="E56" s="168"/>
+      <c r="F56" s="168"/>
+      <c r="G56" s="168"/>
+      <c r="H56" s="168"/>
+      <c r="I56" s="168"/>
+      <c r="J56" s="168"/>
+      <c r="K56" s="168"/>
+      <c r="L56" s="168"/>
+      <c r="M56" s="168"/>
+      <c r="N56" s="168"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C57" s="239" t="s">
         <v>130</v>
       </c>
-      <c r="D57" s="205"/>
-      <c r="E57" s="205"/>
-      <c r="F57" s="205"/>
-      <c r="G57" s="205"/>
-      <c r="H57" s="205"/>
-      <c r="I57" s="205"/>
-      <c r="J57" s="205"/>
-      <c r="K57" s="205"/>
-      <c r="L57" s="205"/>
-      <c r="M57" s="205"/>
-      <c r="N57" s="205"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C58" s="205"/>
-      <c r="D58" s="205"/>
-      <c r="E58" s="205"/>
-      <c r="F58" s="205"/>
-      <c r="G58" s="205"/>
-      <c r="H58" s="205"/>
-      <c r="I58" s="205"/>
-      <c r="J58" s="205"/>
-      <c r="K58" s="205"/>
-      <c r="L58" s="205"/>
-      <c r="M58" s="205"/>
-      <c r="N58" s="205"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C59" s="205"/>
-      <c r="D59" s="205"/>
-      <c r="E59" s="205"/>
-      <c r="F59" s="205"/>
-      <c r="G59" s="205"/>
-      <c r="H59" s="205"/>
-      <c r="I59" s="205"/>
-      <c r="J59" s="205"/>
-      <c r="K59" s="205"/>
-      <c r="L59" s="205"/>
-      <c r="M59" s="205"/>
-      <c r="N59" s="205"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C60" s="205"/>
-      <c r="D60" s="205"/>
-      <c r="E60" s="205"/>
-      <c r="F60" s="205"/>
-      <c r="G60" s="205"/>
-      <c r="H60" s="205"/>
-      <c r="I60" s="205"/>
-      <c r="J60" s="205"/>
-      <c r="K60" s="205"/>
-      <c r="L60" s="205"/>
-      <c r="M60" s="205"/>
-      <c r="N60" s="205"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C61" s="205"/>
-      <c r="D61" s="205"/>
-      <c r="E61" s="205"/>
-      <c r="F61" s="205"/>
-      <c r="G61" s="205"/>
-      <c r="H61" s="205"/>
-      <c r="I61" s="205"/>
-      <c r="J61" s="205"/>
-      <c r="K61" s="205"/>
-      <c r="L61" s="205"/>
-      <c r="M61" s="205"/>
-      <c r="N61" s="205"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C62" s="205"/>
-      <c r="D62" s="205"/>
-      <c r="E62" s="205"/>
-      <c r="F62" s="205"/>
-      <c r="G62" s="205"/>
-      <c r="H62" s="205"/>
-      <c r="I62" s="205"/>
-      <c r="J62" s="205"/>
-      <c r="K62" s="205"/>
-      <c r="L62" s="205"/>
-      <c r="M62" s="205"/>
-      <c r="N62" s="205"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C63" s="205"/>
-      <c r="D63" s="205"/>
-      <c r="E63" s="205"/>
-      <c r="F63" s="205"/>
-      <c r="G63" s="205"/>
-      <c r="H63" s="205"/>
-      <c r="I63" s="205"/>
-      <c r="J63" s="205"/>
-      <c r="K63" s="205"/>
-      <c r="L63" s="205"/>
-      <c r="M63" s="205"/>
-      <c r="N63" s="205"/>
+      <c r="D57" s="239"/>
+      <c r="E57" s="239"/>
+      <c r="F57" s="239"/>
+      <c r="G57" s="239"/>
+      <c r="H57" s="239"/>
+      <c r="I57" s="239"/>
+      <c r="J57" s="239"/>
+      <c r="K57" s="239"/>
+      <c r="L57" s="239"/>
+      <c r="M57" s="239"/>
+      <c r="N57" s="239"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C58" s="239"/>
+      <c r="D58" s="239"/>
+      <c r="E58" s="239"/>
+      <c r="F58" s="239"/>
+      <c r="G58" s="239"/>
+      <c r="H58" s="239"/>
+      <c r="I58" s="239"/>
+      <c r="J58" s="239"/>
+      <c r="K58" s="239"/>
+      <c r="L58" s="239"/>
+      <c r="M58" s="239"/>
+      <c r="N58" s="239"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C59" s="239"/>
+      <c r="D59" s="239"/>
+      <c r="E59" s="239"/>
+      <c r="F59" s="239"/>
+      <c r="G59" s="239"/>
+      <c r="H59" s="239"/>
+      <c r="I59" s="239"/>
+      <c r="J59" s="239"/>
+      <c r="K59" s="239"/>
+      <c r="L59" s="239"/>
+      <c r="M59" s="239"/>
+      <c r="N59" s="239"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C60" s="239"/>
+      <c r="D60" s="239"/>
+      <c r="E60" s="239"/>
+      <c r="F60" s="239"/>
+      <c r="G60" s="239"/>
+      <c r="H60" s="239"/>
+      <c r="I60" s="239"/>
+      <c r="J60" s="239"/>
+      <c r="K60" s="239"/>
+      <c r="L60" s="239"/>
+      <c r="M60" s="239"/>
+      <c r="N60" s="239"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C61" s="239"/>
+      <c r="D61" s="239"/>
+      <c r="E61" s="239"/>
+      <c r="F61" s="239"/>
+      <c r="G61" s="239"/>
+      <c r="H61" s="239"/>
+      <c r="I61" s="239"/>
+      <c r="J61" s="239"/>
+      <c r="K61" s="239"/>
+      <c r="L61" s="239"/>
+      <c r="M61" s="239"/>
+      <c r="N61" s="239"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C62" s="239"/>
+      <c r="D62" s="239"/>
+      <c r="E62" s="239"/>
+      <c r="F62" s="239"/>
+      <c r="G62" s="239"/>
+      <c r="H62" s="239"/>
+      <c r="I62" s="239"/>
+      <c r="J62" s="239"/>
+      <c r="K62" s="239"/>
+      <c r="L62" s="239"/>
+      <c r="M62" s="239"/>
+      <c r="N62" s="239"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C63" s="239"/>
+      <c r="D63" s="239"/>
+      <c r="E63" s="239"/>
+      <c r="F63" s="239"/>
+      <c r="G63" s="239"/>
+      <c r="H63" s="239"/>
+      <c r="I63" s="239"/>
+      <c r="J63" s="239"/>
+      <c r="K63" s="239"/>
+      <c r="L63" s="239"/>
+      <c r="M63" s="239"/>
+      <c r="N63" s="239"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
@@ -6707,6 +7148,11 @@
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="I5:I6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -6716,16 +7162,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="48"/>
       <c r="B1" s="49"/>
       <c r="C1" s="49"/>
@@ -6749,7 +7195,7 @@
       </c>
       <c r="O1" s="52"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="49"/>
       <c r="B2" s="51"/>
       <c r="C2" s="51"/>
@@ -6768,7 +7214,7 @@
       <c r="N2" s="49"/>
       <c r="O2" s="49"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="49"/>
       <c r="B3" s="51"/>
       <c r="C3" s="51"/>
@@ -6791,7 +7237,7 @@
       </c>
       <c r="O3" s="54"/>
     </row>
-    <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
@@ -6812,7 +7258,7 @@
       <c r="N4" s="49"/>
       <c r="O4" s="49"/>
     </row>
-    <row r="5" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="250" t="s">
         <v>74</v>
       </c>
@@ -6857,7 +7303,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="251"/>
       <c r="B6" s="251"/>
       <c r="C6" s="56" t="s">
@@ -6892,7 +7338,7 @@
       <c r="N6" s="251"/>
       <c r="O6" s="251"/>
     </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15">
         <v>1</v>
       </c>
@@ -6938,7 +7384,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
         <v>2</v>
       </c>
@@ -6984,7 +7430,7 @@
         <v>12569.682901267399</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15">
         <v>3</v>
       </c>
@@ -7030,7 +7476,7 @@
         <v>9919.7751374005984</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
         <v>4</v>
       </c>
@@ -7076,7 +7522,7 @@
         <v>14159.627559587479</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15">
         <v>5</v>
       </c>
@@ -7122,7 +7568,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <v>6</v>
       </c>
@@ -7168,7 +7614,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15">
         <v>7</v>
       </c>
@@ -7214,7 +7660,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15">
         <v>8</v>
       </c>
@@ -7260,7 +7706,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15">
         <v>9</v>
       </c>
@@ -7306,7 +7752,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15">
         <v>10</v>
       </c>
@@ -7352,7 +7798,7 @@
         <v>13629.64600681412</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15">
         <v>11</v>
       </c>
@@ -7398,7 +7844,7 @@
         <v>13099.66445404076</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15">
         <v>12</v>
       </c>
@@ -7444,7 +7890,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="15">
         <v>13</v>
       </c>
@@ -7490,7 +7936,7 @@
         <v>12569.682901267399</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15">
         <v>14</v>
       </c>
@@ -7536,7 +7982,7 @@
         <v>9919.7751374005984</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="15">
         <v>15</v>
       </c>
@@ -7582,7 +8028,7 @@
         <v>14159.627559587479</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15">
         <v>16</v>
       </c>
@@ -7628,7 +8074,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="15">
         <v>17</v>
       </c>
@@ -7674,7 +8120,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15">
         <v>18</v>
       </c>
@@ -7720,7 +8166,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15">
         <v>19</v>
       </c>
@@ -7766,7 +8212,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15">
         <v>20</v>
       </c>
@@ -7812,7 +8258,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15">
         <v>21</v>
       </c>
@@ -7858,7 +8304,7 @@
         <v>13629.64600681412</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15">
         <v>22</v>
       </c>
@@ -7904,7 +8350,7 @@
         <v>13099.66445404076</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="15"/>
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
@@ -7921,7 +8367,7 @@
       <c r="N29" s="6"/>
       <c r="O29" s="6"/>
     </row>
-    <row r="30" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
       <c r="B30" s="14"/>
       <c r="C30" s="57">
@@ -7962,7 +8408,7 @@
         <v>264873.42966686888</v>
       </c>
     </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E33" s="33"/>
       <c r="F33" s="33"/>
     </row>
